--- a/InfoSummary.xlsx
+++ b/InfoSummary.xlsx
@@ -20,11 +20,11 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">学位!$A$1:$M$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">综述!$A$1:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">综述!$A$1:$N$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">框架!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">模型!$A$1:$N$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Swap!$A$1:$P$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Recomp!$A$1:$P$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">模型!$A$1:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Swap!$A$1:$P$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Recomp!$A$1:$P$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hybrid!$A$1:$P$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">MAS!$A$1:$P$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">电子书!$A$1:$J$3</definedName>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1371" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="992">
   <si>
     <t>序号</t>
   </si>
@@ -389,6 +389,36 @@
     <t>资源</t>
   </si>
   <si>
+    <t>v1</t>
+  </si>
+  <si>
+    <t>arXiv:2001.08361</t>
+  </si>
+  <si>
+    <t>OpenAI</t>
+  </si>
+  <si>
+    <t>Scaling Laws for Neural Language Models</t>
+  </si>
+  <si>
+    <t>综述;Scaling Laws;</t>
+  </si>
+  <si>
+    <t>[1]Kaplan J, McCandlish S, Henighan T, et al. Scaling laws for neural language models[J]. arXiv preprint arXiv:2001.08361, 2020.</t>
+  </si>
+  <si>
+    <t>kaplan2020scaling</t>
+  </si>
+  <si>
+    <t>论文地址：https://arxiv.org/abs/2001.08361
+论文翻译：https://yiyibooks.cn/arxiv/2001.08361v1/index.html
+论文博客1：https://zhuanlan.zhihu.com/p/692024380
+论文博客2：https://zhuanlan.zhihu.com/p/667489780</t>
+  </si>
+  <si>
+    <t>可参考综述;强调增大模型规模;</t>
+  </si>
+  <si>
     <t>T2刊</t>
   </si>
   <si>
@@ -404,174 +434,233 @@
     <t>内存管理;深度学习;内存交换;重计算;内存共享;压缩;</t>
   </si>
   <si>
+    <t>综述;单个设备训练显存优化</t>
+  </si>
+  <si>
+    <t>[1]马玮良,彭轩,熊倩,等.深度学习中的内存管理问题研究综述[J].大数据,2020,6(04):56-68.</t>
+  </si>
+  <si>
+    <t>CNKI-20250304154636911</t>
+  </si>
+  <si>
+    <t>重要综述;</t>
+  </si>
+  <si>
+    <t>SCI二区</t>
+  </si>
+  <si>
+    <t>AIR</t>
+  </si>
+  <si>
+    <t>PIEAS（巴铁）</t>
+  </si>
+  <si>
+    <t>A survey of the recent architectures of deep convolutional neural networks</t>
+  </si>
+  <si>
+    <t>Deep learning,Convolutional neural networks,Taxonomy,Representational capacity,Residual learning,Channel boosted CNN</t>
+  </si>
+  <si>
+    <t>综述;CNN;</t>
+  </si>
+  <si>
+    <t>[1]Khan A, Sohail A, Zahoora U, et al. A survey of the recent architectures of deep convolutional neural networks[J]. Artificial intelligence review, 2020, 53: 5455-5516.</t>
+  </si>
+  <si>
+    <t>khan2020survey</t>
+  </si>
+  <si>
+    <t>论文地址：https://arxiv.org/abs/1901.06032</t>
+  </si>
+  <si>
+    <t>可参考综述;</t>
+  </si>
+  <si>
+    <t>v2</t>
+  </si>
+  <si>
+    <t>arXiv:2106.04554</t>
+  </si>
+  <si>
+    <t>复旦</t>
+  </si>
+  <si>
+    <t>A Survey of Transformers</t>
+  </si>
+  <si>
+    <t>Transformer,Self-attention,Pre-trained models,Deep learning.</t>
+  </si>
+  <si>
+    <t>综述;Transformer;</t>
+  </si>
+  <si>
+    <t>[1]Lin T, Wang Y, Liu X, et al. A Survey of Transformers[J]. arXiv preprint arXiv:2106.04554, 2021.</t>
+  </si>
+  <si>
+    <t>lin2021survey</t>
+  </si>
+  <si>
+    <t>论文地址1：https://arxiv.org/abs/2106.04554
+论文地址2：https://www.sciencedirect.com/science/article/pii/S2666651022000146
+论文翻译：https://yiyibooks.cn/arxiv/2106.04554v2/index.html</t>
+  </si>
+  <si>
+    <t>A会</t>
+  </si>
+  <si>
+    <t>IJCAI</t>
+  </si>
+  <si>
+    <t>Skoltech</t>
+  </si>
+  <si>
+    <t>Survey on Efficient Training of Large Neural Networks</t>
+  </si>
+  <si>
+    <t>综述; LLM训练;内存;计算;通信;</t>
+  </si>
+  <si>
+    <t>[1]Gusak J, Cherniuk D, Shilova A, et al. Survey on Efficient Training of Large Neural Networks[C]//IJCAI. 2022: 5494-5501.</t>
+  </si>
+  <si>
+    <t>gusak2022survey</t>
+  </si>
+  <si>
+    <t>论文地址1：https://www.ijcai.org/proceedings/2022/769
+论文地址2：https://arxiv.org/abs/2202.10435
+论文博客：https://mp.weixin.qq.com/s/JoME47vT7FumM1AHBLeo2w</t>
+  </si>
+  <si>
+    <t>不参考;</t>
+  </si>
+  <si>
+    <t>NeurIPS</t>
+  </si>
+  <si>
+    <t>DeepMind</t>
+  </si>
+  <si>
+    <t>Training Compute-Optimal Large Language Models</t>
+  </si>
+  <si>
+    <t>[1]Hoffmann J, Borgeaud S, Mensch A, et al. Training compute-optimal large language models[C]//Proceedings of the 36th International Conference on Neural Information Processing Systems. 2022: 30016-30030.</t>
+  </si>
+  <si>
+    <t>hoffmann2022training</t>
+  </si>
+  <si>
+    <t>论文地址1：https://dl.acm.org/doi/10.5555/3600270.3602446
+论文地址2：https://arxiv.org/abs/2203.15556
+论文翻译：https://yiyibooks.cn/arxiv/2203.15556v1/index.html
+论文博客：https://zhuanlan.zhihu.com/p/692024380</t>
+  </si>
+  <si>
+    <t>可参考综述;强调增大数据集规模;</t>
+  </si>
+  <si>
+    <t>T1刊</t>
+  </si>
+  <si>
+    <t>中国科学:信息科学</t>
+  </si>
+  <si>
+    <t>国防科大</t>
+  </si>
+  <si>
+    <t>并行智能训练技术:挑战与发展</t>
+  </si>
+  <si>
+    <t>智能训练;高性能计算;并行智能训练;深度学习;</t>
+  </si>
+  <si>
+    <t>综述;并行智能训练技术</t>
+  </si>
+  <si>
+    <t>[1]卢凯,赖志权,李笙维,等.并行智能训练技术:挑战与发展[J].中国科学:信息科学,2023,53(08):1441-1468.</t>
+  </si>
+  <si>
+    <t>CNKI-20250304153106953</t>
+  </si>
+  <si>
+    <t>论文地址：https://www.sciengine.com/SSI/doi/10.1360/SSI-2023-0051；</t>
+  </si>
+  <si>
+    <t>重要综述;重点关注文中的单进程内存优化;</t>
+  </si>
+  <si>
+    <t>软件学报</t>
+  </si>
+  <si>
+    <t>面向深度学习训练的内存交换机制综述</t>
+  </si>
+  <si>
+    <t>深度学习训练;内存交换;内存需求特征;</t>
+  </si>
+  <si>
+    <t>综述;训练;内存交换;</t>
+  </si>
+  <si>
+    <t>[1]高赫然,吴恒,许源佳,等.面向深度学习训练的内存交换机制综述[J].软件学报,2023,34(12):5862-5886.DOI:10.13328/j.cnki.jos.006800.</t>
+  </si>
+  <si>
+    <t>CNKI-20250304154044099</t>
+  </si>
+  <si>
+    <t>重要综述;对内存交换相关的工作分析、分类得非常深入;</t>
+  </si>
+  <si>
+    <t>普刊</t>
+  </si>
+  <si>
+    <t>电子元器件与信息技术</t>
+  </si>
+  <si>
+    <t>北京机电工程研究所</t>
+  </si>
+  <si>
+    <t>国内外深度学习框架分析与研究</t>
+  </si>
+  <si>
+    <t>人工智能;深度学习框架;智能时代;开源社区;</t>
+  </si>
+  <si>
+    <t>综述;深度学习框架;</t>
+  </si>
+  <si>
+    <t>[1]薛晨兴.国内外深度学习框架分析与研究[J].电子元器件与信息技术,2023,7(05):66-71+87.DOI:10.19772/j.cnki.2096-4455.2023.5.017.</t>
+  </si>
+  <si>
+    <t>CNKI-20250308230919125</t>
+  </si>
+  <si>
+    <t>调研世界</t>
+  </si>
+  <si>
+    <t>对外经贸</t>
+  </si>
+  <si>
+    <t>深度学习框架发展综述</t>
+  </si>
+  <si>
+    <t>深度学习框架;深度学习平台;MindSpore;TensorFlow;PyTorch;</t>
+  </si>
+  <si>
+    <t>[1]唐晓彬,沈童.深度学习框架发展综述[J].调研世界,2023,(04):83-88.DOI:10.13778/j.cnki.11-3705/c.2023.04.009.</t>
+  </si>
+  <si>
+    <t>CNKI-20250308231905390</t>
+  </si>
+  <si>
+    <t>arXiv:2302.14017</t>
+  </si>
+  <si>
+    <t>伯克利</t>
+  </si>
+  <si>
+    <t>Full Stack Optimization of Transformer Inference: a Survey</t>
+  </si>
+  <si>
     <t>综述;</t>
-  </si>
-  <si>
-    <t>[1]马玮良,彭轩,熊倩,等.深度学习中的内存管理问题研究综述[J].大数据,2020,6(04):56-68.</t>
-  </si>
-  <si>
-    <t>CNKI-20250304154636911</t>
-  </si>
-  <si>
-    <t>SCI二区</t>
-  </si>
-  <si>
-    <t>AIR</t>
-  </si>
-  <si>
-    <t>PIEAS（巴铁）</t>
-  </si>
-  <si>
-    <t>A survey of the recent architectures of deep convolutional neural networks</t>
-  </si>
-  <si>
-    <t>Deep learning,Convolutional neural networks,Taxonomy,Representational capacity,Residual learning,Channel boosted CNN</t>
-  </si>
-  <si>
-    <t>[1]Khan A, Sohail A, Zahoora U, et al. A survey of the recent architectures of deep convolutional neural networks[J]. Artificial intelligence review, 2020, 53: 5455-5516.</t>
-  </si>
-  <si>
-    <t>khan2020survey</t>
-  </si>
-  <si>
-    <t>论文地址：https://arxiv.org/abs/1901.06032</t>
-  </si>
-  <si>
-    <t>v2</t>
-  </si>
-  <si>
-    <t>arXiv:2106.04554</t>
-  </si>
-  <si>
-    <t>复旦</t>
-  </si>
-  <si>
-    <t>A Survey of Transformers</t>
-  </si>
-  <si>
-    <t>Transformer,Self-attention,Pre-trained models,Deep learning.</t>
-  </si>
-  <si>
-    <t>[1]Lin T, Wang Y, Liu X, et al. A Survey of Transformers[J]. arXiv preprint arXiv:2106.04554, 2021.</t>
-  </si>
-  <si>
-    <t>lin2021survey</t>
-  </si>
-  <si>
-    <t>论文地址1：https://arxiv.org/abs/2106.04554
-论文地址2：https://www.sciencedirect.com/science/article/pii/S2666651022000146</t>
-  </si>
-  <si>
-    <t>A会</t>
-  </si>
-  <si>
-    <t>IJCAI</t>
-  </si>
-  <si>
-    <t>Skoltech</t>
-  </si>
-  <si>
-    <t>Survey on Efficient Training of Large Neural Networks</t>
-  </si>
-  <si>
-    <t>[1]Gusak J, Cherniuk D, Shilova A, et al. Survey on Efficient Training of Large Neural Networks[C]//IJCAI. 2022: 5494-5501.</t>
-  </si>
-  <si>
-    <t>gusak2022survey</t>
-  </si>
-  <si>
-    <t>论文地址1：https://www.ijcai.org/proceedings/2022/769
-论文地址2：https://arxiv.org/abs/2202.10435</t>
-  </si>
-  <si>
-    <t>T1刊</t>
-  </si>
-  <si>
-    <t>中国科学:信息科学</t>
-  </si>
-  <si>
-    <t>国防科大</t>
-  </si>
-  <si>
-    <t>并行智能训练技术:挑战与发展</t>
-  </si>
-  <si>
-    <t>智能训练;高性能计算;并行智能训练;深度学习;</t>
-  </si>
-  <si>
-    <t>[1]卢凯,赖志权,李笙维,等.并行智能训练技术:挑战与发展[J].中国科学:信息科学,2023,53(08):1441-1468.</t>
-  </si>
-  <si>
-    <t>CNKI-20250304153106953</t>
-  </si>
-  <si>
-    <t>论文地址：https://www.sciengine.com/SSI/doi/10.1360/SSI-2023-0051；</t>
-  </si>
-  <si>
-    <t>软件学报</t>
-  </si>
-  <si>
-    <t>面向深度学习训练的内存交换机制综述</t>
-  </si>
-  <si>
-    <t>深度学习训练;内存交换;内存需求特征;</t>
-  </si>
-  <si>
-    <t>[1]高赫然,吴恒,许源佳,等.面向深度学习训练的内存交换机制综述[J].软件学报,2023,34(12):5862-5886.DOI:10.13328/j.cnki.jos.006800.</t>
-  </si>
-  <si>
-    <t>CNKI-20250304154044099</t>
-  </si>
-  <si>
-    <t>普刊</t>
-  </si>
-  <si>
-    <t>电子元器件与信息技术</t>
-  </si>
-  <si>
-    <t>北京机电工程研究所</t>
-  </si>
-  <si>
-    <t>国内外深度学习框架分析与研究</t>
-  </si>
-  <si>
-    <t>人工智能;深度学习框架;智能时代;开源社区;</t>
-  </si>
-  <si>
-    <t>[1]薛晨兴.国内外深度学习框架分析与研究[J].电子元器件与信息技术,2023,7(05):66-71+87.DOI:10.19772/j.cnki.2096-4455.2023.5.017.</t>
-  </si>
-  <si>
-    <t>CNKI-20250308230919125</t>
-  </si>
-  <si>
-    <t>调研世界</t>
-  </si>
-  <si>
-    <t>对外经贸</t>
-  </si>
-  <si>
-    <t>深度学习框架发展综述</t>
-  </si>
-  <si>
-    <t>深度学习框架;深度学习平台;MindSpore;TensorFlow;PyTorch;</t>
-  </si>
-  <si>
-    <t>[1]唐晓彬,沈童.深度学习框架发展综述[J].调研世界,2023,(04):83-88.DOI:10.13778/j.cnki.11-3705/c.2023.04.009.</t>
-  </si>
-  <si>
-    <t>CNKI-20250308231905390</t>
-  </si>
-  <si>
-    <t>v1</t>
-  </si>
-  <si>
-    <t>arXiv:2302.14017</t>
-  </si>
-  <si>
-    <t>伯克利</t>
-  </si>
-  <si>
-    <t>Full Stack Optimization of Transformer Inference: a Survey</t>
   </si>
   <si>
     <t>[1]Kim S, Hooper C, Wattanawong T, et al. Full stack optimization of transformer inference: a survey[J]. arXiv preprint arXiv:2302.14017, 2023.</t>
@@ -619,6 +708,9 @@
     <t>Resource-efficient AIoT system, cross-level optimization, DL inference and training tasks.</t>
   </si>
   <si>
+    <t>综述;AIoT训推;单卡多卡;</t>
+  </si>
+  <si>
     <t>[1]Liu S, Guo B, Fang C, et al. Enabling resource-efficient aiot system with cross-level optimization: A survey[J]. IEEE Communications Surveys &amp; Tutorials, 2023, 26(1): 389-427.</t>
   </si>
   <si>
@@ -640,13 +732,20 @@
     <t>Classification, computer vision (CV), detec_x0002_tion, point clouds, segmentation, self-supervision, visual-linguistic pretraining, visual Transformer.</t>
   </si>
   <si>
+    <t>综述;视觉Transformer;</t>
+  </si>
+  <si>
     <t>[1]Liu Y, Zhang Y, Wang Y, et al. A survey of visual transformers[J]. IEEE Transactions on Neural Networks and Learning Systems, 2023.</t>
   </si>
   <si>
     <t>liu2023survey</t>
   </si>
   <si>
-    <t>论文地址：https://arxiv.org/abs/2111.06091</t>
+    <t>论文地址：https://arxiv.org/abs/2111.06091
+论文翻译：https://yiyibooks.cn/arxiv/2106.04554v2/index.html</t>
+  </si>
+  <si>
+    <t>不参考;只是不需要了;</t>
   </si>
   <si>
     <t>莫纳什大学（澳）</t>
@@ -662,7 +761,8 @@
   </si>
   <si>
     <t>论文地址1：https://dl.acm.org/doi/abs/10.24963/ijcai.2023/764
-论文地址2：https://arxiv.org/abs/2302.01107</t>
+论文地址2：https://arxiv.org/abs/2302.01107
+论文翻译：https://yiyibooks.cn/arxiv/2302.01107v3/index.html</t>
   </si>
   <si>
     <t>计算机工程</t>
@@ -677,12 +777,18 @@
     <t>通用图形处理器;统一内存;显存超额订阅;数据管理;异构系统;</t>
   </si>
   <si>
+    <t>综述;CUDA UM;内存交换;</t>
+  </si>
+  <si>
     <t>[1]庞文豪,王嘉伦,翁楚良.GPGPU和CUDA统一内存研究现状综述[J].计算机工程,2024,50(12):1-15.DOI:10.19678/j.issn.1000-3428.0068694.</t>
   </si>
   <si>
     <t>CNKI-20250304155141873</t>
   </si>
   <si>
+    <t>弱参考综述;</t>
+  </si>
+  <si>
     <t>T3刊</t>
   </si>
   <si>
@@ -698,6 +804,9 @@
     <t>大语言模型;Transformer;注意力;</t>
   </si>
   <si>
+    <t>综述;LLM推理;LLM模型;</t>
+  </si>
+  <si>
     <t>[1]朱炫鹏,姚海东,刘隽,等.大语言模型算法演进综述[J].中兴通讯技术,2024,30(02):9-20.</t>
   </si>
   <si>
@@ -714,6 +823,9 @@
   </si>
   <si>
     <t>Large Language Models; Distributed Training; Machine Learning Systems.</t>
+  </si>
+  <si>
+    <t>综述;LLM训练;并行通信内存计算容错;</t>
   </si>
   <si>
     <t>[1]Duan J, Zhang S, Wang Z, et al. Efficient training of large language models on distributed infrastructures: a survey[J]. arXiv preprint arXiv:2407.20018, 2024.</t>
@@ -738,13 +850,19 @@
     <t>Computational modeling,Training data,Transformers,Bandwidth,Arithmetic,Hardware,Data models,Unsupervised learning,Artificial intelligence,Memory management</t>
   </si>
   <si>
+    <t>综述;AI 内存墙;背景;挑战;</t>
+  </si>
+  <si>
     <t>[1]Amir Gholami;Zhewei Yao;Sehoon Kim;Coleman Hooper;Michael W. Mahoney;Kurt Keutzer.AI and Memory Wall[J].IEEE Micro,2024,Vol.44(3): 33-39</t>
   </si>
   <si>
     <t>gholami2024ai</t>
   </si>
   <si>
-    <t>论文地址：https://ieeexplore.ieee.org/abstract/document/10477550</t>
+    <t>论文地址：https://ieeexplore.ieee.org/abstract/document/10477550
+论文翻译：https://yiyibooks.cn/arxiv/2403.14123v1/index.html
+论文博客：https://medium.com/riselab/ai-and-memory-wall-2cb4265cb0b8
+博客翻译：https://zhuanlan.zhihu.com/p/363041668</t>
   </si>
   <si>
     <t>arXiv:2401.15347</t>
@@ -756,6 +874,9 @@
     <t>A Comprehensive Survey of Compression Algorithms for Language Models</t>
   </si>
   <si>
+    <t>综述;LLM训推;模型压缩算法;</t>
+  </si>
+  <si>
     <t>[1]Park S, Choi J, Lee S, et al. A comprehensive survey of compression algorithms for language models[J]. arXiv preprint arXiv:2401.15347, 2024.</t>
   </si>
   <si>
@@ -765,6 +886,9 @@
     <t>论文地址：https://arxiv.org/abs/2401.15347</t>
   </si>
   <si>
+    <t>可参考综述;用来了解模型压缩算法;</t>
+  </si>
+  <si>
     <t>v4</t>
   </si>
   <si>
@@ -775,6 +899,9 @@
   </si>
   <si>
     <t>Efficient Large Language Models: A Survey</t>
+  </si>
+  <si>
+    <t>综述;LLM训推;模型数据框架;</t>
   </si>
   <si>
     <t>[1]Wan Z, Wang X, Liu C, et al. Efficient large language models: A survey[J]. arXiv preprint arXiv:2312.03863, 2023.</t>
@@ -785,13 +912,14 @@
   <si>
     <t>论文地址1：https://openreview.net/forum?id=bsCCJHbO8A
 论文地址2：https://arxiv.org/abs/2312.03863
+论文翻译：https://yiyibooks.cn/arxiv/2312.03863v2/index.html
 论文仓库：https://github.com/AIoT-MLSys-Lab/Efficient-LLMs-Survey</t>
   </si>
   <si>
-    <t>这篇论文已经被TMLR 2025接收;</t>
-  </si>
-  <si>
-    <t>v15</t>
+    <t>可参考综述;这篇论文已经被TMLR 2025接收;思维导图画得不错;</t>
+  </si>
+  <si>
+    <t>v16</t>
   </si>
   <si>
     <t>arXiv:2303.18223</t>
@@ -806,14 +934,22 @@
     <t>Large Language Models; Emergent Abilities; Adaptation Tuning; Utilization; Alignment; Capacity Evaluation</t>
   </si>
   <si>
-    <t>[1]Zhao W X, Zhou K, Li J, et al. A Survey of Large Language Models[J]. arXiv preprint arXiv:2303.18223, 2023.</t>
+    <t>综述;LLM;</t>
+  </si>
+  <si>
+    <t>[1]Zhao W X, Zhou K, Li J, et al. A survey of large language models[J]. arXiv preprint arXiv:2303.18223, 2023, 1(2).</t>
   </si>
   <si>
     <t>zhao2023survey</t>
   </si>
   <si>
     <t>论文地址：https://arxiv.org/abs/2303.18223
-论文仓库：https://github.com/rucaibox/llmsurvey</t>
+论文仓库：https://github.com/rucaibox/llmsurvey
+论文翻译：https://yiyibooks.cn/arxiv/2303.18223v15/index.html
+中文书：https://llmbook-zh.github.io/</t>
+  </si>
+  <si>
+    <t>重要综述;一篇涵盖LLM方方面面的优质综述;</t>
   </si>
   <si>
     <t>OJ-CS</t>
@@ -828,13 +964,20 @@
     <t>Foundation model system, training, serving, network, computing, storage.</t>
   </si>
   <si>
+    <t>综述;LLM训推;通信存储计算;</t>
+  </si>
+  <si>
     <t>[1]Zhou J, Chen Y, Hong Z, et al. Training and serving system of foundation models: A comprehensive survey[J]. IEEE Open Journal of the Computer Society, 2024.</t>
   </si>
   <si>
     <t>zhou2024training</t>
   </si>
   <si>
-    <t>论文地址：https://ieeexplore.ieee.org/abstract/document/10478189</t>
+    <t>论文地址1：https://ieeexplore.ieee.org/abstract/document/10478189
+论文地址2：https://arxiv.org/abs/2401.02643</t>
+  </si>
+  <si>
+    <t>弱参考综述;没什么亮点;</t>
   </si>
   <si>
     <t>清华</t>
@@ -846,12 +989,18 @@
     <t>大模型;存储系统;数据管理;存储扩容;数据容错;</t>
   </si>
   <si>
+    <t>综述;LLM训推存储系统;</t>
+  </si>
+  <si>
     <t>[1]冯杨洋,汪庆,舒继武.大模型时代下的存储系统挑战与技术发展[J].大数据,2025,11(01):79-91.</t>
   </si>
   <si>
     <t>CNKI-20250305193439265</t>
   </si>
   <si>
+    <t>可参考综述;引用的相关工作太少了;</t>
+  </si>
+  <si>
     <t>计算机学报</t>
   </si>
   <si>
@@ -861,6 +1010,9 @@
     <t>深度学习;数据存储技术;数据加载优化;数据预处理优化;模型计算优化;</t>
   </si>
   <si>
+    <t>综述;Storage for AI;训练;</t>
+  </si>
+  <si>
     <t>[1]贺巩山,赵传磊,蒋金虎,等.面向深度学习的数据存储技术综述[J/OL].计算机学报,1-56[2025-0308].http://kns.cnki.net/kcms/detail/11.1826.tp.20250217.0938.002.html.</t>
   </si>
   <si>
@@ -870,6 +1022,9 @@
     <t>作者博客：https://www.hegongshan.com/cv/</t>
   </si>
   <si>
+    <t>可参考综述;重点关注“5.1 模型状态存储技术”；</t>
+  </si>
+  <si>
     <t>软件导刊</t>
   </si>
   <si>
@@ -882,12 +1037,18 @@
     <t>训练性能;深度学习;前向计算;反向传播;参数更新;负载均衡;</t>
   </si>
   <si>
+    <t>综述;训练流程各优化技术;</t>
+  </si>
+  <si>
     <t>[1]介飞,张海俊,汪锦想.深度学习训练性能优化：原理、技术与工具[J/OL].软件导刊,1-7[2025-03-08].http://kns.cnki.net/kcms/detail/42.1671.TP.20250220.1643.024.html.</t>
   </si>
   <si>
     <t>CNKI-20250308222920968</t>
   </si>
   <si>
+    <t>弱参考综述;样样都有，样样不精;</t>
+  </si>
+  <si>
     <t>C刊</t>
   </si>
   <si>
@@ -903,13 +1064,20 @@
     <t>Large language model, hardware-software co-design.</t>
   </si>
   <si>
+    <t>综述;LLM训推;模型算法;软硬件;</t>
+  </si>
+  <si>
     <t>[1]Guo C, Cheng F, Du Z, et al. A Survey: Collaborative Hardware and Software Design in the Era of Large Language Models[J]. IEEE Circuits and Systems Magazine, 2025, 25(1): 35-57.</t>
   </si>
   <si>
     <t>guo2025survey</t>
   </si>
   <si>
-    <t>论文地址：https://arxiv.org/abs/2410.07265</t>
+    <t>论文地址：https://arxiv.org/abs/2410.07265
+论文翻译：https://yiyibooks.cn/arxiv/2410.07265v1/index.html</t>
+  </si>
+  <si>
+    <t>重要综述;图表稍微少了点;</t>
   </si>
   <si>
     <t>arXiv:2412.19442</t>
@@ -921,6 +1089,9 @@
     <t>A Survey on Large Language Model Acceleration based on KV Cache Management</t>
   </si>
   <si>
+    <t>综述;KV cache;LLM推理;</t>
+  </si>
+  <si>
     <t>[1]Li H, Li Y, Tian A, et al. A survey on large language model acceleration based on kv cache management[J]. arXiv preprint arXiv:2412.19442, 2024.</t>
   </si>
   <si>
@@ -928,9 +1099,37 @@
   </si>
   <si>
     <t>论文地址：https://arxiv.org/abs/2412.19442
+论文翻译：https://yiyibooks.cn/arxiv/2412.19442v2/index.html
 论文仓库：https://github.com/TreeAI-Lab/Awesome-KV-Cache-Management</t>
   </si>
   <si>
+    <t>B刊/T1刊</t>
+  </si>
+  <si>
+    <t>JCST</t>
+  </si>
+  <si>
+    <t>中科大&amp;计算所</t>
+  </si>
+  <si>
+    <t>AI Computing Systems for Large Language Models Training</t>
+  </si>
+  <si>
+    <t>artificial intelligence (AI) chip, large language model (LLM), AI computing system, accelerator</t>
+  </si>
+  <si>
+    <t>综述;LLM训练;模型算法;软硬件;</t>
+  </si>
+  <si>
+    <t>[1]Zhang Z X, Wen Y B, Lyu H Q, et al. AI Computing Systems for Large Language Models Training[J]. Journal of Computer Science and Technology, 2025, 40(1): 6-41.</t>
+  </si>
+  <si>
+    <t>zhang2025ai</t>
+  </si>
+  <si>
+    <t>论文地址：https://jcst.ict.ac.cn/article/cstr/32374.14.s11390-024-4178-1</t>
+  </si>
+  <si>
     <t>缩写</t>
   </si>
   <si>
@@ -982,6 +1181,9 @@
     <t>jia2014caffe</t>
   </si>
   <si>
+    <t>论文地址：https://arxiv.org/abs/1408.5093</t>
+  </si>
+  <si>
     <t>arXiv:1512.01274</t>
   </si>
   <si>
@@ -1021,10 +1223,8 @@
     <t>abadi2016tensorflow</t>
   </si>
   <si>
-    <t>论文地址：https://www.usenix.org/conference/osdi16/technical-sessions/presentation/abadi</t>
-  </si>
-  <si>
-    <t>NeurIPS</t>
+    <t>论文地址：https://www.usenix.org/conference/osdi16/technical-sessions/presentation/abadi
+论文翻译：https://zhuanlan.zhihu.com/p/638373346</t>
   </si>
   <si>
     <t>Meta</t>
@@ -1042,7 +1242,9 @@
     <t>paszke2019pytorch</t>
   </si>
   <si>
-    <t>论文地址：https://proceedings.neurips.cc/paper/2019/hash/bdbca288fee7f92f2bfa9f7012727740-Abstract.html</t>
+    <t>论文地址1：https://proceedings.neurips.cc/paper/2019/hash/bdbca288fee7f92f2bfa9f7012727740-Abstract.html
+论文地址2：https://arxiv.org/abs/1912.01703
+论文翻译：https://zhuanlan.zhihu.com/p/639060886</t>
   </si>
   <si>
     <t>数据与计算发展前沿</t>
@@ -1481,9 +1683,6 @@
     <t>arXiv:2303.08774</t>
   </si>
   <si>
-    <t>OpenAI</t>
-  </si>
-  <si>
     <t>GPT-4 Technical Report</t>
   </si>
   <si>
@@ -1785,6 +1984,27 @@
     <t>论文地址：https://arxiv.org/abs/1903.06631</t>
   </si>
   <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>UNIST（韩）</t>
+  </si>
+  <si>
+    <t>Hotness- and Lifetime-Aware Data Placement and Migration for High-Performance Deep Learning on Heterogeneous Memory Systems</t>
+  </si>
+  <si>
+    <t>HALO</t>
+  </si>
+  <si>
+    <t>Hotness-and lifetime-aware data placement and migration, high-performance deep learning, heterogeneous memory systems</t>
+  </si>
+  <si>
+    <t>[1]Han M, Hyun J, Park S, et al. Hotness-and lifetime-aware data placement and migration for high-performance deep learning on heterogeneous memory systems[J]. IEEE Transactions on Computers, 2019, 69(3): 377-391.</t>
+  </si>
+  <si>
+    <t>han2019hotness</t>
+  </si>
+  <si>
     <t>ASPLOS</t>
   </si>
   <si>
@@ -1846,6 +2066,27 @@
     <t>论文地址：https://dl.acm.org/doi/abs/10.1145/3369583.3392684</t>
   </si>
   <si>
+    <t>Euro-Par</t>
+  </si>
+  <si>
+    <t>INRIA（法）</t>
+  </si>
+  <si>
+    <t>Optimal GPU-CPU Offloading Strategies for Deep Neural Network Training</t>
+  </si>
+  <si>
+    <t>Memory management,Deep Neural Network,Dynamic programming,Scheduling</t>
+  </si>
+  <si>
+    <t>[1]Beaumont O, Eyraud-Dubois L, Shilova A. Optimal GPU-CPU offloading strategies for deep neural network training[C]//European Conference on Parallel Processing. Cham: Springer International Publishing, 2020: 151-166.</t>
+  </si>
+  <si>
+    <t>beaumont2020optimal</t>
+  </si>
+  <si>
+    <t>论文地址：https://link.springer.com/chapter/10.1007/978-3-030-57675-2_10</t>
+  </si>
+  <si>
     <t>FAST</t>
   </si>
   <si>
@@ -2037,6 +2278,9 @@
   </si>
   <si>
     <t>Training Deep Nets with Sublinear Memory Cost</t>
+  </si>
+  <si>
+    <t>Sublinear</t>
   </si>
   <si>
     <t>重计算;</t>
@@ -2054,6 +2298,22 @@
 代码仓库3：https://github.com/Lyken17/pytorch-memonger</t>
   </si>
   <si>
+    <t>Memory-Efficient Backpropagation Through Time</t>
+  </si>
+  <si>
+    <t>BPTT</t>
+  </si>
+  <si>
+    <t>[1]Gruslys A, Munos R, Danihelka I, et al. Memory-efficient backpropagation through time[J]. Advances in neural information processing systems, 2016, 29.</t>
+  </si>
+  <si>
+    <t>gruslys2016memory</t>
+  </si>
+  <si>
+    <t>论文地址1：https://proceedings.neurips.cc/paper/2016/hash/a501bebf79d570651ff601788ea9d16d-Abstract.html
+论文地址2：https://arxiv.org/abs/1606.03401</t>
+  </si>
+  <si>
     <t>Efficient Rematerialization for Deep Networks</t>
   </si>
   <si>
@@ -2066,12 +2326,25 @@
     <t>论文地址：https://proceedings.neurips.cc/paper/2019/hash/ffe10334251de1dc98339d99ae4743ba-Abstract.html</t>
   </si>
   <si>
+    <t>PFN（日）</t>
+  </si>
+  <si>
+    <t>A Graph Theoretic Framework of Recomputation Algorithms for Memory-Efficient Backpropagation</t>
+  </si>
+  <si>
+    <t>[1]Kusumoto M, Inoue T, Watanabe G, et al. A graph theoretic framework of recomputation algorithms for memory-efficient backpropagation[J]. Advances in Neural Information Processing Systems, 2019, 32.</t>
+  </si>
+  <si>
+    <t>kusumoto2019graph</t>
+  </si>
+  <si>
+    <t>论文地址：https://proceedings.neurips.cc/paper/2019/hash/e555ebe0ce426f7f9b2bef0706315e0c-Abstract.html
+代码仓库：https://github.com/pfnet-research/recompute</t>
+  </si>
+  <si>
     <t>arXiv:1911.13214</t>
   </si>
   <si>
-    <t>INRIA（法）</t>
-  </si>
-  <si>
     <t>Optimal checkpointing for heterogeneous chains: how to train deep neural networks with limited memory</t>
   </si>
   <si>
@@ -2087,8 +2360,10 @@
     <t>herrmann2019optimal</t>
   </si>
   <si>
-    <t>论文地址：https://arxiv.org/abs/1911.13214
-代码仓库：https://gitlab.inria.fr/hiepacs/rotor</t>
+    <t>论文地址1：https://inria.hal.science/hal-02352969
+论文地址2：https://arxiv.org/abs/1911.13214
+代码仓库：https://gitlab.inria.fr/hiepacs/rotor
+论文PPT：extension://ngbkcglbmlglgldjfcnhaijeecaccgfi/https://team.inria.fr/moliere/files/2021/07/LionelEyraudDubois.pdf</t>
   </si>
   <si>
     <t>MLSys</t>
@@ -2128,7 +2403,8 @@
     <t>zheng2020echo</t>
   </si>
   <si>
-    <t>代码仓库：https://issues.apache.org/jira/browse/MXNET-1450</t>
+    <t>论文地址：https://arxiv.org/abs/1805.08899v5
+代码仓库：https://issues.apache.org/jira/browse/MXNET-1450</t>
   </si>
   <si>
     <t>得克萨斯大学</t>
@@ -2286,7 +2562,8 @@
     <t>bartan2023moccasin</t>
   </si>
   <si>
-    <t>论文地址：https://proceedings.mlr.press/v202/bartan23a.html
+    <t>论文地址1：https://proceedings.mlr.press/v202/bartan23a.html
+论文地址2：https://arxiv.org/abs/2304.14463
 代码仓库：https://github.com/haoming-codes/moccasin</t>
   </si>
   <si>
@@ -2314,7 +2591,9 @@
     <t>zhao2023rockmate</t>
   </si>
   <si>
-    <t>论文地址：https://proceedings.mlr.press/v202/zhao23b.html
+    <t>论文地址1：https://proceedings.mlr.press/v202/zhao23b.html
+论文地址2：https://icml.cc/virtual/2023/oral/25451
+论文地址3：https://arxiv.org/abs/2307.01236
 代码仓库：https://github.com/topal-team/rockmate</t>
   </si>
   <si>
@@ -2431,9 +2710,6 @@
     <t>论文地址：https://proceedings.neurips.cc/paper/2021/hash/c8461bf13fca8a2b9912ab2eb1668e4b-Abstract.html</t>
   </si>
   <si>
-    <t>TC</t>
-  </si>
-  <si>
     <t>HOME: A Holistic GPU Memory Management Framework for Deep Learning</t>
   </si>
   <si>
@@ -2531,7 +2807,9 @@
     <t>patil2022poet</t>
   </si>
   <si>
-    <t>论文地址：https://proceedings.mlr.press/v162/patil22b.html
+    <t>论文地址1：https://proceedings.mlr.press/v162/patil22b.html
+论文地址2：https://icml.cc/virtual/2022/spotlight/18172
+论文地址3：https://arxiv.org/abs/2207.07697
 代码仓库：https://github.com/ShishirPatil/poet</t>
   </si>
   <si>
@@ -2718,7 +2996,8 @@
   </si>
   <si>
     <t>论文地址1：https://proceedings.mlr.press/v202/steiner23a.html
-论文地址2：https://arxiv.org/abs/2210.12924
+论文地址2：https://icml.cc/virtual/2023/poster/24377
+论文地址3：https://arxiv.org/abs/2210.12924
 代码仓库：https://github.com/facebookresearch/model_opt</t>
   </si>
   <si>
@@ -2830,6 +3109,18 @@
   <si>
     <t>电子书地址：https://pages.cs.wisc.edu/~remzi/OSTEP/
 中文版地址：https://github.com/iTanken/ostep-chinese</t>
+  </si>
+  <si>
+    <t>大语言模型</t>
+  </si>
+  <si>
+    <t>[1]赵鑫.大语言模型[M].北京：高等教育出版社,2024</t>
+  </si>
+  <si>
+    <t>LLMBook</t>
+  </si>
+  <si>
+    <t>电子书地址：https://llmbook-zh.github.io/</t>
   </si>
 </sst>
 </file>
@@ -2842,7 +3133,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2866,6 +3157,13 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.15"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3354,16 +3652,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3372,119 +3667,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3504,6 +3802,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3815,13 +4116,13 @@
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>537845</xdr:colOff>
-          <xdr:row>25</xdr:row>
+          <xdr:row>27</xdr:row>
           <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
@@ -3837,7 +4138,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1874520" y="11430000"/>
+              <a:off x="1874520" y="12344400"/>
               <a:ext cx="537845" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -3861,13 +4162,13 @@
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>537845</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
@@ -3883,7 +4184,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1874520" y="2743200"/>
+              <a:off x="1874520" y="3200400"/>
               <a:ext cx="537845" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4286,17 +4587,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="5.77777777777778" style="8" customWidth="1"/>
-    <col min="2" max="5" width="10.7777777777778" style="8" customWidth="1"/>
-    <col min="6" max="6" width="20.7777777777778" style="8" customWidth="1"/>
-    <col min="7" max="8" width="10.7777777777778" style="8" customWidth="1"/>
+    <col min="1" max="1" width="5.77777777777778" style="9" customWidth="1"/>
+    <col min="2" max="5" width="10.7777777777778" style="9" customWidth="1"/>
+    <col min="6" max="6" width="20.7777777777778" style="9" customWidth="1"/>
+    <col min="7" max="8" width="10.7777777777778" style="9" customWidth="1"/>
     <col min="9" max="9" width="10.7777777777778" style="1" customWidth="1"/>
-    <col min="10" max="13" width="20.7777777777778" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="8.88888888888889" style="8"/>
+    <col min="10" max="13" width="20.7777777777778" style="9" customWidth="1"/>
+    <col min="14" max="16384" width="8.88888888888889" style="9"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:13">
@@ -4780,7 +5083,7 @@
       </c>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" s="8" customFormat="1" ht="36" customHeight="1" spans="1:13">
+    <row r="13" s="9" customFormat="1" ht="36" customHeight="1" spans="1:13">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -4828,6 +5131,7 @@
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="71" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -4848,7 +5152,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -4904,9 +5208,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:14">
+    <row r="2" s="1" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A2" s="3">
-        <f t="shared" ref="A2:A27" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A7" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="3">
@@ -4924,27 +5228,29 @@
       <c r="F2" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="3"/>
+      <c r="H2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3">
+        <v>3086</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="I2" s="3">
-        <v>16</v>
-      </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="str">
+        <f t="shared" ref="L2:L7" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+        <v>2020_arXiv:2001.08361_v1_Scaling Laws for Neural Language Models</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="L2" s="3" t="str">
-        <f t="shared" ref="L2:L27" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
-        <v>2020_大数据_T2刊_深度学习中的内存管理问题研究综述</v>
-      </c>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="N2" s="3" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:14">
       <c r="A3" s="3">
@@ -4955,40 +5261,40 @@
         <v>2020</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="I3" s="3">
-        <v>3422</v>
+        <v>16</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L3" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2020_AIR_SCI二区_A survey of the recent architectures of deep convolutional neural networks</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="N3" s="3"/>
+        <v>2020_大数据_T2刊_深度学习中的内存管理问题研究综述</v>
+      </c>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:14">
       <c r="A4" s="3">
@@ -4996,43 +5302,45 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="I4" s="3">
-        <v>1501</v>
+        <v>3422</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L4" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2021_arXiv:2106.04554_v2_A Survey of Transformers</v>
+        <v>2020_AIR_SCI二区_A survey of the recent architectures of deep convolutional neural networks</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N4" s="3"/>
+        <v>139</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:14">
       <c r="A5" s="3">
@@ -5040,85 +5348,89 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G5" s="3"/>
+        <v>144</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>145</v>
+      </c>
       <c r="H5" s="3" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="I5" s="3">
-        <v>14</v>
+        <v>1501</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="L5" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_IJCAI_A会_Survey on Efficient Training of Large Neural Networks</v>
+        <v>2021_arXiv:2106.04554_v2_A Survey of Transformers</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="N5" s="3"/>
+        <v>149</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:14">
-      <c r="A6" s="3">
+      <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I6" s="3">
-        <v>6</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="K6" s="3" t="s">
+      <c r="B6" s="7">
+        <v>2022</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="L6" s="3" t="str">
+      <c r="D6" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I6" s="7">
+        <v>14</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="L6" s="7" t="str">
         <f t="shared" si="1"/>
-        <v>2023_中国科学:信息科学_T1刊_并行智能训练技术:挑战与发展</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="N6" s="3"/>
+        <v>2022_IJCAI_A会_Survey on Efficient Training of Large Neural Networks</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:14">
       <c r="A7" s="3">
@@ -5126,907 +5438,1083 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>154</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I7" s="3">
-        <v>3</v>
+        <v>2010</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="L7" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2023_软件学报_T1刊_面向深度学习训练的内存交换机制综述</v>
-      </c>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
+        <f>B7&amp;"_"&amp;D7&amp;"_"&amp;C7&amp;"_"&amp;F7&amp;""</f>
+        <v>2022_NeurIPS_A会_Training Compute-Optimal Large Language Models</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:14">
       <c r="A8" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A8:A30" si="2">ROW()-1</f>
         <v>7</v>
       </c>
       <c r="B8" s="3">
         <v>2023</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>118</v>
+        <v>171</v>
       </c>
       <c r="I8" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L8" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2023_电子元器件与信息技术_普刊_国内外深度学习框架分析与研究</v>
-      </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
+        <f t="shared" ref="L8:L30" si="3">B8&amp;"_"&amp;D8&amp;"_"&amp;C8&amp;"_"&amp;F8&amp;""</f>
+        <v>2023_中国科学:信息科学_T1刊_并行智能训练技术:挑战与发展</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:14">
       <c r="A9" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="B9" s="3">
         <v>2023</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>165</v>
+        <v>46</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>118</v>
+        <v>179</v>
       </c>
       <c r="I9" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="L9" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2023_调研世界_普刊_深度学习框架发展综述</v>
+        <f t="shared" si="3"/>
+        <v>2023_软件学报_T1刊_面向深度学习训练的内存交换机制综述</v>
       </c>
       <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
+      <c r="N9" s="3" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:14">
       <c r="A10" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9</v>
       </c>
       <c r="B10" s="3">
         <v>2023</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G10" s="3"/>
+        <v>186</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="H10" s="3" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="I10" s="3">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="L10" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2023_arXiv:2302.14017_v1_Full Stack Optimization of Transformer Inference: a Survey</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="N10" s="3"/>
+        <f t="shared" si="3"/>
+        <v>2023_电子元器件与信息技术_普刊_国内外深度学习框架分析与研究</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:14">
       <c r="A11" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="B11" s="3">
         <v>2023</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>146</v>
+        <v>192</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="I11" s="3">
+        <v>27</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L11" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>2023_调研世界_普刊_深度学习框架发展综述</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:14">
+      <c r="A12" s="7">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="7">
+        <v>2023</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I12" s="7">
+        <v>99</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="L12" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>2023_arXiv:2302.14017_v1_Full Stack Optimization of Transformer Inference: a Survey</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:14">
+      <c r="A13" s="7">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="7">
+        <v>2023</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I13" s="7">
         <v>16</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="L11" s="3" t="str">
-        <f t="shared" si="1"/>
+      <c r="J13" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="L13" s="7" t="str">
+        <f t="shared" si="3"/>
         <v>2023_TPDS_A刊_A Survey on Auto-Parallelism of Large-Scale Deep Learning Training</v>
       </c>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:14">
-      <c r="A12" s="3">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I12" s="3">
-        <v>32</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="L12" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2023_IEEE ComST_SCI一区_Enabling Resource-Efficient AIoT System With Cross-Level Optimization: A Survey</v>
-      </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:14">
-      <c r="A13" s="3">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I13" s="3">
-        <v>353</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="L13" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2023_TNNLS_B刊_A Survey of Visual Transformers</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="N13" s="3"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:14">
       <c r="A14" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
       <c r="B14" s="3">
         <v>2023</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>138</v>
+        <v>211</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G14" s="3"/>
+        <v>213</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="H14" s="3" t="s">
-        <v>118</v>
+        <v>215</v>
       </c>
       <c r="I14" s="3">
+        <v>32</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>2023_IEEE ComST_SCI一区_Enabling Resource-Efficient AIoT System With Cross-Level Optimization: A Survey</v>
+      </c>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:14">
+      <c r="A15" s="7">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="7">
+        <v>2023</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I15" s="7">
+        <v>353</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="L15" s="7" t="str">
+        <f t="shared" si="3"/>
+        <v>2023_TNNLS_B刊_A Survey of Visual Transformers</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:14">
+      <c r="A16" s="7">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="7">
+        <v>2023</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I16" s="7">
         <v>66</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="L14" s="3" t="str">
-        <f t="shared" si="1"/>
+      <c r="J16" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="L16" s="7" t="str">
+        <f t="shared" si="3"/>
         <v>2023_IJCAI_A会_A Survey on Efficient Training of Transformers</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:14">
-      <c r="A15" s="3">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="3">
-        <v>2024</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="L15" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_计算机工程_T2刊_GPGPU和CUDA统一内存研究现状综述</v>
-      </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:14">
-      <c r="A16" s="3">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="3">
-        <v>2024</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I16" s="3">
-        <v>3</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="L16" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_中兴通讯技术_T3刊_大语言模型算法演进综述</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
+      <c r="M16" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:14">
       <c r="A17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="B17" s="3">
         <v>2024</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>118</v>
+        <v>237</v>
       </c>
       <c r="I17" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="L17" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_arXiv:2407.20018_v1_Efficient Training of Large Language Models on Distributed Infrastructures: A Survey</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="N17" s="3"/>
+        <f t="shared" si="3"/>
+        <v>2024_计算机工程_T2刊_GPGPU和CUDA统一内存研究现状综述</v>
+      </c>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:14">
       <c r="A18" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
       <c r="B18" s="3">
         <v>2024</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>172</v>
+        <v>243</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>118</v>
+        <v>246</v>
       </c>
       <c r="I18" s="3">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="L18" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_IEEE Micro_SCI三区_AI and Memory Wall</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="N18" s="3"/>
+        <f t="shared" si="3"/>
+        <v>2024_中兴通讯技术_T3刊_大语言模型算法演进综述</v>
+      </c>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:14">
       <c r="A19" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="B19" s="3">
         <v>2024</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="G19" s="3"/>
+        <v>251</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>252</v>
+      </c>
       <c r="H19" s="3" t="s">
-        <v>118</v>
+        <v>253</v>
       </c>
       <c r="I19" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="L19" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_arXiv:2401.15347_v1_A Comprehensive Survey of Compression Algorithms for Language Models</v>
+        <f t="shared" si="3"/>
+        <v>2024_arXiv:2407.20018_v1_Efficient Training of Large Language Models on Distributed Infrastructures: A Survey</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="N19" s="3"/>
+        <v>256</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:14">
       <c r="A20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>19</v>
       </c>
       <c r="B20" s="3">
         <v>2024</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G20" s="3"/>
+        <v>259</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="H20" s="3" t="s">
-        <v>118</v>
+        <v>261</v>
       </c>
       <c r="I20" s="3">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="L20" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_arXiv:2312.03863_v4_Efficient Large Language Models: A Survey</v>
+        <f t="shared" si="3"/>
+        <v>2024_IEEE Micro_SCI三区_AI and Memory Wall</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>243</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:14">
       <c r="A21" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="B21" s="3">
         <v>2024</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>244</v>
+        <v>113</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>248</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>118</v>
+        <v>268</v>
       </c>
       <c r="I21" s="3">
-        <v>3911</v>
+        <v>15</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="L21" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_arXiv:2303.18223_v15_A Survey of Large Language Models</v>
+        <f t="shared" si="3"/>
+        <v>2024_arXiv:2401.15347_v1_A Comprehensive Survey of Compression Algorithms for Language Models</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="N21" s="3"/>
+        <v>271</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:14">
       <c r="A22" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
       <c r="B22" s="3">
         <v>2024</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>157</v>
+        <v>273</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>255</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>118</v>
+        <v>277</v>
       </c>
       <c r="I22" s="3">
-        <v>10</v>
+        <v>146</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="L22" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_OJ-CS_普刊_Training and Serving System of Foundation Models: A Comprehensive Survey</v>
+        <f t="shared" si="3"/>
+        <v>2024_arXiv:2312.03863_v4_Efficient Large Language Models: A Survey</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="N22" s="3"/>
+        <v>280</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="23" ht="36" customHeight="1" spans="1:14">
       <c r="A23" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="B23" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>113</v>
+        <v>282</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>114</v>
+        <v>283</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>51</v>
+        <v>287</v>
+      </c>
+      <c r="I23" s="3">
+        <v>3964</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>262</v>
+        <v>288</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="L23" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2025_大数据_T2刊_大模型时代下的存储系统挑战与技术发展</v>
-      </c>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
+        <f t="shared" si="3"/>
+        <v>2024_arXiv:2303.18223_v16_A Survey of Large Language Models</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1" spans="1:14">
       <c r="A24" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="B24" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>131</v>
+        <v>293</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>51</v>
+        <v>296</v>
+      </c>
+      <c r="I24" s="3">
+        <v>10</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>268</v>
+        <v>298</v>
       </c>
       <c r="L24" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2025_计算机学报_T1刊_面向深度学习的数据存储技术综述</v>
+        <f t="shared" si="3"/>
+        <v>2024_OJ-CS_普刊_Training and Serving System of Foundation Models: A Comprehensive Survey</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="N24" s="3"/>
+        <v>299</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="25" ht="36" customHeight="1" spans="1:14">
       <c r="A25" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="B25" s="3">
         <v>2025</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>270</v>
+        <v>123</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I25" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="I25" s="8" t="s">
         <v>51</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
       <c r="L25" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2025_软件导刊_T3刊_深度学习训练性能优化：原理、技术与工具</v>
+        <f t="shared" si="3"/>
+        <v>2025_大数据_T2刊_大模型时代下的存储系统挑战与技术发展</v>
       </c>
       <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
+      <c r="N25" s="3" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="26" ht="36" customHeight="1" spans="1:14">
       <c r="A26" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="B26" s="3">
         <v>2025</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>276</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>278</v>
+        <v>143</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>279</v>
+        <v>309</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>280</v>
+        <v>310</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I26" s="7">
-        <v>5</v>
+        <v>311</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="L26" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2025_TCASI_C刊_A Survey: Collaborative Hardware and Software Design in the Era of Large Language Models</v>
+        <f t="shared" si="3"/>
+        <v>2025_计算机学报_T1刊_面向深度学习的数据存储技术综述</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="N26" s="3"/>
+        <v>314</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="27" ht="36" customHeight="1" spans="1:14">
       <c r="A27" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="B27" s="3">
         <v>2025</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>129</v>
+        <v>241</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>285</v>
+        <v>317</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="G27" s="3"/>
+        <v>318</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="H27" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I27" s="7">
+        <v>320</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="L27" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>2025_软件导刊_T3刊_深度学习训练性能优化：原理、技术与工具</v>
+      </c>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" spans="1:14">
+      <c r="A28" s="3">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="I28" s="8">
         <v>5</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="L27" s="3" t="str">
-        <f t="shared" si="1"/>
+      <c r="J28" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="L28" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>2025_TCASI_C刊_A Survey: Collaborative Hardware and Software Design in the Era of Large Language Models</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1" spans="1:14">
+      <c r="A29" s="7">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="7">
+        <v>2025</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="I29" s="7">
+        <v>5</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="L29" s="7" t="str">
+        <f t="shared" si="3"/>
         <v>2025_arXiv:2412.19442_v2_A Survey on Large Language Model Acceleration based on KV Cache Management</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="N27" s="3"/>
+      <c r="M29" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1" spans="1:14">
+      <c r="A30" s="3">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="L30" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>2025_JCST_B刊/T1刊_AI Computing Systems for Large Language Models Training</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>130</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N27" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:N27">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N30" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:N30">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="49" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="44" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -6039,13 +6527,13 @@
               <from>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>25</xdr:row>
+                <xdr:row>27</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>537845</xdr:colOff>
-                <xdr:row>25</xdr:row>
+                <xdr:row>27</xdr:row>
                 <xdr:rowOff>182880</xdr:rowOff>
               </to>
             </anchor>
@@ -6062,7 +6550,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:O17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
@@ -6097,7 +6587,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -6133,41 +6623,41 @@
         <v>2010</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>291</v>
+        <v>351</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>292</v>
+        <v>352</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>293</v>
+        <v>353</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>294</v>
+        <v>354</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>295</v>
+        <v>355</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>296</v>
+        <v>356</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J2" s="3">
         <v>874</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>298</v>
+        <v>358</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>299</v>
+        <v>359</v>
       </c>
       <c r="M2" s="3" t="str">
         <f t="shared" ref="M2:M17" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2010_SciPy_Python领域_Theano: A CPU and GPU Math Compiler in Python</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="O2" s="3"/>
     </row>
@@ -6180,40 +6670,42 @@
         <v>2014</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>301</v>
+        <v>361</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>302</v>
+        <v>362</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>304</v>
+        <v>364</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J3" s="3">
         <v>18557</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>305</v>
+        <v>365</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>306</v>
+        <v>366</v>
       </c>
       <c r="M3" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2014_ACM MM_A会_Caffe: Convolutional Architecture for Fast Feature Embedding</v>
       </c>
-      <c r="N3" s="3"/>
+      <c r="N3" s="3" t="s">
+        <v>367</v>
+      </c>
       <c r="O3" s="3"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="36" customHeight="1" spans="1:15">
@@ -6225,39 +6717,39 @@
         <v>2015</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>307</v>
+        <v>368</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>309</v>
+        <v>370</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>310</v>
+        <v>371</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J4" s="3">
         <v>2936</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>311</v>
+        <v>372</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>312</v>
+        <v>373</v>
       </c>
       <c r="M4" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2015_arXiv:1512.01274_v1_MXNet: A Flexible and Efficient Machine Learning Library for Heterogeneous Distributed Systems</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>313</v>
+        <v>374</v>
       </c>
       <c r="O4" s="3"/>
     </row>
@@ -6270,39 +6762,39 @@
         <v>2016</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>317</v>
+        <v>378</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J5" s="3">
         <v>46587</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>318</v>
+        <v>379</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>319</v>
+        <v>380</v>
       </c>
       <c r="M5" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2016_OSDI_A会_TensorFlow: A System for Large-Scale Machine Learning</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>320</v>
+        <v>381</v>
       </c>
       <c r="O5" s="3"/>
     </row>
@@ -6315,39 +6807,39 @@
         <v>2019</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>321</v>
+        <v>159</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>323</v>
+        <v>383</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>324</v>
+        <v>384</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J6" s="3">
         <v>54391</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>325</v>
+        <v>385</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>326</v>
+        <v>386</v>
       </c>
       <c r="M6" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_NeurIPS_A会_PyTorch: An Imperative Style, High-Performance Deep Learning Library</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>327</v>
+        <v>387</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -6360,39 +6852,39 @@
         <v>2019</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>328</v>
+        <v>388</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>329</v>
+        <v>389</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>330</v>
+        <v>390</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>331</v>
+        <v>391</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J7" s="3">
         <v>364</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>332</v>
+        <v>392</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>333</v>
+        <v>393</v>
       </c>
       <c r="M7" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_数据与计算发展前沿_T3刊_PaddlePaddle: An Open-Source Deep Learning Platform from Industrial Practice</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>334</v>
+        <v>394</v>
       </c>
       <c r="O7" s="3"/>
     </row>
@@ -6405,41 +6897,41 @@
         <v>2020</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>335</v>
+        <v>395</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>336</v>
+        <v>396</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>337</v>
+        <v>397</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>338</v>
+        <v>398</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J8" s="3">
         <v>160</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>340</v>
+        <v>400</v>
       </c>
       <c r="M8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_SCIS_A刊_Jittor: a novel deep learning framework with meta-operators and unified graph execution</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>341</v>
+        <v>401</v>
       </c>
       <c r="O8" s="3"/>
     </row>
@@ -6452,41 +6944,41 @@
         <v>2020</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>342</v>
+        <v>402</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>343</v>
+        <v>403</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>345</v>
+        <v>405</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>346</v>
+        <v>406</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="J9" s="3">
         <v>1283</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>348</v>
+        <v>408</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>349</v>
+        <v>409</v>
       </c>
       <c r="M9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_SIGKDD_A会_DeepSpeed: System Optimizations Enable Training Deep Learning Models with Over 100 Billion Parameters</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>350</v>
+        <v>410</v>
       </c>
       <c r="O9" s="3"/>
     </row>
@@ -6499,39 +6991,39 @@
         <v>2020</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>351</v>
+        <v>411</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>353</v>
+        <v>413</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>354</v>
+        <v>414</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="J10" s="3">
         <v>1996</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>355</v>
+        <v>415</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="M10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_arXiv:1909.08053_v4_Megatron-LM: Training Multi-Billion Parameter Language Models Using Model Parallelism</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>357</v>
+        <v>417</v>
       </c>
       <c r="O10" s="3"/>
     </row>
@@ -6544,32 +7036,32 @@
         <v>2020</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>343</v>
+        <v>403</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="J11" s="3">
         <v>1366</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>362</v>
+        <v>422</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>363</v>
+        <v>423</v>
       </c>
       <c r="M11" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6587,39 +7079,39 @@
         <v>2021</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>364</v>
+        <v>424</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>365</v>
+        <v>425</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J12" s="3">
         <v>45</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>369</v>
+        <v>429</v>
       </c>
       <c r="M12" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_arXiv:2110.15032_v6_OneFlow: Redesign the Distributed Deep Learning Framework from Scratch</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="O12" s="3"/>
     </row>
@@ -6632,39 +7124,39 @@
         <v>2021</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>343</v>
+        <v>403</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>372</v>
+        <v>432</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>373</v>
+        <v>433</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="J13" s="3">
         <v>427</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>374</v>
+        <v>434</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>375</v>
+        <v>435</v>
       </c>
       <c r="M13" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_USENIX ATC_A会_ZeRO-Offload: Democratizing Billion-Scale Model Training</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>376</v>
+        <v>436</v>
       </c>
       <c r="O13" s="3"/>
     </row>
@@ -6677,39 +7169,39 @@
         <v>2021</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>343</v>
+        <v>403</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>361</v>
+        <v>421</v>
       </c>
       <c r="J14" s="3">
         <v>360</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>379</v>
+        <v>439</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>380</v>
+        <v>440</v>
       </c>
       <c r="M14" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_SC_A会_ZeRO-infinity: breaking the GPU memory wall for extreme scale deep learning</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>381</v>
+        <v>441</v>
       </c>
       <c r="O14" s="3"/>
     </row>
@@ -6722,39 +7214,39 @@
         <v>2022</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>382</v>
+        <v>442</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>383</v>
+        <v>443</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>384</v>
+        <v>444</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>385</v>
+        <v>445</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>386</v>
+        <v>446</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>297</v>
+        <v>357</v>
       </c>
       <c r="J15" s="3">
         <v>7</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>387</v>
+        <v>447</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>388</v>
+        <v>448</v>
       </c>
       <c r="M15" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_Textbook_白皮书_Huawei MindSpore AI Development Framework</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>389</v>
+        <v>449</v>
       </c>
       <c r="O15" s="3"/>
     </row>
@@ -6767,41 +7259,41 @@
         <v>2023</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>391</v>
+        <v>451</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>392</v>
+        <v>452</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>393</v>
+        <v>453</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>394</v>
+        <v>454</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="J16" s="3">
         <v>146</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>396</v>
+        <v>456</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>397</v>
+        <v>457</v>
       </c>
       <c r="M16" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICPP_B会_Colossal-AI: A Unified Deep Learning System For Large-Scale Parallel Training</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
       <c r="O16" s="3"/>
     </row>
@@ -6814,39 +7306,39 @@
         <v>2023</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>399</v>
+        <v>459</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>401</v>
+        <v>461</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="J17" s="3">
         <v>284</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>403</v>
+        <v>463</v>
       </c>
       <c r="M17" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_arXiv:2304.11277_v2_PyTorch FSDP: Experiences on Scaling Fully Sharded Data Parallel</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>404</v>
+        <v>464</v>
       </c>
       <c r="O17" s="3"/>
     </row>
@@ -6858,14 +7350,17 @@
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="52" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N17"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -6897,7 +7392,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>110</v>
@@ -6921,91 +7416,66 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:14">
+    <row r="2" s="1" customFormat="1" ht="36" customHeight="1" spans="1:14">
       <c r="A2" s="3">
-        <f t="shared" ref="A2:A17" si="0">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="3">
-        <v>2012</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="I2" s="3">
-        <v>141067</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="L2" s="3" t="str">
-        <f t="shared" ref="L2:L17" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
-        <v>2012_NeurIPS_A会_ImageNet Classification with Deep Convolutional Neural Networks</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>411</v>
-      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
       <c r="N2" s="3"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:14">
       <c r="A3" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A3:A18" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>412</v>
+        <v>150</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>413</v>
+        <v>159</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>414</v>
+        <v>465</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>415</v>
+        <v>466</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>416</v>
+        <v>467</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>408</v>
+        <v>468</v>
       </c>
       <c r="I3" s="3">
-        <v>140476</v>
+        <v>141067</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>417</v>
+        <v>469</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>418</v>
+        <v>470</v>
       </c>
       <c r="L3" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2015_ICLR_顶会_Very Deep Convolutional Networks for Large-Scale Image Recognition</v>
+        <f t="shared" ref="L3:L18" si="1">B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
+        <v>2012_NeurIPS_A会_ImageNet Classification with Deep Convolutional Neural Networks</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>419</v>
+        <v>471</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -7015,41 +7485,41 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>137</v>
+        <v>472</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>343</v>
+        <v>474</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>421</v>
+        <v>475</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>422</v>
+        <v>476</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>408</v>
+        <v>468</v>
       </c>
       <c r="I4" s="3">
-        <v>259309</v>
+        <v>140476</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>423</v>
+        <v>477</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>424</v>
+        <v>478</v>
       </c>
       <c r="L4" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2016_CVPR_A会_Deep Residual Learning for Image Recognition</v>
+        <v>2015_ICLR_顶会_Very Deep Convolutional Networks for Large-Scale Image Recognition</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>425</v>
+        <v>479</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -7059,41 +7529,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>420</v>
+        <v>480</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>427</v>
+        <v>481</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>428</v>
+        <v>482</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>408</v>
+        <v>468</v>
       </c>
       <c r="I5" s="3">
-        <v>52228</v>
+        <v>259309</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>429</v>
+        <v>483</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>430</v>
+        <v>484</v>
       </c>
       <c r="L5" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2017_CVPR_A会_Densely Connected Convolutional Networks</v>
+        <v>2016_CVPR_A会_Deep Residual Learning for Image Recognition</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>431</v>
+        <v>485</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -7106,38 +7576,38 @@
         <v>2017</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>321</v>
+        <v>480</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>315</v>
+        <v>486</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>432</v>
+        <v>487</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>433</v>
+        <v>488</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>434</v>
+        <v>468</v>
       </c>
       <c r="I6" s="3">
-        <v>170262</v>
+        <v>52228</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>436</v>
+        <v>490</v>
       </c>
       <c r="L6" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2017_NeurIPS_A会_Attention is All you Need</v>
+        <v>2017_CVPR_A会_Densely Connected Convolutional Networks</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>437</v>
+        <v>491</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -7147,41 +7617,41 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>438</v>
+        <v>159</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>439</v>
+        <v>492</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>434</v>
+        <v>494</v>
       </c>
       <c r="I7" s="3">
-        <v>125703</v>
+        <v>170262</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>441</v>
+        <v>495</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>442</v>
+        <v>496</v>
       </c>
       <c r="L7" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2019_NAACL_B会_BERT: Pre-training of Deep Bidirectional Transformers for Language Understanding</v>
+        <v>2017_NeurIPS_A会_Attention is All you Need</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>443</v>
+        <v>497</v>
       </c>
       <c r="N7" s="3"/>
     </row>
@@ -7191,41 +7661,41 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>413</v>
+        <v>498</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>444</v>
+        <v>499</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>445</v>
+        <v>500</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>434</v>
+        <v>494</v>
       </c>
       <c r="I8" s="3">
-        <v>56822</v>
+        <v>125703</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>446</v>
+        <v>501</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>447</v>
+        <v>502</v>
       </c>
       <c r="L8" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2021_ICLR_顶会_An Image is Worth 16x16 Words: Transformers for Image Recognition at Scale</v>
+        <v>2019_NAACL_B会_BERT: Pre-training of Deep Bidirectional Transformers for Language Understanding</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>448</v>
+        <v>503</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -7235,41 +7705,41 @@
         <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>236</v>
+        <v>472</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>450</v>
+        <v>504</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>451</v>
+        <v>505</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>452</v>
+        <v>494</v>
       </c>
       <c r="I9" s="3">
-        <v>2935</v>
+        <v>56822</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>453</v>
+        <v>506</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>454</v>
+        <v>507</v>
       </c>
       <c r="L9" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_arXiv:2205.01068_v4_OPT: Open Pre-trained Transformer Language Models</v>
+        <v>2021_ICLR_顶会_An Image is Worth 16x16 Words: Transformers for Image Recognition at Scale</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>455</v>
+        <v>508</v>
       </c>
       <c r="N9" s="3"/>
     </row>
@@ -7282,38 +7752,38 @@
         <v>2022</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>456</v>
+        <v>273</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>457</v>
+        <v>509</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>458</v>
+        <v>382</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>459</v>
+        <v>510</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>460</v>
+        <v>511</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="I10" s="3">
-        <v>1064</v>
+        <v>2935</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>461</v>
+        <v>513</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>462</v>
+        <v>514</v>
       </c>
       <c r="L10" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_arXiv:2203.13474_v5_CodeGen: An Open Large Language Model for Code with Multi-Turn Program Synthesis</v>
+        <v>2022_arXiv:2205.01068_v4_OPT: Open Pre-trained Transformer Language Models</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>463</v>
+        <v>515</v>
       </c>
       <c r="N10" s="3"/>
     </row>
@@ -7323,41 +7793,41 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>129</v>
+        <v>516</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>464</v>
+        <v>517</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>458</v>
+        <v>518</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>465</v>
+        <v>519</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>466</v>
+        <v>520</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="I11" s="3">
-        <v>196</v>
+        <v>1064</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>467</v>
+        <v>521</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>468</v>
+        <v>522</v>
       </c>
       <c r="L11" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2023_arXiv:2305.02309_v2_CodeGen2: Lessons for Training LLMs on Programming and Natural Languages</v>
+        <v>2022_arXiv:2203.13474_v5_CodeGen: An Open Large Language Model for Code with Multi-Turn Program Synthesis</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>469</v>
+        <v>523</v>
       </c>
       <c r="N11" s="3"/>
     </row>
@@ -7367,41 +7837,41 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>364</v>
+        <v>141</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>470</v>
+        <v>524</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>471</v>
+        <v>518</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>472</v>
+        <v>525</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>473</v>
+        <v>526</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="I12" s="3">
-        <v>9183</v>
+        <v>196</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>474</v>
+        <v>527</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>475</v>
+        <v>528</v>
       </c>
       <c r="L12" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_arXiv:2303.08774_v6_GPT-4 Technical Report</v>
+        <v>2023_arXiv:2305.02309_v2_CodeGen2: Lessons for Training LLMs on Programming and Natural Languages</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>476</v>
+        <v>529</v>
       </c>
       <c r="N12" s="3"/>
     </row>
@@ -7414,38 +7884,38 @@
         <v>2024</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>477</v>
+        <v>424</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>478</v>
+        <v>530</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>322</v>
+        <v>115</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>479</v>
+        <v>531</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>480</v>
+        <v>532</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="I13" s="3">
-        <v>3298</v>
+        <v>9183</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>481</v>
+        <v>533</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>482</v>
+        <v>534</v>
       </c>
       <c r="L13" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_arXiv:2407.21783_v3_The Llama 3 Herd of Models</v>
+        <v>2024_arXiv:2303.08774_v6_GPT-4 Technical Report</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>483</v>
+        <v>535</v>
       </c>
       <c r="N13" s="3"/>
     </row>
@@ -7458,38 +7928,38 @@
         <v>2024</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>477</v>
+        <v>536</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>484</v>
+        <v>537</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>315</v>
+        <v>382</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>485</v>
+        <v>538</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>486</v>
+        <v>539</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="I14" s="3">
-        <v>522</v>
+        <v>3298</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>487</v>
+        <v>540</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>488</v>
+        <v>541</v>
       </c>
       <c r="L14" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_arXiv:2408.00118_v3_Gemma 2: Improving Open Language Models at a Practical Size</v>
+        <v>2024_arXiv:2407.21783_v3_The Llama 3 Herd of Models</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -7502,38 +7972,38 @@
         <v>2024</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>137</v>
+        <v>536</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>490</v>
+        <v>543</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>322</v>
+        <v>376</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>491</v>
+        <v>544</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>492</v>
+        <v>545</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="I15" s="3">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>493</v>
+        <v>546</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>494</v>
+        <v>547</v>
       </c>
       <c r="L15" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_ICML_A会_MobileLLM: Optimizing Sub-billion Parameter Language Models for On-Device Use Cases</v>
+        <v>2024_arXiv:2408.00118_v3_Gemma 2: Improving Open Language Models at a Practical Size</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>495</v>
+        <v>548</v>
       </c>
       <c r="N15" s="3"/>
     </row>
@@ -7546,38 +8016,38 @@
         <v>2024</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>496</v>
+        <v>549</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>497</v>
+        <v>382</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>498</v>
+        <v>550</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>499</v>
+        <v>551</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="I16" s="3">
-        <v>326</v>
+        <v>84</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>500</v>
+        <v>552</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>501</v>
+        <v>553</v>
       </c>
       <c r="L16" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_arXiv:2401.02385_v2_TinyLlama: An Open-Source Small Language Model</v>
+        <v>2024_ICML_A会_MobileLLM: Optimizing Sub-billion Parameter Language Models for On-Device Use Cases</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>502</v>
+        <v>554</v>
       </c>
       <c r="N16" s="3"/>
     </row>
@@ -7587,52 +8057,97 @@
         <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>503</v>
+        <v>555</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>504</v>
+        <v>556</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>505</v>
+        <v>557</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>506</v>
+        <v>558</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="I17" s="3">
-        <v>201</v>
+        <v>326</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>507</v>
+        <v>559</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>508</v>
+        <v>560</v>
       </c>
       <c r="L17" s="3" t="str">
         <f t="shared" si="1"/>
+        <v>2024_arXiv:2401.02385_v2_TinyLlama: An Open-Source Small Language Model</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:14">
+      <c r="A18" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="I18" s="3">
+        <v>201</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="L18" s="3" t="str">
+        <f t="shared" si="1"/>
         <v>2025_arXiv:2412.19437_v2_DeepSeek-V3 Technical Report</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="N17" s="3"/>
+      <c r="M18" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="N18" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N17" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:N17">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N18" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:N18">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="57" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -7645,13 +8160,13 @@
               <from>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>6</xdr:row>
+                <xdr:row>7</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>537845</xdr:colOff>
-                <xdr:row>6</xdr:row>
+                <xdr:row>7</xdr:row>
                 <xdr:rowOff>182880</xdr:rowOff>
               </to>
             </anchor>
@@ -7668,8 +8183,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P22"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -7705,7 +8222,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -7726,7 +8243,7 @@
         <v>11</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>112</v>
@@ -7737,48 +8254,48 @@
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:16">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A22" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A24" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="4">
         <v>2016</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>511</v>
+        <v>570</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>352</v>
+        <v>412</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>512</v>
+        <v>571</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>513</v>
+        <v>572</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J2" s="4">
         <v>540</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>515</v>
+        <v>574</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>516</v>
+        <v>575</v>
       </c>
       <c r="M2" s="4" t="str">
-        <f t="shared" ref="M2:M22" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+        <f t="shared" ref="M2:M24" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2016_MICRO_A会_vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design</v>
       </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4" t="s">
-        <v>517</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:16">
@@ -7790,32 +8307,32 @@
         <v>2018</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>518</v>
+        <v>577</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>519</v>
+        <v>578</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>520</v>
+        <v>579</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>521</v>
+        <v>580</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>522</v>
+        <v>581</v>
       </c>
       <c r="J3" s="4">
         <v>42</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>523</v>
+        <v>582</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>524</v>
+        <v>583</v>
       </c>
       <c r="M3" s="4" t="str">
         <f t="shared" si="1"/>
@@ -7824,7 +8341,7 @@
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4" t="s">
-        <v>525</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:16">
@@ -7836,34 +8353,34 @@
         <v>2018</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>526</v>
+        <v>585</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>527</v>
+        <v>586</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>528</v>
+        <v>587</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J4" s="3">
         <v>19</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>529</v>
+        <v>588</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>530</v>
+        <v>589</v>
       </c>
       <c r="M4" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7882,44 +8399,44 @@
         <v>2018</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>532</v>
+        <v>591</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>533</v>
+        <v>592</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>534</v>
+        <v>593</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J5" s="3">
         <v>53</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>535</v>
+        <v>594</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>536</v>
+        <v>595</v>
       </c>
       <c r="M5" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2018_TACO_A刊_Layer-Centric Memory Reuse and Data Migration for Extreme-Scale Deep Learning on Many-Core Architectures</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>538</v>
+        <v>597</v>
       </c>
       <c r="P5" s="3"/>
     </row>
@@ -7932,34 +8449,34 @@
         <v>2019</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>539</v>
+        <v>598</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>540</v>
+        <v>599</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>541</v>
+        <v>600</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>542</v>
+        <v>601</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>543</v>
+        <v>602</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J6" s="3">
         <v>15</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>544</v>
+        <v>603</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>545</v>
+        <v>604</v>
       </c>
       <c r="M6" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7978,44 +8495,44 @@
         <v>2019</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>546</v>
+        <v>605</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>548</v>
+        <v>607</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>549</v>
+        <v>608</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>550</v>
+        <v>609</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>551</v>
+        <v>610</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J7" s="3">
         <v>22</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>552</v>
+        <v>611</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>553</v>
+        <v>612</v>
       </c>
       <c r="M7" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_ISMM_内存领域_Automatic GPU memory management for large neural models in TensorFlow</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>554</v>
+        <v>613</v>
       </c>
       <c r="P7" s="3"/>
     </row>
@@ -8028,44 +8545,44 @@
         <v>2019</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>555</v>
+        <v>614</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>556</v>
+        <v>615</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>557</v>
+        <v>616</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>558</v>
+        <v>617</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>559</v>
+        <v>618</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>560</v>
+        <v>619</v>
       </c>
       <c r="J8" s="3">
         <v>58</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>561</v>
+        <v>620</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>562</v>
+        <v>621</v>
       </c>
       <c r="M8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_IPDPS_B会_Dynamic Memory Management for GPU-Based Training of Deep Neural Networks</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>563</v>
+        <v>622</v>
       </c>
       <c r="P8" s="3"/>
     </row>
@@ -8078,32 +8595,32 @@
         <v>2019</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>564</v>
+        <v>623</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>565</v>
+        <v>624</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>566</v>
+        <v>625</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>567</v>
+        <v>626</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>560</v>
+        <v>619</v>
       </c>
       <c r="J9" s="3">
         <v>57</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>568</v>
+        <v>627</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>569</v>
+        <v>628</v>
       </c>
       <c r="M9" s="3" t="str">
         <f t="shared" si="1"/>
@@ -8111,7 +8628,7 @@
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>570</v>
+        <v>629</v>
       </c>
       <c r="P9" s="3"/>
     </row>
@@ -8121,141 +8638,139 @@
         <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>571</v>
+        <v>630</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>572</v>
+        <v>631</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
-        <v>514</v>
-      </c>
       <c r="J10" s="3">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>575</v>
+        <v>635</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>576</v>
+        <v>636</v>
       </c>
       <c r="M10" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2020_ASPLOS_A会_AutoTM: Automatic Tensor Movement in Heterogeneous Memory Systems using Integer Linear Programming</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>577</v>
-      </c>
+        <v>2019_TC_A刊_Hotness- and Lifetime-Aware Data Placement and Migration for High-Performance Deep Learning on Heterogeneous Memory Systems</v>
+      </c>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:16">
-      <c r="A11" s="4">
+      <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11" s="3">
         <v>2020</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="J11" s="4">
+      <c r="C11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="J11" s="3">
+        <v>86</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="M11" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2020_ASPLOS_A会_AutoTM: Automatic Tensor Movement in Heterogeneous Memory Systems using Integer Linear Programming</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:16">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2020</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="J12" s="4">
         <v>214</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="M11" s="4" t="str">
+      <c r="K12" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="M12" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2020_ASPLOS_A会_SwapAdvisor: Pushing Deep Learning Beyond the GPU Memory Limit via Smart Swapping</v>
       </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:16">
-      <c r="A12" s="3">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="3">
-        <v>2020</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="J12" s="3">
-        <v>15</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="M12" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2020_HPDC_B会_Efficient GPU Memory Management for Nonlinear DNNs</v>
-      </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="P12" s="3"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:16">
       <c r="A13" s="3">
@@ -8263,45 +8778,45 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>137</v>
+        <v>450</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>591</v>
+        <v>649</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>231</v>
+        <v>650</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>592</v>
+        <v>651</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="H13" s="3"/>
+        <v>652</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>653</v>
+      </c>
       <c r="I13" s="3" t="s">
-        <v>514</v>
+        <v>619</v>
       </c>
       <c r="J13" s="3">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>594</v>
+        <v>654</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>595</v>
+        <v>655</v>
       </c>
       <c r="M13" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2021_FAST_A会_FlashNeuron: SSD-Enabled Large-Batch Training of Very Deep Neural Networks</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>537</v>
-      </c>
+        <v>2020_HPDC_B会_Efficient GPU Memory Management for Nonlinear DNNs</v>
+      </c>
+      <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>596</v>
+        <v>656</v>
       </c>
       <c r="P13" s="3"/>
     </row>
@@ -8311,44 +8826,44 @@
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>450</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>597</v>
+        <v>657</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>572</v>
+        <v>658</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>599</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J14" s="3">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>601</v>
+        <v>661</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>602</v>
+        <v>662</v>
       </c>
       <c r="M14" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2021_HPCA_A会_Sentinel: Efficient Tensor Migration and Allocation on Heterogeneous Memory Systems for Deep Learning</v>
+        <v>2020_Euro-Par_B会_Optimal GPU-CPU Offloading Strategies for Deep Neural Network Training</v>
       </c>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="O14" s="3" t="s">
+        <v>663</v>
+      </c>
       <c r="P14" s="3"/>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:16">
@@ -8357,47 +8872,45 @@
         <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>178</v>
+        <v>664</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>69</v>
+        <v>266</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>603</v>
+        <v>665</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>605</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J15" s="3">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>606</v>
+        <v>667</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>607</v>
+        <v>668</v>
       </c>
       <c r="M15" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_TPDS_A刊_Accelerating Tensor Swapping in GPUs With Self-Tuning Compression</v>
+        <v>2021_FAST_A会_FlashNeuron: SSD-Enabled Large-Batch Training of Very Deep Neural Networks</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>608</v>
+        <v>669</v>
       </c>
       <c r="P15" s="3"/>
     </row>
@@ -8407,46 +8920,44 @@
         <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>531</v>
+        <v>670</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>192</v>
+        <v>638</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>609</v>
+        <v>671</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>610</v>
+        <v>672</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>611</v>
+        <v>673</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J16" s="3">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>612</v>
+        <v>674</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>613</v>
+        <v>675</v>
       </c>
       <c r="M16" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_TACO_A刊_An Application-oblivious Memory Scheduling System for DNN Accelerators</v>
+        <v>2021_HPCA_A会_Sentinel: Efficient Tensor Migration and Allocation on Heterogeneous Memory Systems for Deep Learning</v>
       </c>
       <c r="N16" s="3"/>
-      <c r="O16" s="3" t="s">
-        <v>614</v>
-      </c>
+      <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:16">
@@ -8458,41 +8969,45 @@
         <v>2022</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>358</v>
+        <v>205</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>615</v>
+        <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>616</v>
+        <v>676</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>617</v>
+        <v>677</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>618</v>
+        <v>678</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>514</v>
+        <v>573</v>
       </c>
       <c r="J17" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>619</v>
+        <v>679</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>620</v>
+        <v>680</v>
       </c>
       <c r="M17" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_SC_A会_STRONGHOLD: Fast and Affordable Billion-Scale Deep Learning Model Training</v>
-      </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
+        <v>2022_TPDS_A刊_Accelerating Tensor Swapping in GPUs With Self-Tuning Compression</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>681</v>
+      </c>
       <c r="P17" s="3"/>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:16">
@@ -8501,44 +9016,46 @@
         <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>621</v>
+        <v>682</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>622</v>
+        <v>683</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>623</v>
+        <v>684</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>522</v>
+        <v>573</v>
       </c>
       <c r="J18" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>624</v>
+        <v>685</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>625</v>
+        <v>686</v>
       </c>
       <c r="M18" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2023_ASPLOS_A会_DeepUM: Tensor Migration and Prefetching in Unified Memory</v>
+        <v>2022_TACO_A刊_An Application-oblivious Memory Scheduling System for DNN Accelerators</v>
       </c>
       <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="O18" s="3" t="s">
+        <v>687</v>
+      </c>
       <c r="P18" s="3"/>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:16">
@@ -8547,48 +9064,44 @@
         <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>511</v>
+        <v>418</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>626</v>
+        <v>688</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>627</v>
+        <v>689</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>628</v>
+        <v>690</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>629</v>
+        <v>691</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>522</v>
+        <v>573</v>
       </c>
       <c r="J19" s="3">
         <v>18</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>630</v>
+        <v>692</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>631</v>
+        <v>693</v>
       </c>
       <c r="M19" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2023_MICRO_A会_G10: Enabling An Efficient Unified GPU Memory and Storage Architecture with Smart Tensor Migrations</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>632</v>
-      </c>
+        <v>2022_SC_A会_STRONGHOLD: Fast and Affordable Billion-Scale Deep Learning Model Training</v>
+      </c>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:16">
@@ -8597,44 +9110,44 @@
         <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>597</v>
+        <v>637</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>633</v>
+        <v>266</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>634</v>
+        <v>694</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="H20" s="3"/>
+        <v>695</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>696</v>
+      </c>
       <c r="I20" s="3" t="s">
-        <v>514</v>
+        <v>581</v>
       </c>
       <c r="J20" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>636</v>
+        <v>697</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>637</v>
+        <v>698</v>
       </c>
       <c r="M20" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_HPCA_A会_Enabling Large Dynamic Neural Network Training with Learning-based Memory Management</v>
+        <v>2023_ASPLOS_A会_DeepUM: Tensor Migration and Prefetching in Unified Memory</v>
       </c>
       <c r="N20" s="3"/>
-      <c r="O20" s="3" t="s">
-        <v>638</v>
-      </c>
+      <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
     <row r="21" ht="36" customHeight="1" spans="1:16">
@@ -8643,44 +9156,48 @@
         <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>178</v>
+        <v>570</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>639</v>
+        <v>699</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>640</v>
+        <v>700</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>641</v>
+        <v>701</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>642</v>
+        <v>702</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>514</v>
+        <v>581</v>
       </c>
       <c r="J21" s="3">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>643</v>
+        <v>703</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>644</v>
+        <v>704</v>
       </c>
       <c r="M21" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_TPDS_A刊_DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training</v>
-      </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
+        <v>2023_MICRO_A会_G10: Enabling An Efficient Unified GPU Memory and Storage Architecture with Smart Tensor Migrations</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>705</v>
+      </c>
       <c r="P21" s="3"/>
     </row>
     <row r="22" ht="36" customHeight="1" spans="1:16">
@@ -8689,56 +9206,149 @@
         <v>21</v>
       </c>
       <c r="B22" s="3">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>646</v>
+        <v>706</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>647</v>
+        <v>707</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>648</v>
+        <v>708</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>51</v>
+        <v>573</v>
+      </c>
+      <c r="J22" s="3">
+        <v>8</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>649</v>
+        <v>709</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>650</v>
+        <v>710</v>
       </c>
       <c r="M22" s="3" t="str">
         <f t="shared" si="1"/>
+        <v>2024_HPCA_A会_Enabling Large Dynamic Neural Network Training with Learning-based Memory Management</v>
+      </c>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:16">
+      <c r="A23" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="M23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2024_TPDS_A刊_DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" ht="36" customHeight="1" spans="1:16">
+      <c r="A24" s="3">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="M24" s="3" t="str">
+        <f t="shared" si="1"/>
         <v>2025_arXiv:2406.10181_v2_Practical offloading for fine-tuning LLM on commodity GPU via learned sparse projectors</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="P22" s="3"/>
+      <c r="N24" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="P24" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P22" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:P22">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P24" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:P24">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -8774,8 +9384,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:P17"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -8811,7 +9423,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -8832,7 +9444,7 @@
         <v>11</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>112</v>
@@ -8843,343 +9455,339 @@
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:16">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A17" si="0">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="4">
         <v>2016</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>652</v>
+        <v>725</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>308</v>
+        <v>369</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>726</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>727</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>654</v>
+        <v>728</v>
       </c>
       <c r="J2" s="4">
         <v>1122</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>655</v>
+        <v>729</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>656</v>
+        <v>730</v>
       </c>
       <c r="M2" s="4" t="str">
-        <f t="shared" ref="M2:M17" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+        <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2016_arXiv:1604.06174_v2_Training Deep Nets with Sublinear Memory Cost</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>657</v>
+        <v>731</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>517</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:16">
       <c r="A3" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>321</v>
+        <v>159</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="G3" s="3"/>
+        <v>732</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>733</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>654</v>
+        <v>728</v>
       </c>
       <c r="J3" s="3">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>659</v>
+        <v>734</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>660</v>
+        <v>735</v>
       </c>
       <c r="M3" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2019_NeurIPS_A会_Efficient Rematerialization for Deep Networks</v>
+        <f>B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
+        <v>2016_NeurIPS_A会_Memory-Efficient Backpropagation Through Time</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>661</v>
+        <v>736</v>
       </c>
       <c r="P3" s="3"/>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:16">
       <c r="A4" s="3">
-        <f t="shared" si="0"/>
+        <f>ROW()-1</f>
         <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>2019</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>662</v>
+        <v>159</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>663</v>
+        <v>376</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>666</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>654</v>
+        <v>728</v>
       </c>
       <c r="J4" s="3">
+        <v>65</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>738</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="M4" s="3" t="str">
+        <f>B4&amp;"_"&amp;D4&amp;"_"&amp;C4&amp;"_"&amp;F4&amp;""</f>
+        <v>2019_NeurIPS_A会_Efficient Rematerialization for Deep Networks</v>
+      </c>
+      <c r="N4" s="3"/>
+      <c r="O4" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:16">
+      <c r="A5" s="3">
+        <f>ROW()-1</f>
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="J5" s="3">
+        <v>49</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="M5" s="3" t="str">
+        <f>B5&amp;"_"&amp;D5&amp;"_"&amp;C5&amp;"_"&amp;F5&amp;""</f>
+        <v>2019_NeurIPS_A会_A Graph Theoretic Framework of Recomputation Algorithms for Memory-Efficient Backpropagation</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:16">
+      <c r="A6" s="3">
+        <f t="shared" ref="A6:A19" si="0">ROW()-1</f>
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="J6" s="3">
         <v>35</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="M4" s="3" t="str">
-        <f t="shared" si="1"/>
+      <c r="K6" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="M6" s="3" t="str">
+        <f t="shared" ref="M6:M19" si="1">B6&amp;"_"&amp;D6&amp;"_"&amp;C6&amp;"_"&amp;F6&amp;""</f>
         <v>2019_arXiv:1911.13214_v1_Optimal checkpointing for heterogeneous chains: how to train deep neural networks with limited memory</v>
       </c>
-      <c r="N4" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:16">
-      <c r="A5" s="4">
+      <c r="N6" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="P6" s="3"/>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:16">
+      <c r="A7" s="4">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
         <v>2020</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>671</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>672</v>
-      </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="J5" s="4">
+      <c r="C7" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="J7" s="4">
         <v>208</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="M5" s="4" t="str">
+      <c r="K7" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="M7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2020_MLSys_顶会_Checkmate: Breaking the Memory Wall with Optimal Tensor Rematerialization</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:16">
-      <c r="A6" s="3">
+      <c r="N7" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:16">
+      <c r="A8" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
         <v>2020</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="C8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>761</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="J8" s="3">
         <v>40</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="M6" s="3" t="str">
+      <c r="K8" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="M8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_ISCA_A会_Echo: Compiler-based GPU Memory Footprint Reduction for LSTM RNN Training</v>
       </c>
-      <c r="N6" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="P6" s="3"/>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:16">
-      <c r="A7" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="3">
-        <v>2021</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="J7" s="3">
-        <v>29</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="M7" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2021_ICLR_顶会_Memory Optimization for Deep Networks</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:16">
-      <c r="A8" s="4">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="4">
-        <v>2021</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>689</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>690</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="J8" s="4">
-        <v>95</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="M8" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>2021_ICLR_顶会_Dynamic Tensor Rematerialization</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>693</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>517</v>
-      </c>
+      <c r="N8" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="P8" s="3"/>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:16">
       <c r="A9" s="3">
@@ -9190,88 +9798,94 @@
         <v>2021</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>137</v>
+        <v>472</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>694</v>
+        <v>766</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="G9" s="3"/>
+        <v>767</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>768</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>654</v>
+        <v>728</v>
       </c>
       <c r="J9" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>696</v>
+        <v>769</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>697</v>
+        <v>770</v>
       </c>
       <c r="M9" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2021_CVPR_A会_Optimal Gradient Checkpoint Search for Arbitrary Computation Graphs</v>
+        <v>2021_ICLR_顶会_Memory Optimization for Deep Networks</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>698</v>
+        <v>771</v>
       </c>
       <c r="P9" s="3"/>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:16">
-      <c r="A10" s="3">
+      <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" s="3">
-        <v>2022</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="J10" s="3">
-        <v>7</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="M10" s="3" t="str">
+      <c r="B10" s="4">
+        <v>2021</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4" t="s">
+        <v>728</v>
+      </c>
+      <c r="J10" s="4">
+        <v>95</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="M10" s="4" t="str">
         <f t="shared" si="1"/>
-        <v>2022_NeurIPS_A会_Tempo: Accelerating Transformer-Based Model Training through Memory Footprint Reduction</v>
-      </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="P10" s="3"/>
+        <v>2021_ICLR_顶会_Dynamic Tensor Rematerialization</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:16">
       <c r="A11" s="3">
@@ -9279,47 +9893,43 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>390</v>
+        <v>150</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>704</v>
+        <v>480</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>705</v>
+        <v>777</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>708</v>
-      </c>
+        <v>778</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>709</v>
+        <v>728</v>
       </c>
       <c r="J11" s="3">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>710</v>
+        <v>779</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>711</v>
+        <v>780</v>
       </c>
       <c r="M11" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_MobiSys_B会_Melon: breaking the memory wall for resource-efficient on-device machine learning</v>
+        <v>2021_CVPR_A会_Optimal Gradient Checkpoint Search for Arbitrary Computation Graphs</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>712</v>
+        <v>781</v>
       </c>
       <c r="P11" s="3"/>
     </row>
@@ -9332,44 +9942,40 @@
         <v>2022</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>531</v>
+        <v>159</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>713</v>
+        <v>465</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>714</v>
+        <v>782</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>716</v>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>654</v>
+        <v>728</v>
       </c>
       <c r="J12" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>717</v>
+        <v>784</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>718</v>
+        <v>785</v>
       </c>
       <c r="M12" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_TACO_A刊_XEngine: Optimal Tensor Rematerialization for Neural Networks in Heterogeneous Environments</v>
-      </c>
-      <c r="N12" s="5" t="s">
-        <v>537</v>
-      </c>
+        <v>2022_NeurIPS_A会_Tempo: Accelerating Transformer-Based Model Training through Memory Footprint Reduction</v>
+      </c>
+      <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>719</v>
+        <v>786</v>
       </c>
       <c r="P12" s="3"/>
     </row>
@@ -9379,47 +9985,47 @@
         <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>555</v>
+        <v>787</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>720</v>
+        <v>788</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>721</v>
+        <v>789</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>722</v>
+        <v>790</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>723</v>
+        <v>791</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>654</v>
+        <v>792</v>
       </c>
       <c r="J13" s="3">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>724</v>
+        <v>793</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>725</v>
+        <v>794</v>
       </c>
       <c r="M13" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2023_IPDPS_B会_Exploiting Input Tensor Dynamics in Activation Checkpointing for Efficient Training on GPU</v>
+        <v>2022_MobiSys_B会_Melon: breaking the memory wall for resource-efficient on-device machine learning</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>726</v>
+        <v>795</v>
       </c>
       <c r="P13" s="3"/>
     </row>
@@ -9429,45 +10035,47 @@
         <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>490</v>
+        <v>590</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>727</v>
+        <v>796</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3" t="s">
-        <v>654</v>
-      </c>
       <c r="J14" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>730</v>
+        <v>800</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>731</v>
+        <v>801</v>
       </c>
       <c r="M14" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2023_ICML_A会_Moccasin: Efficient Tensor Rematerialization for Neural Networks</v>
+        <v>2022_TACO_A刊_XEngine: Optimal Tensor Rematerialization for Neural Networks in Heterogeneous Environments</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>732</v>
+        <v>802</v>
       </c>
       <c r="P14" s="3"/>
     </row>
@@ -9480,38 +10088,44 @@
         <v>2023</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>412</v>
+        <v>450</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>670</v>
+        <v>614</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>322</v>
+        <v>803</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+        <v>804</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>806</v>
+      </c>
       <c r="I15" s="3" t="s">
-        <v>654</v>
+        <v>728</v>
       </c>
       <c r="J15" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>734</v>
+        <v>807</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>735</v>
+        <v>808</v>
       </c>
       <c r="M15" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2023_MLSys_顶会_Transcending Runtime-Memory Tradeoffs in Checkpointing by being Fusion Aware</v>
-      </c>
-      <c r="N15" s="3"/>
+        <v>2023_IPDPS_B会_Exploiting Input Tensor Dynamics in Activation Checkpointing for Efficient Training on GPU</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>596</v>
+      </c>
       <c r="O15" s="3" t="s">
-        <v>736</v>
+        <v>809</v>
       </c>
       <c r="P15" s="3"/>
     </row>
@@ -9524,42 +10138,42 @@
         <v>2023</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>490</v>
+        <v>549</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>663</v>
+        <v>810</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>737</v>
+        <v>811</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>738</v>
+        <v>812</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>654</v>
+        <v>728</v>
       </c>
       <c r="J16" s="3">
         <v>3</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>739</v>
+        <v>813</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>740</v>
+        <v>814</v>
       </c>
       <c r="M16" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2023_ICML_A会_Rockmate: an Efficient, Fast, Automatic and Generic Tool for Re-materialization in PyTorch</v>
+        <v>2023_ICML_A会_Moccasin: Efficient Tensor Rematerialization for Neural Networks</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>741</v>
+        <v>815</v>
       </c>
       <c r="P16" s="3"/>
     </row>
@@ -9569,56 +10183,149 @@
         <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>190</v>
+        <v>472</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>743</v>
+        <v>382</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>744</v>
+        <v>816</v>
       </c>
       <c r="G17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>745</v>
-      </c>
+      <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>51</v>
+        <v>728</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>746</v>
+        <v>817</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>747</v>
+        <v>818</v>
       </c>
       <c r="M17" s="3" t="str">
         <f t="shared" si="1"/>
+        <v>2023_MLSys_顶会_Transcending Runtime-Memory Tradeoffs in Checkpointing by being Fusion Aware</v>
+      </c>
+      <c r="N17" s="3"/>
+      <c r="O17" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:16">
+      <c r="A18" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="M18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2023_ICML_A会_Rockmate: an Efficient, Fast, Automatic and Generic Tool for Re-materialization in PyTorch</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:16">
+      <c r="A19" s="3">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="M19" s="3" t="str">
+        <f t="shared" si="1"/>
         <v>2025_JPDC_B刊_GPU memory usage optimization for backward propagation in deep network training</v>
       </c>
-      <c r="N17" s="5" t="s">
-        <v>537</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="P17" s="3"/>
+      <c r="N19" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="P19" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P17" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:P17">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P19" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:P19">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -9654,7 +10361,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
@@ -9691,7 +10400,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -9712,7 +10421,7 @@
         <v>11</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>112</v>
@@ -9730,30 +10439,30 @@
         <v>2017</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>321</v>
+        <v>159</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>749</v>
+        <v>832</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>750</v>
+        <v>833</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J2" s="3">
         <v>105</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>752</v>
+        <v>835</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>753</v>
+        <v>836</v>
       </c>
       <c r="M2" s="3" t="str">
         <f t="shared" ref="M2:M18" si="0">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
@@ -9761,7 +10470,7 @@
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3" t="s">
-        <v>754</v>
+        <v>837</v>
       </c>
       <c r="P2" s="3"/>
     </row>
@@ -9774,47 +10483,47 @@
         <v>2018</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>755</v>
+        <v>838</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>756</v>
+        <v>839</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>757</v>
+        <v>840</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>758</v>
+        <v>841</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>759</v>
+        <v>842</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J3" s="4">
         <v>322</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>760</v>
+        <v>843</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>761</v>
+        <v>844</v>
       </c>
       <c r="M3" s="4" t="str">
         <f t="shared" si="0"/>
         <v>2018_PPoPP_A会_Superneurons: dynamic GPU memory management for training deep neural networks</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>762</v>
+        <v>845</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>517</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:16">
@@ -9826,44 +10535,44 @@
         <v>2019</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>763</v>
+        <v>846</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>764</v>
+        <v>847</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>765</v>
+        <v>848</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J4" s="3">
         <v>14</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>766</v>
+        <v>849</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>767</v>
+        <v>850</v>
       </c>
       <c r="M4" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2019_TACO_A刊_Layup: Layer-adaptive and Multi-type Intermediate-oriented Memory Optimization for GPU-based CNNs</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>768</v>
+        <v>851</v>
       </c>
       <c r="P4" s="3"/>
     </row>
@@ -9876,34 +10585,34 @@
         <v>2020</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>571</v>
+        <v>637</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>769</v>
+        <v>852</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>770</v>
+        <v>853</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>771</v>
+        <v>854</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J5" s="4">
         <v>185</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>772</v>
+        <v>855</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>773</v>
+        <v>856</v>
       </c>
       <c r="M5" s="4" t="str">
         <f t="shared" si="0"/>
@@ -9912,7 +10621,7 @@
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4" t="s">
-        <v>517</v>
+        <v>576</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:16">
@@ -9924,30 +10633,30 @@
         <v>2021</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>321</v>
+        <v>159</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>774</v>
+        <v>857</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J6" s="3">
         <v>44</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>775</v>
+        <v>858</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>776</v>
+        <v>859</v>
       </c>
       <c r="M6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -9955,7 +10664,7 @@
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>777</v>
+        <v>860</v>
       </c>
       <c r="P6" s="3"/>
     </row>
@@ -9968,34 +10677,34 @@
         <v>2022</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>778</v>
+        <v>630</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>779</v>
+        <v>861</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>780</v>
+        <v>862</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>781</v>
+        <v>863</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J7" s="3">
         <v>7</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>782</v>
+        <v>864</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>783</v>
+        <v>865</v>
       </c>
       <c r="M7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -10014,34 +10723,34 @@
         <v>2022</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>390</v>
+        <v>450</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>784</v>
+        <v>866</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>785</v>
+        <v>867</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>786</v>
+        <v>868</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>787</v>
+        <v>869</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>788</v>
+        <v>870</v>
       </c>
       <c r="J8" s="3">
         <v>13</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>789</v>
+        <v>871</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>790</v>
+        <v>872</v>
       </c>
       <c r="M8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -10049,7 +10758,7 @@
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>791</v>
+        <v>873</v>
       </c>
       <c r="P8" s="3"/>
     </row>
@@ -10062,44 +10771,44 @@
         <v>2022</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>792</v>
+        <v>874</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>793</v>
+        <v>875</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>794</v>
+        <v>876</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>795</v>
+        <v>877</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>796</v>
+        <v>878</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J9" s="3">
         <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>797</v>
+        <v>879</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>798</v>
+        <v>880</v>
       </c>
       <c r="M9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_TKDE_A刊_TENSILE: A Tensor Granularity Dynamic GPU Memory Scheduling Method Toward Multiple Dynamic Workloads System</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>799</v>
+        <v>881</v>
       </c>
       <c r="P9" s="3"/>
     </row>
@@ -10112,44 +10821,44 @@
         <v>2022</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>800</v>
+        <v>882</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>705</v>
+        <v>788</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>801</v>
+        <v>883</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>802</v>
+        <v>884</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>803</v>
+        <v>885</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J10" s="3">
         <v>22</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>804</v>
+        <v>886</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>805</v>
+        <v>887</v>
       </c>
       <c r="M10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_ICDE_A会_TSPLIT: Fine-grained GPU Memory Management for Efficient DNN Training via Tensor Splitting</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>806</v>
+        <v>888</v>
       </c>
       <c r="P10" s="3"/>
     </row>
@@ -10162,42 +10871,42 @@
         <v>2022</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>490</v>
+        <v>549</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>807</v>
+        <v>889</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>808</v>
+        <v>890</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J11" s="3">
         <v>52</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>809</v>
+        <v>891</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>810</v>
+        <v>892</v>
       </c>
       <c r="M11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_ICML_A会_POET: Training Neural Networks on Tiny Devices with Integrated Rematerialization and Paging</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>811</v>
+        <v>893</v>
       </c>
       <c r="P11" s="3"/>
     </row>
@@ -10210,44 +10919,44 @@
         <v>2023</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>812</v>
+        <v>894</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>813</v>
+        <v>895</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>814</v>
+        <v>896</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J12" s="3">
         <v>5</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>815</v>
+        <v>897</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>816</v>
+        <v>898</v>
       </c>
       <c r="M12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2023_TPDS_A刊_STR: Hybrid Tensor Re-Generation to Break Memory Wall for DNN Training</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>817</v>
+        <v>899</v>
       </c>
       <c r="P12" s="3"/>
     </row>
@@ -10260,32 +10969,32 @@
         <v>2023</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>412</v>
+        <v>472</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>670</v>
+        <v>753</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>818</v>
+        <v>900</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>819</v>
+        <v>901</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>820</v>
+        <v>902</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>51</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>821</v>
+        <v>903</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>822</v>
+        <v>904</v>
       </c>
       <c r="M13" s="3" t="str">
         <f t="shared" si="0"/>
@@ -10293,7 +11002,7 @@
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>823</v>
+        <v>905</v>
       </c>
       <c r="P13" s="3"/>
     </row>
@@ -10306,44 +11015,44 @@
         <v>2024</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>824</v>
+        <v>906</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>825</v>
+        <v>907</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>826</v>
+        <v>908</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>51</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>827</v>
+        <v>909</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>828</v>
+        <v>910</v>
       </c>
       <c r="M14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2024_TACO_A刊_DELTA: Memory-Efficient Training via Dynamic Fine-Grained Recomputation and Swapping</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>829</v>
+        <v>911</v>
       </c>
       <c r="P14" s="3"/>
     </row>
@@ -10356,34 +11065,34 @@
         <v>2024</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>830</v>
+        <v>912</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>831</v>
+        <v>913</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>832</v>
+        <v>914</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>833</v>
+        <v>915</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>51</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>834</v>
+        <v>916</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>835</v>
+        <v>917</v>
       </c>
       <c r="M15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -10391,7 +11100,7 @@
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>836</v>
+        <v>918</v>
       </c>
       <c r="P15" s="3"/>
     </row>
@@ -10404,42 +11113,42 @@
         <v>2024</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>571</v>
+        <v>637</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>705</v>
+        <v>788</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>837</v>
+        <v>919</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>838</v>
+        <v>920</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J16" s="3">
         <v>4</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>839</v>
+        <v>921</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>840</v>
+        <v>922</v>
       </c>
       <c r="M16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2024_ASPLOS_A会_MAGIS: Memory Optimization via Coordinated Graph Transformation and Scheduling for DNN</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>841</v>
+        <v>923</v>
       </c>
       <c r="P16" s="3"/>
     </row>
@@ -10452,34 +11161,34 @@
         <v>2025</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>842</v>
+        <v>924</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>705</v>
+        <v>788</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>843</v>
+        <v>925</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>844</v>
+        <v>926</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>845</v>
+        <v>927</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>788</v>
+        <v>870</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>51</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>846</v>
+        <v>928</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>847</v>
+        <v>929</v>
       </c>
       <c r="M17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -10487,7 +11196,7 @@
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>848</v>
+        <v>930</v>
       </c>
       <c r="P17" s="3"/>
     </row>
@@ -10500,45 +11209,45 @@
         <v>2025</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>800</v>
+        <v>882</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>849</v>
+        <v>931</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>850</v>
+        <v>932</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>751</v>
+        <v>834</v>
       </c>
       <c r="J18" s="3">
         <v>1</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>851</v>
+        <v>933</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>852</v>
+        <v>934</v>
       </c>
       <c r="M18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2025_ICDE_A会_LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>853</v>
+        <v>935</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>854</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -10549,6 +11258,7 @@
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -10584,7 +11294,9 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:P7"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
@@ -10621,7 +11333,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>290</v>
+        <v>350</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -10642,7 +11354,7 @@
         <v>11</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>510</v>
+        <v>569</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>112</v>
@@ -10660,30 +11372,30 @@
         <v>2018</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>855</v>
+        <v>937</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>548</v>
+        <v>607</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>856</v>
+        <v>938</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>857</v>
+        <v>939</v>
       </c>
       <c r="J2" s="4">
         <v>24</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>858</v>
+        <v>940</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>859</v>
+        <v>941</v>
       </c>
       <c r="M2" s="4" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
@@ -10691,10 +11403,10 @@
       </c>
       <c r="N2" s="4"/>
       <c r="O2" s="4" t="s">
-        <v>860</v>
+        <v>942</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>517</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:16">
@@ -10706,42 +11418,42 @@
         <v>2023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>321</v>
+        <v>159</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>366</v>
+        <v>426</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>861</v>
+        <v>943</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>862</v>
+        <v>944</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>857</v>
+        <v>939</v>
       </c>
       <c r="J3" s="3">
         <v>5</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>863</v>
+        <v>945</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>864</v>
+        <v>946</v>
       </c>
       <c r="M3" s="3" t="str">
         <f t="shared" ref="M2:M7" si="1">B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
         <v>2023_NeurIPS_A会_Coop: Memory is not a Commodity</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>865</v>
+        <v>947</v>
       </c>
       <c r="P3" s="3"/>
     </row>
@@ -10754,42 +11466,42 @@
         <v>2023</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>490</v>
+        <v>549</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>322</v>
+        <v>382</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>866</v>
+        <v>948</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>867</v>
+        <v>949</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>857</v>
+        <v>939</v>
       </c>
       <c r="J4" s="3">
         <v>12</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>868</v>
+        <v>950</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>869</v>
+        <v>951</v>
       </c>
       <c r="M4" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_MODeL: Memory Optimizations for Deep Learning</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>870</v>
+        <v>952</v>
       </c>
       <c r="P4" s="3"/>
     </row>
@@ -10802,34 +11514,34 @@
         <v>2023</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>871</v>
+        <v>953</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>872</v>
+        <v>954</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>873</v>
+        <v>955</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>874</v>
+        <v>956</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>875</v>
+        <v>957</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>857</v>
+        <v>939</v>
       </c>
       <c r="J5" s="3">
         <v>2</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>876</v>
+        <v>958</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>877</v>
+        <v>959</v>
       </c>
       <c r="M5" s="3" t="str">
         <f t="shared" si="1"/>
@@ -10837,7 +11549,7 @@
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>878</v>
+        <v>960</v>
       </c>
       <c r="P5" s="3"/>
     </row>
@@ -10850,47 +11562,47 @@
         <v>2024</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>571</v>
+        <v>637</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>879</v>
+        <v>961</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>880</v>
+        <v>962</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>881</v>
+        <v>963</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>882</v>
+        <v>964</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>857</v>
+        <v>939</v>
       </c>
       <c r="J6" s="4">
         <v>12</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>883</v>
+        <v>965</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>884</v>
+        <v>966</v>
       </c>
       <c r="M6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2024_ASPLOS_A会_GMLake: Efficient and Transparent GPU Memory Defragmentation for Large-scale DNN Training with Virtual Memory Stitching</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>885</v>
+        <v>967</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>517</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:16">
@@ -10902,32 +11614,32 @@
         <v>2024</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>546</v>
+        <v>605</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>547</v>
+        <v>606</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>886</v>
+        <v>968</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>887</v>
+        <v>969</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>888</v>
+        <v>970</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>857</v>
+        <v>939</v>
       </c>
       <c r="J7" s="3">
         <v>1</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>889</v>
+        <v>971</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>890</v>
+        <v>972</v>
       </c>
       <c r="M7" s="3" t="str">
         <f t="shared" si="1"/>
@@ -10945,15 +11657,18 @@
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.7777777777778" style="1" customWidth="1"/>
@@ -10967,16 +11682,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>891</v>
+        <v>973</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>892</v>
+        <v>974</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>893</v>
+        <v>975</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -11003,26 +11718,26 @@
         <v>2019</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>894</v>
+        <v>976</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>895</v>
+        <v>977</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>896</v>
+        <v>978</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>897</v>
+        <v>979</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>898</v>
+        <v>980</v>
       </c>
       <c r="H2" s="3" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;E2&amp;""</f>
         <v>2019_A Taxonomy of Cache Replacement Policies_缓存替换策略的分类</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>899</v>
+        <v>981</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -11035,28 +11750,58 @@
         <v>2023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>900</v>
+        <v>982</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>901</v>
+        <v>983</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>902</v>
+        <v>984</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>903</v>
+        <v>985</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>904</v>
+        <v>986</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>B3&amp;"_"&amp;D3&amp;"_"&amp;E3&amp;""</f>
         <v>2023_Operating Systems: Three Easy Pieces_操作系统导论</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>905</v>
+        <v>987</v>
       </c>
       <c r="J3" s="3"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:10">
+      <c r="A4" s="3">
+        <f>ROW()-1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="H4" s="3" t="str">
+        <f>B4&amp;"_"&amp;D4&amp;""</f>
+        <v>2024_大语言模型</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="J4" s="3"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J3" etc:filterBottomFollowUsedRange="0">
@@ -11066,6 +11811,7 @@
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="74" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/InfoSummary.xlsx
+++ b/InfoSummary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" firstSheet="2" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="14088" firstSheet="2" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="学位" sheetId="10" r:id="rId1"/>
@@ -23,11 +23,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">综述!$A$1:$N$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">框架!$A$1:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">模型!$A$1:$N$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Swap!$A$1:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Recomp!$A$1:$P$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hybrid!$A$1:$P$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">MAS!$A$1:$P$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">电子书!$A$1:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Swap!$A$1:$T$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Recomp!$A$1:$U$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hybrid!$A$1:$T$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">MAS!$A$1:$T$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">电子书!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1468" uniqueCount="992">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="1064">
   <si>
     <t>序号</t>
   </si>
@@ -1798,6 +1798,18 @@
     <t>论文地址：https://arxiv.org/abs/2412.19437</t>
   </si>
   <si>
+    <t>Granularity</t>
+  </si>
+  <si>
+    <t>Strategy</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>Baseline (s)</t>
+  </si>
+  <si>
     <t>开源</t>
   </si>
   <si>
@@ -2274,6 +2286,9 @@
 代码仓库：https://github.com/gulang2019/LSP-Offload/tree/main</t>
   </si>
   <si>
+    <t>Target (s)</t>
+  </si>
+  <si>
     <t>arXiv:1604.06174</t>
   </si>
   <si>
@@ -2283,7 +2298,19 @@
     <t>Sublinear</t>
   </si>
   <si>
-    <t>重计算;</t>
+    <t>重计算;静态;离线;</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>intermediate results (feature maps);</t>
+  </si>
+  <si>
+    <t>gradient graph construction algorithm; greedy allocation; heuristic search;</t>
+  </si>
+  <si>
+    <t>MXNet;</t>
   </si>
   <si>
     <t>[1]Chen T, Xu B, Zhang C, et al. Training deep nets with sublinear memory cost[J]. arXiv preprint arXiv:1604.06174, 2016.</t>
@@ -2293,15 +2320,42 @@
   </si>
   <si>
     <t>论文地址：https://arxiv.org/abs/1604.06174
+论文翻译1：https://blog.csdn.net/yiran103/article/details/79475945
+论文翻译2：https://mp.weixin.qq.com/s/cdUpymti1eRqClPWA4ffXQ
+论文博客1：https://medium.com/tensorflow/fitting-larger-networks-into-memory-583e3c758ff9
+论文博客2：https://zhuanlan.zhihu.com/p/357373040
+论文博客3：https://zhuanlan.zhihu.com/p/62270652
+论文博客4：https://blog.csdn.net/xixiaoyaoww/article/details/105672374
+论文博客5：https://mp.weixin.qq.com/s/6paG8tuGiXyOtMHXkogqzQ
+MXNET 相关优化1：https://www.cnblogs.com/yymn/articles/5559379.html
+MXNET 相关优化2：https://zhuanlan.zhihu.com/p/398134230
 代码仓库1：https://github.com/dmlc/mxnet-memonger
 代码仓库2：https://github.com/cybertronai/gradient-checkpointing
-代码仓库3：https://github.com/Lyken17/pytorch-memonger</t>
+代码仓库3：https://github.com/Lyken17/pytorch-memonger
+OneFlow 中的实现：https://zhuanlan.zhihu.com/p/373662730
+Paddle 中的实现：https://www.paddlepaddle.org.cn/documentation/docs/zh/1.8/api_cn/optimizer_cn/RecomputeOptimizer_cn.html#paddle.fluid.optimizer.RecomputeOptimizer
+MegEngine 中的实现：https://zhuanlan.zhihu.com/p/138730559</t>
+  </si>
+  <si>
+    <t>有影响力的工作。Sublinear 论文里引用了 vDNN，说明 vDNN 论文发的更早。</t>
   </si>
   <si>
     <t>Memory-Efficient Backpropagation Through Time</t>
   </si>
   <si>
     <t>BPTT</t>
+  </si>
+  <si>
+    <t>RNNs; intermediate results (hidden state);</t>
+  </si>
+  <si>
+    <t>dynamic programming;</t>
+  </si>
+  <si>
+    <t>未知</t>
+  </si>
+  <si>
+    <t>Sublinear;</t>
   </si>
   <si>
     <t>[1]Gruslys A, Munos R, Danihelka I, et al. Memory-efficient backpropagation through time[J]. Advances in neural information processing systems, 2016, 29.</t>
@@ -2317,6 +2371,21 @@
     <t>Efficient Rematerialization for Deep Networks</t>
   </si>
   <si>
+    <t>TWRemat</t>
+  </si>
+  <si>
+    <t>重计算;静态;离线;图论;</t>
+  </si>
+  <si>
+    <t>intermediate results;</t>
+  </si>
+  <si>
+    <t>tree decomposition; divide-and-conquer;</t>
+  </si>
+  <si>
+    <t>TensorFlow (GreedyRemat);</t>
+  </si>
+  <si>
     <t>[1]Kumar R, Purohit M, Svitkina Z, et al. Efficient rematerialization for deep networks[J]. Advances in Neural Information Processing Systems, 2019, 32.</t>
   </si>
   <si>
@@ -2330,6 +2399,15 @@
   </si>
   <si>
     <t>A Graph Theoretic Framework of Recomputation Algorithms for Memory-Efficient Backpropagation</t>
+  </si>
+  <si>
+    <t>intermediate activation tensors;</t>
+  </si>
+  <si>
+    <t>Chainer</t>
+  </si>
+  <si>
+    <t>Chainer; Sublinear;</t>
   </si>
   <si>
     <t>[1]Kusumoto M, Inoue T, Watanabe G, et al. A graph theoretic framework of recomputation algorithms for memory-efficient backpropagation[J]. Advances in Neural Information Processing Systems, 2019, 32.</t>
@@ -2352,6 +2430,9 @@
   </si>
   <si>
     <t>Deep Learning, Machine Learning, Scheduling, Checkpointing, Automatic Differentiation</t>
+  </si>
+  <si>
+    <t>重计算;</t>
   </si>
   <si>
     <t>[1]Herrmann J, Beaumont O, Eyraud-Dubois L, et al. Optimal checkpointing for heterogeneous chains: how to train deep neural networks with limited memory[J]. arXiv preprint arXiv:1911.13214, 2019.</t>
@@ -2375,14 +2456,33 @@
     <t>Checkmate</t>
   </si>
   <si>
+    <t>重计算;静态;离线;整数线性规划;</t>
+  </si>
+  <si>
+    <t>activation tensors;</t>
+  </si>
+  <si>
+    <t>mixed integer linear program (MILP); Gurobi;</t>
+  </si>
+  <si>
+    <t>TensorFlow 2.0</t>
+  </si>
+  <si>
+    <t>TensorFlow; Sublinear;</t>
+  </si>
+  <si>
     <t>[1]Jain P, Jain A, Nrusimha A, et al. Checkmate: Breaking the memory wall with optimal tensor rematerialization[J]. Proceedings of Machine Learning and Systems, 2020, 2: 497-511.</t>
   </si>
   <si>
     <t>jain2020checkmate</t>
   </si>
   <si>
-    <t>论文地址：https://proceedings.mlsys.org/paper_files/paper/2020/hash/0b816ae8f06f8dd3543dc3d9ef196cab-Abstract.html
-代码仓库：https://proceedings.mlsys.org/paper_files/paper/2020/hash/0b816ae8f06f8dd3543dc3d9ef196cab-Abstract.html</t>
+    <t>论文地址1：https://proceedings.mlsys.org/paper_files/paper/2020/hash/0b816ae8f06f8dd3543dc3d9ef196cab-Abstract.html
+论文地址2：https://arxiv.org/abs/1910.02653
+代码仓库：https://github.com/parasj/checkmate
+论文博客1：https://zhuanlan.zhihu.com/p/299861314
+论文博客2：https://www.jianshu.com/p/4d3ebdd305f1
+关于MILP：https://www.zhihu.com/question/25560707?sort=created</t>
   </si>
   <si>
     <t>ISCA</t>
@@ -2395,6 +2495,18 @@
   </si>
   <si>
     <t>DNN Training, GPU Memory Footprint Reduction, LSTM RNN</t>
+  </si>
+  <si>
+    <t>LSTM RNNs; feature maps;</t>
+  </si>
+  <si>
+    <t>computation graph partition; dataflow analysis;</t>
+  </si>
+  <si>
+    <t>MXNet 0.12.1</t>
+  </si>
+  <si>
+    <t>MXNet; Sublinear;</t>
   </si>
   <si>
     <t>[1]Zheng B, Vijaykumar N, Pekhimenko G. Echo: Compiler-based GPU memory footprint reduction for LSTM RNN training[C]//2020 ACM/IEEE 47th Annual International Symposium on Computer Architecture (ISCA). IEEE, 2020: 1089-1102.</t>
@@ -2416,6 +2528,18 @@
     <t>MONeT</t>
   </si>
   <si>
+    <t>intermediate activations;</t>
+  </si>
+  <si>
+    <t>0-1 integer program; Gurobi;</t>
+  </si>
+  <si>
+    <t>PyTorch 1.5.1</t>
+  </si>
+  <si>
+    <t>PyTorch; Checkmate;</t>
+  </si>
+  <si>
     <t>[1]Shah A, Wu C Y, Mohan J, et al. Memory Optimization for Deep Networks[C]//International Conference on Learning Representations.</t>
   </si>
   <si>
@@ -2423,7 +2547,8 @@
   </si>
   <si>
     <t>论文地址1：https://openreview.net/forum?id=bnY0jm4l59
-论文地址2：https://arxiv.org/abs/2010.14501
+论文地址2：https://iclr.cc/virtual/2021/spotlight/3420
+论文地址3：https://arxiv.org/abs/2010.14501
 代码仓库：https://github.com/utsaslab/MONeT</t>
   </si>
   <si>
@@ -2433,6 +2558,21 @@
     <t>DTR</t>
   </si>
   <si>
+    <t>重计算;动态;在线;</t>
+  </si>
+  <si>
+    <t>Tensor</t>
+  </si>
+  <si>
+    <t>online; heuristic; greedy algorithm;</t>
+  </si>
+  <si>
+    <t>PyTorch 1.7.0</t>
+  </si>
+  <si>
+    <t>PyTorch; Sublinear; Checkmate;</t>
+  </si>
+  <si>
     <t>[1]Kirisame M, Lyubomirsky S, Haan A, et al. Dynamic Tensor Rematerialization[C]//International Conference on Learning Representations.</t>
   </si>
   <si>
@@ -2440,14 +2580,35 @@
   </si>
   <si>
     <t>论文地址1：https://openreview.net/forum?id=Vfs_2RnOD0H
-论文地址2：https://arxiv.org/abs/2006.09616
-代码仓库：https://github.com/uwsampl/dtr-prototype</t>
+论文地址2：https://iclr.cc/virtual/2021/spotlight/3533
+论文地址3：https://sampl.cs.washington.edu/projects/dtr.html
+论文地址4：https://marisa.moe/dtr.html
+论文地址5：https://arxiv.org/abs/2006.09616
+代码仓库1：https://github.com/uwsampl/dtr-prototype
+代码仓库2：https://github.com/uwsampl/pytorch
+论文博客1：https://shihan-ma.github.io//posts/2021-07-03-DTR_annotation
+论文博客2：https://www.zhihu.com/question/274635237/answer/2249788578</t>
   </si>
   <si>
     <t>卡内基梅隆大学</t>
   </si>
   <si>
     <t>Optimal Gradient Checkpoint Search for Arbitrary Computation Graphs</t>
+  </si>
+  <si>
+    <t>Optimal ACG</t>
+  </si>
+  <si>
+    <t>intermediate tensors;</t>
+  </si>
+  <si>
+    <t>division tree; ACG Solver;</t>
+  </si>
+  <si>
+    <t>Pytorch 1.5</t>
+  </si>
+  <si>
+    <t>Pytorch; Sublinear;</t>
   </si>
   <si>
     <t>[1]Feng J, Huang D. Optimal gradient checkpoint search for arbitrary computation graphs[C]//Proceedings of the IEEE/CVF Conference on Computer Vision and Pattern Recognition. 2021: 11433-11442.</t>
@@ -2467,13 +2628,21 @@
     <t>Tempo</t>
   </si>
   <si>
+    <t>activations; feature maps;</t>
+  </si>
+  <si>
+    <t>Layer-Specific; Transformer-Specific;</t>
+  </si>
+  <si>
     <t>[1]Andoorveedu M, Zhu Z, Zheng B, et al. Tempo: Accelerating transformer-based model training through memory footprint reduction[J]. Advances in Neural Information Processing Systems, 2022, 35: 12267-12282.</t>
   </si>
   <si>
     <t>andoorveedu2022tempo</t>
   </si>
   <si>
-    <t>论文地址：https://proceedings.neurips.cc/paper_files/paper/2022/hash/4fc81f4cd2715d995018e0799262176b-Abstract-Conference.html</t>
+    <t>论文地址：https://proceedings.neurips.cc/paper_files/paper/2022/hash/4fc81f4cd2715d995018e0799262176b-Abstract-Conference.html
+论文博客：https://blog.csdn.net/qq_43207982/article/details/134215344
+代码仓库：https://github.com/UofT-EcoSystem/Tempo</t>
   </si>
   <si>
     <t>MobiSys</t>
@@ -2491,7 +2660,19 @@
     <t>Mobile device, deep learning, memory optimization</t>
   </si>
   <si>
-    <t>重计算;内存分配;</t>
+    <t>重计算;内存分配;静态;离线;</t>
+  </si>
+  <si>
+    <t>activation memory; intermediate outputs;</t>
+  </si>
+  <si>
+    <t>greedy algorithm; heuristics;</t>
+  </si>
+  <si>
+    <t>MNN 1.1.0</t>
+  </si>
+  <si>
+    <t>MNN; vDNN; Sublinear; Capuchin;</t>
   </si>
   <si>
     <t>[1]Wang Q, Xu M, Jin C, et al. Melon: Breaking the memory wall for resource-efficient on-device machine learning[C]//Proceedings of the 20th Annual International Conference on Mobile Systems, Applications and Services. 2022: 450-463.</t>
@@ -2515,13 +2696,26 @@
     <t>Rematerialization, integer linear programming, neural networks, memory management, heterogeneous computing</t>
   </si>
   <si>
+    <t>activations;</t>
+  </si>
+  <si>
+    <t>mixed-integer quadratic program; integer linear programming; Gurobi;</t>
+  </si>
+  <si>
+    <t>oneDNN 2.5</t>
+  </si>
+  <si>
+    <t>oneDNN; Checkmate;</t>
+  </si>
+  <si>
     <t>[1]Schuler M, Membarth R, Slusallek P. Xengine: Optimal tensor rematerialization for neural networks in heterogeneous environments[J]. ACM Transactions on Architecture and Code Optimization, 2022, 20(1): 1-25.</t>
   </si>
   <si>
     <t>schuler2022xengine</t>
   </si>
   <si>
-    <t>论文地址：https://dl.acm.org/doi/full/10.1145/3568956
+    <t>论文地址1：https://dl.acm.org/doi/full/10.1145/3568956
+论文地址2：https://arxiv.org/abs/2212.09290
 代码仓库：https://github.com/dfki-asr/xengine</t>
   </si>
   <si>
@@ -2537,13 +2731,27 @@
     <t>model training, GPU memory, tensor checkpointing, input dynamics</t>
   </si>
   <si>
+    <t>重计算;静态;在线;</t>
+  </si>
+  <si>
+    <t>prediction model;</t>
+  </si>
+  <si>
+    <t>PyTorch 1.11</t>
+  </si>
+  <si>
+    <t>PyTorch; Sublinear; Checkmate; MONeT; DTR;</t>
+  </si>
+  <si>
     <t>[1]Liao J, Li M, Yang H, et al. Exploiting Input Tensor Dynamics in Activation Checkpointing for Efficient Training on GPU[C]//2023 IEEE International Parallel and Distributed Processing Symposium (IPDPS). IEEE, 2023: 156-166.</t>
   </si>
   <si>
     <t>liao2023exploiting</t>
   </si>
   <si>
-    <t>代码仓库1：https://github.com/buaa-hipo/mimose-mmdet
+    <t>论文地址：https://arxiv.org/abs/2209.02478
+论文博客：https://mp.weixin.qq.com/s/6bmQpOlRMwwUm-FqkPyvzA
+代码仓库1：https://github.com/buaa-hipo/mimose-mmdet
 代码仓库2：https://github.com/buaa-hipo/mimose-transformers</t>
   </si>
   <si>
@@ -2554,6 +2762,18 @@
   </si>
   <si>
     <t>Moccasin</t>
+  </si>
+  <si>
+    <t>intermediate output tensors;</t>
+  </si>
+  <si>
+    <t>constraint programming;</t>
+  </si>
+  <si>
+    <t>没在深度学习框架上实现</t>
+  </si>
+  <si>
+    <t>Checkmate;</t>
   </si>
   <si>
     <t>[1]Bartan B, Li H, Teague H, et al. Moccasin: Efficient tensor rematerialization for neural networks[C]//International Conference on Machine Learning. PMLR, 2023: 1826-1837.</t>
@@ -2570,6 +2790,15 @@
     <t>Transcending Runtime-Memory Tradeoffs in Checkpointing by being Fusion Aware</t>
   </si>
   <si>
+    <t>重计算;静态;离线; 图论;</t>
+  </si>
+  <si>
+    <t>minimum s-t cut problem;</t>
+  </si>
+  <si>
+    <t>PyTorch;</t>
+  </si>
+  <si>
     <t>[1]He H, Yu S. Transcending runtime-memory tradeoffs in checkpointing by being fusion aware[J]. Proceedings of Machine Learning and Systems, 2023, 5: 414-427.</t>
   </si>
   <si>
@@ -2583,6 +2812,15 @@
   </si>
   <si>
     <t>Rockmate</t>
+  </si>
+  <si>
+    <t>rotor + Checkmate</t>
+  </si>
+  <si>
+    <t>PyTorch 1.13.0</t>
+  </si>
+  <si>
+    <t>PyTorch; Checkmate; Rotor;</t>
   </si>
   <si>
     <t>[1]Zhao X, Le Hellard T, Eyraud-Dubois L, et al. Rockmate: an efficient, fast, automatic and generic tool for re-materialization in pytorch[C]//International Conference on Machine Learning. PMLR, 2023: 42018-42045.</t>
@@ -2607,6 +2845,12 @@
   </si>
   <si>
     <t>Deep learning, Dynamic programming, Memory usage optimization, Memory pressure, Checkpointing</t>
+  </si>
+  <si>
+    <t>intermediate data;</t>
+  </si>
+  <si>
+    <t>PyTorch; Sublinear; Optimal ACG;</t>
   </si>
   <si>
     <t>[1]Hong D Y, Tsai T H, Wang N, et al. GPU Memory Usage Optimization for Backward Propagation in Deep Network Training[J]. Journal of Parallel and Distributed Computing, 2025: 105053.</t>
@@ -3154,16 +3398,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <strike/>
       <sz val="10"/>
       <color theme="0" tint="-0.15"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -3801,10 +4045,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5389,46 +5633,46 @@
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:14">
-      <c r="A6" s="7">
+      <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="5">
         <v>2022</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="5">
         <v>14</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="L6" s="7" t="str">
+      <c r="L6" s="5" t="str">
         <f t="shared" si="1"/>
         <v>2022_IJCAI_A会_Survey on Efficient Training of Large Neural Networks</v>
       </c>
-      <c r="M6" s="7" t="s">
+      <c r="M6" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -5466,7 +5710,7 @@
         <v>163</v>
       </c>
       <c r="L7" s="3" t="str">
-        <f>B7&amp;"_"&amp;D7&amp;"_"&amp;C7&amp;"_"&amp;F7&amp;""</f>
+        <f t="shared" si="1"/>
         <v>2022_NeurIPS_A会_Training Compute-Optimal Large Language Models</v>
       </c>
       <c r="M7" s="3" t="s">
@@ -5655,90 +5899,90 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:14">
-      <c r="A12" s="7">
+      <c r="A12" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="5">
         <v>2023</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7" t="s">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="5">
         <v>99</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="L12" s="7" t="str">
+      <c r="L12" s="5" t="str">
         <f t="shared" si="3"/>
         <v>2023_arXiv:2302.14017_v1_Full Stack Optimization of Transformer Inference: a Survey</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:14">
-      <c r="A13" s="7">
+      <c r="A13" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="5">
         <v>2023</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I13" s="7">
+      <c r="I13" s="5">
         <v>16</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="L13" s="7" t="str">
+      <c r="L13" s="5" t="str">
         <f t="shared" si="3"/>
         <v>2023_TPDS_A刊_A Survey on Auto-Parallelism of Large-Scale Deep Learning Training</v>
       </c>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7" t="s">
+      <c r="M13" s="5"/>
+      <c r="N13" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -5787,92 +6031,92 @@
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:14">
-      <c r="A15" s="7">
+      <c r="A15" s="5">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="5">
         <v>2023</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="I15" s="7">
+      <c r="I15" s="5">
         <v>353</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="L15" s="7" t="str">
+      <c r="L15" s="5" t="str">
         <f t="shared" si="3"/>
         <v>2023_TNNLS_B刊_A Survey of Visual Transformers</v>
       </c>
-      <c r="M15" s="7" t="s">
+      <c r="M15" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="5" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:14">
-      <c r="A16" s="7">
+      <c r="A16" s="5">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="5">
         <v>2023</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7" t="s">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I16" s="5">
         <v>66</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="L16" s="7" t="str">
+      <c r="L16" s="5" t="str">
         <f t="shared" si="3"/>
         <v>2023_IJCAI_A会_A Survey on Efficient Training of Transformers</v>
       </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="N16" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -6417,46 +6661,46 @@
       </c>
     </row>
     <row r="29" ht="36" customHeight="1" spans="1:14">
-      <c r="A29" s="7">
+      <c r="A29" s="5">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="5">
         <v>2025</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="I29" s="7">
+      <c r="I29" s="5">
         <v>5</v>
       </c>
-      <c r="J29" s="7" t="s">
+      <c r="J29" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="K29" s="7" t="s">
+      <c r="K29" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="L29" s="7" t="str">
+      <c r="L29" s="5" t="str">
         <f t="shared" si="3"/>
         <v>2025_arXiv:2412.19442_v2_A Survey on Large Language Model Acceleration based on KV Cache Management</v>
       </c>
-      <c r="M29" s="7" t="s">
+      <c r="M29" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="N29" s="5" t="s">
         <v>158</v>
       </c>
     </row>
@@ -8186,7 +8430,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -8195,14 +8439,14 @@
     <col min="6" max="6" width="20.7777777777778" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7777777777778" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="10" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="11" max="13" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.77777777777778" style="1" customWidth="1"/>
-    <col min="15" max="16" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88888888888889" style="1"/>
+    <col min="9" max="14" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="15" max="17" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.77777777777778" style="1" customWidth="1"/>
+    <col min="19" max="20" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -8231,28 +8475,40 @@
         <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:16">
+    <row r="2" ht="36" customHeight="1" spans="1:20">
       <c r="A2" s="4">
         <f t="shared" ref="A2:A24" si="0">ROW()-1</f>
         <v>1</v>
@@ -8264,41 +8520,45 @@
         <v>150</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>412</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="J2" s="4">
+        <v>577</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4">
         <v>540</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="M2" s="4" t="str">
-        <f t="shared" ref="M2:M24" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+      <c r="O2" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q2" s="4" t="str">
+        <f t="shared" ref="Q2:Q24" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2016_MICRO_A会_vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:16">
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:20">
       <c r="A3" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -8307,44 +8567,48 @@
         <v>2018</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>275</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="J3" s="4">
+        <v>585</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4">
         <v>42</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="M3" s="4" t="str">
+      <c r="O3" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q3" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2018_HiPC_C会_OC-DNN: Exploiting Advanced Unified Memory Capabilities in CUDA 9 and Volta GPUs for Out-of-Core DNN Training</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:16">
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:20">
       <c r="A4" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -8362,35 +8626,39 @@
         <v>220</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J4" s="3">
+        <v>577</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3">
         <v>19</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="M4" s="3" t="str">
+      <c r="O4" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q4" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2018_TPDS_A刊_moDNN: Memory Optimal Deep Neural Network Training on Graphics Processing Units</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:16">
+      <c r="R4" s="3"/>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:20">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -8402,45 +8670,49 @@
         <v>204</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>124</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J5" s="3">
+        <v>577</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3">
         <v>53</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="M5" s="3" t="str">
+      <c r="O5" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q5" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2018_TACO_A刊_Layer-Centric Memory Reuse and Data Migration for Extreme-Scale Deep Learning on Many-Core Architectures</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="P5" s="3"/>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:16">
+      <c r="R5" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:20">
       <c r="A6" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -8452,41 +8724,45 @@
         <v>450</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J6" s="3">
+        <v>577</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3">
         <v>15</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="M6" s="3" t="str">
+      <c r="O6" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="Q6" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_ICCD_B会_AccUDNN: A GPU Memory Efficient Accelerator for Training Ultra-Deep Neural Networks</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:16">
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:20">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -8495,48 +8771,52 @@
         <v>2019</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J7" s="3">
+        <v>577</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3">
         <v>22</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="M7" s="3" t="str">
+      <c r="O7" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="Q7" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_ISMM_内存领域_Automatic GPU memory management for large neural models in TensorFlow</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:16">
+      <c r="R7" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:20">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -8548,45 +8828,49 @@
         <v>450</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="J8" s="3">
+        <v>623</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3">
         <v>58</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="M8" s="3" t="str">
+      <c r="O8" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_IPDPS_B会_Dynamic Memory Management for GPU-Based Training of Deep Neural Networks</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:16">
+      <c r="R8" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:20">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -8598,41 +8882,45 @@
         <v>113</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="J9" s="3">
+        <v>623</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3">
         <v>57</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="M9" s="3" t="str">
+      <c r="O9" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_arXiv:1903.06631_v1_Efficient Memory Management for GPU-based Deep Learning Systems</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:16">
+      <c r="R9" s="3"/>
+      <c r="S9" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:20">
       <c r="A10" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -8644,41 +8932,45 @@
         <v>204</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J10" s="3">
+        <v>577</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3">
         <v>10</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="M10" s="3" t="str">
+      <c r="O10" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_TC_A刊_Hotness- and Lifetime-Aware Data Placement and Migration for High-Performance Deep Learning on Heterogeneous Memory Systems</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:16">
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:20">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -8690,43 +8982,47 @@
         <v>150</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J11" s="3">
+        <v>577</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3">
         <v>86</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="M11" s="3" t="str">
+      <c r="O11" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="Q11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_ASPLOS_A会_AutoTM: Automatic Tensor Movement in Heterogeneous Memory Systems using Integer Linear Programming</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="P11" s="3"/>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:16">
+      <c r="R11" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:20">
       <c r="A12" s="4">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -8738,41 +9034,45 @@
         <v>150</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="J12" s="4">
+        <v>577</v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4">
         <v>214</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="M12" s="4" t="str">
+      <c r="O12" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="Q12" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2020_ASPLOS_A会_SwapAdvisor: Pushing Deep Learning Beyond the GPU Memory Limit via Smart Swapping</v>
       </c>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:16">
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:20">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -8784,43 +9084,47 @@
         <v>450</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="J13" s="3">
+        <v>623</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3">
         <v>15</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="M13" s="3" t="str">
+      <c r="O13" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="Q13" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_HPDC_B会_Efficient GPU Memory Management for Nonlinear DNNs</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:16">
+      <c r="R13" s="3"/>
+      <c r="S13" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:20">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -8832,41 +9136,45 @@
         <v>450</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J14" s="3">
+        <v>577</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3">
         <v>27</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="M14" s="3" t="str">
+      <c r="O14" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="Q14" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_Euro-Par_B会_Optimal GPU-CPU Offloading Strategies for Deep Neural Network Training</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:16">
+      <c r="R14" s="3"/>
+      <c r="S14" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:20">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -8878,43 +9186,47 @@
         <v>150</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>266</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J15" s="3">
+        <v>577</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3">
         <v>58</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="M15" s="3" t="str">
+      <c r="O15" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="Q15" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_FAST_A会_FlashNeuron: SSD-Enabled Large-Batch Training of Very Deep Neural Networks</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:16">
+      <c r="R15" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:20">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -8926,41 +9238,45 @@
         <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J16" s="3">
+        <v>577</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3">
         <v>75</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="M16" s="3" t="str">
+      <c r="O16" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="Q16" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_HPCA_A会_Sentinel: Efficient Tensor Migration and Allocation on Heterogeneous Memory Systems for Deep Learning</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:16">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:20">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -8978,39 +9294,43 @@
         <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J17" s="3">
+        <v>577</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3">
         <v>4</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="M17" s="3" t="str">
+      <c r="O17" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="Q17" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_TPDS_A刊_Accelerating Tensor Swapping in GPUs With Self-Tuning Compression</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:16">
+      <c r="R17" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:20">
       <c r="A18" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -9022,43 +9342,47 @@
         <v>204</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>220</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J18" s="3">
+        <v>577</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3">
         <v>3</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="M18" s="3" t="str">
+      <c r="O18" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="Q18" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_TACO_A刊_An Application-oblivious Memory Scheduling System for DNN Accelerators</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:16">
+      <c r="R18" s="3"/>
+      <c r="S18" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:20">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -9073,38 +9397,42 @@
         <v>418</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J19" s="3">
+        <v>577</v>
+      </c>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3">
         <v>18</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="M19" s="3" t="str">
+      <c r="O19" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="Q19" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_SC_A会_STRONGHOLD: Fast and Affordable Billion-Scale Deep Learning Model Training</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:16">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:20">
       <c r="A20" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -9116,41 +9444,45 @@
         <v>150</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>266</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="J20" s="3">
+        <v>585</v>
+      </c>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3">
         <v>25</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="M20" s="3" t="str">
+      <c r="O20" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="Q20" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ASPLOS_A会_DeepUM: Tensor Migration and Prefetching in Unified Memory</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:16">
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="1:20">
       <c r="A21" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -9162,45 +9494,49 @@
         <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="J21" s="3">
+        <v>585</v>
+      </c>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3">
         <v>18</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="M21" s="3" t="str">
+      <c r="O21" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="Q21" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_MICRO_A会_G10: Enabling An Efficient Unified GPU Memory and Storage Architecture with Smart Tensor Migrations</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:16">
+      <c r="R21" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" spans="1:20">
       <c r="A22" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -9212,41 +9548,45 @@
         <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J22" s="3">
+        <v>577</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3">
         <v>8</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="M22" s="3" t="str">
+      <c r="O22" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="Q22" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2024_HPCA_A会_Enabling Large Dynamic Neural Network Training with Learning-based Memory Management</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" spans="1:16">
+      <c r="R22" s="3"/>
+      <c r="S22" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:20">
       <c r="A23" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -9261,38 +9601,42 @@
         <v>205</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J23" s="3">
+        <v>577</v>
+      </c>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3">
         <v>1</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="M23" s="3" t="str">
+      <c r="O23" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="Q23" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2024_TPDS_A刊_DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" ht="36" customHeight="1" spans="1:16">
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+    </row>
+    <row r="24" ht="36" customHeight="1" spans="1:20">
       <c r="A24" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -9304,51 +9648,55 @@
         <v>141</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="J24" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="M24" s="3" t="str">
+      <c r="O24" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="Q24" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2025_arXiv:2406.10181_v2_Practical offloading for fine-tuning LLM on commodity GPU via learned sparse projectors</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="P24" s="3"/>
+      <c r="R24" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="T24" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P24" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:P24">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T24" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:T24">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="41" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -9387,7 +9735,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -9396,14 +9744,14 @@
     <col min="6" max="6" width="20.7777777777778" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7777777777778" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="10" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="11" max="13" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.77777777777778" style="1" customWidth="1"/>
-    <col min="15" max="16" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88888888888889" style="1"/>
+    <col min="9" max="15" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="16" max="18" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77777777777778" style="1" customWidth="1"/>
+    <col min="20" max="21" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -9432,28 +9780,43 @@
         <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="S1" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:16">
+    <row r="2" ht="36" customHeight="1" spans="1:21">
       <c r="A2" s="4">
         <f>ROW()-1</f>
         <v>1</v>
@@ -9465,45 +9828,60 @@
         <v>141</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>369</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="J2" s="4">
+        <v>733</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="O2" s="4">
         <v>1122</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>729</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>730</v>
-      </c>
-      <c r="M2" s="4" t="str">
+      <c r="P2" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="R2" s="4" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2016_arXiv:1604.06174_v2_Training Deep Nets with Sublinear Memory Cost</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:16">
+      <c r="S2" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:21">
       <c r="A3" s="3">
         <f>ROW()-1</f>
         <v>2</v>
@@ -9521,35 +9899,50 @@
         <v>376</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>732</v>
+        <v>742</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J3" s="3">
+        <v>733</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="O3" s="3">
         <v>250</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="M3" s="3" t="str">
+      <c r="P3" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="R3" s="3" t="str">
         <f>B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
         <v>2016_NeurIPS_A会_Memory-Efficient Backpropagation Through Time</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="P3" s="3"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:16">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="U3" s="3"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:21">
       <c r="A4" s="3">
         <f>ROW()-1</f>
         <v>3</v>
@@ -9567,33 +9960,50 @@
         <v>376</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="G4" s="3"/>
+        <v>751</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>752</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J4" s="3">
+        <v>753</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="O4" s="3">
         <v>65</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="M4" s="3" t="str">
+      <c r="P4" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="R4" s="3" t="str">
         <f>B4&amp;"_"&amp;D4&amp;"_"&amp;C4&amp;"_"&amp;F4&amp;""</f>
         <v>2019_NeurIPS_A会_Efficient Rematerialization for Deep Networks</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:16">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="U4" s="3"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:21">
       <c r="A5" s="3">
         <f>ROW()-1</f>
         <v>4</v>
@@ -9608,88 +10018,110 @@
         <v>159</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>741</v>
+        <v>760</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>742</v>
+        <v>761</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J5" s="3">
+        <v>753</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="O5" s="3">
         <v>49</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="M5" s="3" t="str">
+      <c r="P5" s="3" t="s">
+        <v>765</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="R5" s="3" t="str">
         <f>B5&amp;"_"&amp;D5&amp;"_"&amp;C5&amp;"_"&amp;F5&amp;""</f>
         <v>2019_NeurIPS_A会_A Graph Theoretic Framework of Recomputation Algorithms for Memory-Efficient Backpropagation</v>
       </c>
-      <c r="N5" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="P5" s="3"/>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:16">
-      <c r="A6" s="3">
+      <c r="S5" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="U5" s="3"/>
+    </row>
+    <row r="6" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A6" s="5">
         <f t="shared" ref="A6:A19" si="0">ROW()-1</f>
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <v>2019</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J6" s="3">
+      <c r="D6" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="5">
         <v>35</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="M6" s="3" t="str">
-        <f t="shared" ref="M6:M19" si="1">B6&amp;"_"&amp;D6&amp;"_"&amp;C6&amp;"_"&amp;F6&amp;""</f>
+      <c r="P6" s="5" t="s">
+        <v>773</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="R6" s="5" t="str">
+        <f t="shared" ref="R6:R19" si="1">B6&amp;"_"&amp;D6&amp;"_"&amp;C6&amp;"_"&amp;F6&amp;""</f>
         <v>2019_arXiv:1911.13214_v1_Optimal checkpointing for heterogeneous chains: how to train deep neural networks with limited memory</v>
       </c>
-      <c r="N6" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="P6" s="3"/>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:16">
+      <c r="S6" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:21">
       <c r="A7" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -9701,45 +10133,60 @@
         <v>472</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>754</v>
+        <v>777</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>755</v>
+        <v>778</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="J7" s="4">
+        <v>779</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="O7" s="4">
         <v>208</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>757</v>
-      </c>
-      <c r="M7" s="4" t="str">
+      <c r="P7" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="R7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2020_MLSys_顶会_Checkmate: Breaking the Memory Wall with Optimal Tensor Rematerialization</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:16">
+      <c r="S7" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:21">
       <c r="A8" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -9751,45 +10198,60 @@
         <v>150</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>759</v>
+        <v>787</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>465</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>760</v>
+        <v>788</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>761</v>
+        <v>789</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>762</v>
+        <v>790</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J8" s="3">
+        <v>733</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="O8" s="3">
         <v>40</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="M8" s="3" t="str">
+      <c r="P8" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="R8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_ISCA_A会_Echo: Compiler-based GPU Memory Footprint Reduction for LSTM RNN Training</v>
       </c>
-      <c r="N8" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:16">
+      <c r="S8" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="U8" s="3"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:21">
       <c r="A9" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -9804,40 +10266,55 @@
         <v>473</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>766</v>
+        <v>798</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>767</v>
+        <v>799</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>768</v>
+        <v>800</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J9" s="3">
+        <v>779</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="O9" s="3">
         <v>29</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="M9" s="3" t="str">
+      <c r="P9" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="R9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_ICLR_顶会_Memory Optimization for Deep Networks</v>
       </c>
-      <c r="N9" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:16">
+      <c r="S9" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="U9" s="3"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:21">
       <c r="A10" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -9855,39 +10332,54 @@
         <v>369</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>772</v>
+        <v>808</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>773</v>
+        <v>809</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
-        <v>728</v>
-      </c>
-      <c r="J10" s="4">
+        <v>810</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="N10" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="O10" s="4">
         <v>95</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>775</v>
-      </c>
-      <c r="M10" s="4" t="str">
+      <c r="P10" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="R10" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2021_ICLR_顶会_Dynamic Tensor Rematerialization</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:16">
+      <c r="S10" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="T10" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:21">
       <c r="A11" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -9902,38 +10394,55 @@
         <v>480</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>777</v>
+        <v>818</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="G11" s="3"/>
+        <v>819</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>820</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J11" s="3">
+        <v>753</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="O11" s="3">
         <v>33</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="M11" s="3" t="str">
+      <c r="P11" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="R11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_CVPR_A会_Optimal Gradient Checkpoint Search for Arbitrary Computation Graphs</v>
       </c>
-      <c r="N11" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="P11" s="3"/>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:16">
+      <c r="S11" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:21">
       <c r="A12" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -9951,35 +10460,52 @@
         <v>465</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>782</v>
+        <v>828</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>783</v>
+        <v>829</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J12" s="3">
+        <v>810</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="O12" s="3">
         <v>7</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="M12" s="3" t="str">
+      <c r="P12" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="R12" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_NeurIPS_A会_Tempo: Accelerating Transformer-Based Model Training through Memory Footprint Reduction</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:16">
+      <c r="S12" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="U12" s="3"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:21">
       <c r="A13" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -9991,45 +10517,60 @@
         <v>450</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>787</v>
+        <v>835</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>789</v>
+        <v>837</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>790</v>
+        <v>838</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>791</v>
+        <v>839</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="J13" s="3">
+        <v>840</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="O13" s="3">
         <v>58</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>793</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>794</v>
-      </c>
-      <c r="M13" s="3" t="str">
+      <c r="P13" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="R13" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_MobiSys_B会_Melon: breaking the memory wall for resource-efficient on-device machine learning</v>
       </c>
-      <c r="N13" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:16">
+      <c r="S13" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T13" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="U13" s="3"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:21">
       <c r="A14" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10041,45 +10582,60 @@
         <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>796</v>
+        <v>848</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>797</v>
+        <v>849</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>798</v>
+        <v>850</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>799</v>
+        <v>851</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J14" s="3">
+        <v>733</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="O14" s="3">
         <v>4</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="M14" s="3" t="str">
+      <c r="P14" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="R14" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_TACO_A刊_XEngine: Optimal Tensor Rematerialization for Neural Networks in Heterogeneous Environments</v>
       </c>
-      <c r="N14" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>802</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:16">
+      <c r="S14" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="U14" s="3"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:21">
       <c r="A15" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10091,45 +10647,60 @@
         <v>450</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>803</v>
+        <v>859</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>805</v>
+        <v>861</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>806</v>
+        <v>862</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J15" s="3">
+        <v>863</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="O15" s="3">
         <v>1</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="M15" s="3" t="str">
+      <c r="P15" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="R15" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_IPDPS_B会_Exploiting Input Tensor Dynamics in Activation Checkpointing for Efficient Training on GPU</v>
       </c>
-      <c r="N15" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:16">
+      <c r="S15" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="U15" s="3"/>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:21">
       <c r="A16" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10144,40 +10715,55 @@
         <v>549</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>810</v>
+        <v>870</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>811</v>
+        <v>871</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>812</v>
+        <v>872</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J16" s="3">
+        <v>733</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="O16" s="3">
         <v>3</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="M16" s="3" t="str">
+      <c r="P16" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="R16" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_Moccasin: Efficient Tensor Rematerialization for Neural Networks</v>
       </c>
-      <c r="N16" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>815</v>
-      </c>
-      <c r="P16" s="3"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:16">
+      <c r="S16" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T16" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:21">
       <c r="A17" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10189,87 +10775,115 @@
         <v>472</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>382</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>816</v>
+        <v>880</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J17" s="3">
+        <v>881</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="O17" s="3">
         <v>4</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="M17" s="3" t="str">
+      <c r="P17" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="R17" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_MLSys_顶会_Transcending Runtime-Memory Tradeoffs in Checkpointing by being Fusion Aware</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3" t="s">
-        <v>819</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:16">
-      <c r="A18" s="3">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="U17" s="3"/>
+    </row>
+    <row r="18" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A18" s="5">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="5">
         <v>2023</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="E18" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5" t="s">
+        <v>889</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="O18" s="5">
         <v>3</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="M18" s="3" t="str">
+      <c r="P18" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="R18" s="5" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_Rockmate: an Efficient, Fast, Automatic and Generic Tool for Re-materialization in PyTorch</v>
       </c>
-      <c r="N18" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:16">
+      <c r="S18" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="U18" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:21">
       <c r="A19" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -10281,51 +10895,66 @@
         <v>218</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>825</v>
+        <v>895</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>826</v>
+        <v>896</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>827</v>
+        <v>897</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>828</v>
+        <v>898</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>830</v>
-      </c>
-      <c r="M19" s="3" t="str">
+      <c r="P19" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="R19" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2025_JPDC_B刊_GPU memory usage optimization for backward propagation in deep network training</v>
       </c>
-      <c r="N19" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="P19" s="3"/>
+      <c r="S19" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="U19" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P19" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:P19">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U19" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:U19">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="39" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -10364,7 +10993,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -10373,14 +11002,14 @@
     <col min="6" max="6" width="20.7777777777778" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7777777777778" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="10" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="11" max="13" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.77777777777778" style="1" customWidth="1"/>
-    <col min="15" max="16" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88888888888889" style="1"/>
+    <col min="9" max="14" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="15" max="17" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.77777777777778" style="1" customWidth="1"/>
+    <col min="19" max="20" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10409,28 +11038,40 @@
         <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:16">
+    <row r="2" ht="36" customHeight="1" spans="1:20">
       <c r="A2" s="3">
         <f>ROW()-1</f>
         <v>1</v>
@@ -10445,36 +11086,40 @@
         <v>159</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>832</v>
+        <v>904</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>833</v>
+        <v>905</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J2" s="3">
+        <v>906</v>
+      </c>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3">
         <v>105</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="M2" s="3" t="str">
-        <f t="shared" ref="M2:M18" si="0">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+      <c r="O2" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="Q2" s="3" t="str">
+        <f t="shared" ref="Q2:Q18" si="0">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2017_NeurIPS_A会_Training Deeper Models by GPU Memory Optimization on TensorFlow</v>
       </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="P2" s="3"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:16">
+      <c r="R2" s="3"/>
+      <c r="S2" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="T2" s="3"/>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:20">
       <c r="A3" s="4">
         <f t="shared" ref="A3:A12" si="1">ROW()-1</f>
         <v>2</v>
@@ -10486,47 +11131,51 @@
         <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>838</v>
+        <v>910</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>839</v>
+        <v>911</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>840</v>
+        <v>912</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>841</v>
+        <v>913</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>842</v>
+        <v>914</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="J3" s="4">
+        <v>906</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4">
         <v>322</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="M3" s="4" t="str">
+      <c r="O3" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="Q3" s="4" t="str">
         <f t="shared" si="0"/>
         <v>2018_PPoPP_A会_Superneurons: dynamic GPU memory management for training deep neural networks</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:16">
+      <c r="R3" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:20">
       <c r="A4" s="3">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -10538,45 +11187,49 @@
         <v>204</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>124</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>846</v>
+        <v>918</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>847</v>
+        <v>919</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>848</v>
+        <v>920</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J4" s="3">
+        <v>906</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3">
         <v>14</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="M4" s="3" t="str">
+      <c r="O4" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="Q4" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2019_TACO_A刊_Layup: Layer-adaptive and Multi-type Intermediate-oriented Memory Optimization for GPU-based CNNs</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:16">
+      <c r="R4" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:20">
       <c r="A5" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
@@ -10588,43 +11241,47 @@
         <v>150</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>852</v>
+        <v>924</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>853</v>
+        <v>925</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>854</v>
+        <v>926</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>834</v>
-      </c>
-      <c r="J5" s="4">
+        <v>906</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4">
         <v>185</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>855</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>856</v>
-      </c>
-      <c r="M5" s="4" t="str">
+      <c r="O5" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="Q5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>2020_ASPLOS_A会_Capuchin: Tensor-based GPU Memory Management for Deep Learning</v>
       </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:16">
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:20">
       <c r="A6" s="3">
         <f t="shared" si="1"/>
         <v>5</v>
@@ -10639,36 +11296,40 @@
         <v>159</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>857</v>
+        <v>929</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J6" s="3">
+        <v>906</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3">
         <v>44</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="M6" s="3" t="str">
+      <c r="O6" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="Q6" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2021_NeurIPS_A会_Efficient Combination of Rematerialization and Offloading for Training DNNs</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3" t="s">
-        <v>860</v>
-      </c>
-      <c r="P6" s="3"/>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:16">
+      <c r="R6" s="3"/>
+      <c r="S6" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:20">
       <c r="A7" s="3">
         <f t="shared" si="1"/>
         <v>6</v>
@@ -10680,41 +11341,45 @@
         <v>204</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>861</v>
+        <v>933</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>862</v>
+        <v>934</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>863</v>
+        <v>935</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J7" s="3">
+        <v>906</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3">
         <v>7</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="M7" s="3" t="str">
+      <c r="O7" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="Q7" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_TC_A刊_HOME: A Holistic GPU Memory Management Framework for Deep Learning</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:16">
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:20">
       <c r="A8" s="3">
         <f t="shared" si="1"/>
         <v>7</v>
@@ -10726,43 +11391,47 @@
         <v>450</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>866</v>
+        <v>938</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>220</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>867</v>
+        <v>939</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>868</v>
+        <v>940</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>869</v>
+        <v>941</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="J8" s="3">
+        <v>942</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3">
         <v>13</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="M8" s="3" t="str">
+      <c r="O8" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="Q8" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_ICS_B会_MegTaiChi: dynamic tensor-based memory management optimization for DNN training</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:16">
+      <c r="R8" s="3"/>
+      <c r="S8" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:20">
       <c r="A9" s="3">
         <f t="shared" si="1"/>
         <v>8</v>
@@ -10774,45 +11443,49 @@
         <v>204</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>874</v>
+        <v>946</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>875</v>
+        <v>947</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>876</v>
+        <v>948</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>877</v>
+        <v>949</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>878</v>
+        <v>950</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J9" s="3">
+        <v>906</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3">
         <v>3</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>879</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>880</v>
-      </c>
-      <c r="M9" s="3" t="str">
+      <c r="O9" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="Q9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_TKDE_A刊_TENSILE: A Tensor Granularity Dynamic GPU Memory Scheduling Method Toward Multiple Dynamic Workloads System</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>881</v>
-      </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:16">
+      <c r="R9" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:20">
       <c r="A10" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
@@ -10824,45 +11497,49 @@
         <v>150</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>882</v>
+        <v>954</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>883</v>
+        <v>955</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>884</v>
+        <v>956</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>885</v>
+        <v>957</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J10" s="3">
+        <v>906</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3">
         <v>22</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="M10" s="3" t="str">
+      <c r="O10" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="Q10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_ICDE_A会_TSPLIT: Fine-grained GPU Memory Management for Efficient DNN Training via Tensor Splitting</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:16">
+      <c r="R10" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:20">
       <c r="A11" s="3">
         <f t="shared" si="1"/>
         <v>10</v>
@@ -10880,37 +11557,41 @@
         <v>198</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>889</v>
+        <v>961</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>890</v>
+        <v>962</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J11" s="3">
+        <v>906</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3">
         <v>52</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>891</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="M11" s="3" t="str">
+      <c r="O11" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="Q11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_ICML_A会_POET: Training Neural Networks on Tiny Devices with Integrated Rematerialization and Paging</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>893</v>
-      </c>
-      <c r="P11" s="3"/>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:16">
+      <c r="R11" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:20">
       <c r="A12" s="3">
         <f t="shared" si="1"/>
         <v>11</v>
@@ -10928,39 +11609,43 @@
         <v>301</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>894</v>
+        <v>966</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>895</v>
+        <v>967</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>896</v>
+        <v>968</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J12" s="3">
+        <v>906</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3">
         <v>5</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>897</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>898</v>
-      </c>
-      <c r="M12" s="3" t="str">
+      <c r="O12" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="Q12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2023_TPDS_A刊_STR: Hybrid Tensor Re-Generation to Break Memory Wall for DNN Training</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>899</v>
-      </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:16">
+      <c r="R12" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:20">
       <c r="A13" s="3">
         <f t="shared" ref="A13:A18" si="2">ROW()-1</f>
         <v>12</v>
@@ -10972,41 +11657,45 @@
         <v>472</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>900</v>
+        <v>972</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>901</v>
+        <v>973</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>902</v>
+        <v>974</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J13" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>904</v>
-      </c>
-      <c r="M13" s="3" t="str">
+      <c r="O13" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="Q13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2023_MLSys_顶会_μ-TWO: 3× Faster Multi-Model Training with Orchestration and Memory Optimization</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:16">
+      <c r="R13" s="3"/>
+      <c r="S13" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:20">
       <c r="A14" s="3">
         <f t="shared" si="2"/>
         <v>13</v>
@@ -11018,45 +11707,49 @@
         <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>168</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="M14" s="3" t="str">
+      <c r="O14" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="Q14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2024_TACO_A刊_DELTA: Memory-Efficient Training via Dynamic Fine-Grained Recomputation and Swapping</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>911</v>
-      </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:16">
+      <c r="R14" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:20">
       <c r="A15" s="3">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -11068,43 +11761,47 @@
         <v>204</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>912</v>
+        <v>984</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>913</v>
+        <v>985</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>914</v>
+        <v>986</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>915</v>
+        <v>987</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J15" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>916</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>917</v>
-      </c>
-      <c r="M15" s="3" t="str">
+      <c r="O15" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="Q15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2024_TACO_A刊_ATP: Achieving Throughput Peak for DNN Training via Smart GPU Memory Management</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:16">
+      <c r="R15" s="3"/>
+      <c r="S15" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:20">
       <c r="A16" s="3">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -11116,43 +11813,47 @@
         <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>919</v>
+        <v>991</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>920</v>
+        <v>992</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J16" s="3">
+        <v>906</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3">
         <v>4</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="M16" s="3" t="str">
+      <c r="O16" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="Q16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2024_ASPLOS_A会_MAGIS: Memory Optimization via Coordinated Graph Transformation and Scheduling for DNN</v>
       </c>
-      <c r="N16" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>923</v>
-      </c>
-      <c r="P16" s="3"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:16">
+      <c r="R16" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:20">
       <c r="A17" s="3">
         <f t="shared" si="2"/>
         <v>16</v>
@@ -11164,43 +11865,47 @@
         <v>150</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>924</v>
+        <v>996</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>788</v>
+        <v>836</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>925</v>
+        <v>997</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>926</v>
+        <v>998</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>927</v>
+        <v>999</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="J17" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>928</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="M17" s="3" t="str">
+      <c r="O17" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="Q17" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2025_SIGMOD_A会_MEMO: Fine-grained Tensor Management For Ultra-long Context LLM Training</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3" t="s">
-        <v>930</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:16">
+      <c r="R17" s="3"/>
+      <c r="S17" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:20">
       <c r="A18" s="3">
         <f t="shared" si="2"/>
         <v>17</v>
@@ -11212,53 +11917,57 @@
         <v>150</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>882</v>
+        <v>954</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>931</v>
+        <v>1003</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>932</v>
+        <v>1004</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="J18" s="3">
+        <v>906</v>
+      </c>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3">
         <v>1</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="M18" s="3" t="str">
+      <c r="O18" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="Q18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2025_ICDE_A会_LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>936</v>
+      <c r="R18" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>1008</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P18" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:P18">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T18" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:T18">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="41" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -11297,7 +12006,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -11306,14 +12015,14 @@
     <col min="6" max="6" width="20.7777777777778" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7777777777778" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="10" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="11" max="13" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="14" max="14" width="5.77777777777778" style="1" customWidth="1"/>
-    <col min="15" max="16" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="8.88888888888889" style="1"/>
+    <col min="9" max="14" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="15" max="17" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.77777777777778" style="1" customWidth="1"/>
+    <col min="19" max="20" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:16">
+    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11342,28 +12051,40 @@
         <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="O1" s="2" t="s">
+      <c r="R1" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:16">
+    <row r="2" ht="36" customHeight="1" spans="1:20">
       <c r="A2" s="4">
         <f t="shared" ref="A2:A7" si="0">ROW()-1</f>
         <v>1</v>
@@ -11375,41 +12096,45 @@
         <v>113</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>937</v>
+        <v>1009</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>938</v>
+        <v>1010</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>939</v>
-      </c>
-      <c r="J2" s="4">
+        <v>1011</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4">
         <v>24</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>940</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>941</v>
-      </c>
-      <c r="M2" s="4" t="str">
+      <c r="O2" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="Q2" s="4" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2018_arXiv:1804.10001_v1_Profile-guided memory optimization for deep neural networks</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4" t="s">
-        <v>942</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:16">
+      <c r="R2" s="4"/>
+      <c r="S2" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:20">
       <c r="A3" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -11427,37 +12152,41 @@
         <v>426</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>943</v>
+        <v>1015</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>944</v>
+        <v>1016</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="J3" s="3">
+        <v>1011</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3">
         <v>5</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="M3" s="3" t="str">
-        <f t="shared" ref="M2:M7" si="1">B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
+      <c r="O3" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="Q3" s="3" t="str">
+        <f t="shared" ref="Q2:Q7" si="1">B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
         <v>2023_NeurIPS_A会_Coop: Memory is not a Commodity</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="P3" s="3"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:16">
+      <c r="R3" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="T3" s="3"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:20">
       <c r="A4" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -11475,37 +12204,41 @@
         <v>382</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>948</v>
+        <v>1020</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>949</v>
+        <v>1021</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="J4" s="3">
+        <v>1011</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3">
         <v>12</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>950</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>951</v>
-      </c>
-      <c r="M4" s="3" t="str">
+      <c r="O4" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="Q4" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_MODeL: Memory Optimizations for Deep Learning</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>952</v>
-      </c>
-      <c r="P4" s="3"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:16">
+      <c r="R4" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="T4" s="3"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:20">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -11517,43 +12250,47 @@
         <v>113</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>953</v>
+        <v>1025</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>954</v>
+        <v>1026</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>955</v>
+        <v>1027</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>956</v>
+        <v>1028</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>957</v>
+        <v>1029</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="J5" s="3">
+        <v>1011</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3">
         <v>2</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>958</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>959</v>
-      </c>
-      <c r="M5" s="3" t="str">
+      <c r="O5" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="Q5" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_arXiv:2310.19295_v1_ROAM: memory-efficient large DNN training via optimized operator ordering and memory layout</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3" t="s">
-        <v>960</v>
-      </c>
-      <c r="P5" s="3"/>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:16">
+      <c r="R5" s="3"/>
+      <c r="S5" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="T5" s="3"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:20">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -11565,47 +12302,51 @@
         <v>150</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>961</v>
+        <v>1033</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>962</v>
+        <v>1034</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>963</v>
+        <v>1035</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>964</v>
+        <v>1036</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>939</v>
-      </c>
-      <c r="J6" s="4">
+        <v>1011</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4">
         <v>12</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>965</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>966</v>
-      </c>
-      <c r="M6" s="4" t="str">
+      <c r="O6" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="Q6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2024_ASPLOS_A会_GMLake: Efficient and Transparent GPU Memory Defragmentation for Large-scale DNN Training with Virtual Memory Stitching</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>967</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:16">
+      <c r="R6" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:20">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -11614,50 +12355,54 @@
         <v>2024</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>968</v>
+        <v>1040</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>969</v>
+        <v>1041</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>970</v>
+        <v>1042</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="J7" s="3">
+        <v>1011</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3">
         <v>1</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>971</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>972</v>
-      </c>
-      <c r="M7" s="3" t="str">
+      <c r="O7" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="Q7" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2024_ISMM_内存领域_A Heuristic for Periodic Memory Allocation with Little Fragmentation to Train Neural Networks</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P7" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:P7">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T7" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:T7">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="41" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -11682,16 +12427,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>973</v>
+        <v>1045</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>974</v>
+        <v>1046</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>975</v>
+        <v>1047</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -11718,26 +12463,26 @@
         <v>2019</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>976</v>
+        <v>1048</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>977</v>
+        <v>1049</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>978</v>
+        <v>1050</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>979</v>
+        <v>1051</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>980</v>
+        <v>1052</v>
       </c>
       <c r="H2" s="3" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;E2&amp;""</f>
         <v>2019_A Taxonomy of Cache Replacement Policies_缓存替换策略的分类</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>981</v>
+        <v>1053</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -11750,26 +12495,26 @@
         <v>2023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>982</v>
+        <v>1054</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>983</v>
+        <v>1055</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>984</v>
+        <v>1056</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>985</v>
+        <v>1057</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>986</v>
+        <v>1058</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>B3&amp;"_"&amp;D3&amp;"_"&amp;E3&amp;""</f>
         <v>2023_Operating Systems: Three Easy Pieces_操作系统导论</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>987</v>
+        <v>1059</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -11785,27 +12530,27 @@
         <v>284</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>988</v>
+        <v>1060</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>989</v>
+        <v>1061</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>990</v>
+        <v>1062</v>
       </c>
       <c r="H4" s="3" t="str">
         <f>B4&amp;"_"&amp;D4&amp;""</f>
         <v>2024_大语言模型</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>991</v>
+        <v>1063</v>
       </c>
       <c r="J4" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J3" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:J3">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J4" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:J4">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>

--- a/InfoSummary.xlsx
+++ b/InfoSummary.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14088" firstSheet="2" activeTab="5"/>
+    <workbookView windowWidth="29868" windowHeight="14088" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="学位" sheetId="10" r:id="rId1"/>
     <sheet name="综述" sheetId="1" r:id="rId2"/>
     <sheet name="框架" sheetId="9" r:id="rId3"/>
     <sheet name="模型" sheetId="12" r:id="rId4"/>
-    <sheet name="Swap" sheetId="2" r:id="rId5"/>
-    <sheet name="Recomp" sheetId="6" r:id="rId6"/>
+    <sheet name="Recomp" sheetId="6" r:id="rId5"/>
+    <sheet name="Swap" sheetId="2" r:id="rId6"/>
     <sheet name="Hybrid" sheetId="7" r:id="rId7"/>
     <sheet name="MAS" sheetId="8" r:id="rId8"/>
     <sheet name="电子书" sheetId="14" r:id="rId9"/>
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">综述!$A$1:$N$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">框架!$A$1:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">模型!$A$1:$N$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Swap!$A$1:$T$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Recomp!$A$1:$U$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Recomp!$A$1:$U$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Swap!$A$1:$U$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hybrid!$A$1:$T$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">MAS!$A$1:$T$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">电子书!$A$1:$J$4</definedName>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="1169">
   <si>
     <t>序号</t>
   </si>
@@ -1801,6 +1801,9 @@
     <t>Granularity</t>
   </si>
   <si>
+    <t>Target (s)</t>
+  </si>
+  <si>
     <t>Strategy</t>
   </si>
   <si>
@@ -1813,510 +1816,37 @@
     <t>开源</t>
   </si>
   <si>
-    <t>MICRO</t>
-  </si>
-  <si>
-    <t>vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design</t>
-  </si>
-  <si>
-    <t>vDNN</t>
-  </si>
-  <si>
-    <t>内存交换;</t>
-  </si>
-  <si>
-    <t>[1]Rhu M, Gimelshein N, Clemons J, et al. vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design[C]//2016 49th Annual IEEE/ACM International Symposium on Microarchitecture (MICRO). IEEE, 2016: 1-13.</t>
-  </si>
-  <si>
-    <t>rhu2016vdnn</t>
-  </si>
-  <si>
-    <t>有影响力的工作。</t>
-  </si>
-  <si>
-    <t>C会</t>
-  </si>
-  <si>
-    <t>HiPC</t>
-  </si>
-  <si>
-    <t>OC-DNN: Exploiting Advanced Unified Memory Capabilities in CUDA 9 and Volta GPUs for Out-of-Core DNN Training</t>
-  </si>
-  <si>
-    <t>OC-DNN</t>
-  </si>
-  <si>
-    <t>内存交换;CUDA UM;</t>
-  </si>
-  <si>
-    <t>[1]Awan A A, Chu C H, Subramoni H, et al. Oc-dnn: Exploiting advanced unified memory capabilities in cuda 9 and volta gpus for out-of-core dnn training[C]//2018 IEEE 25th International Conference on High Performance Computing (HiPC). IEEE, 2018: 143-152.</t>
-  </si>
-  <si>
-    <t>awan2018oc</t>
-  </si>
-  <si>
-    <t>有影响力的工作。
-虽然是C会的工作，但引用量很高，算是CUDA UM最早的工作。</t>
-  </si>
-  <si>
-    <t>moDNN: Memory Optimal Deep Neural Network Training on Graphics Processing Units</t>
-  </si>
-  <si>
-    <t>moDNN</t>
-  </si>
-  <si>
-    <t>Deep neural networks, graphics processing units, memory usage</t>
-  </si>
-  <si>
-    <t>[1]Chen X, Chen D Z, Han Y, et al. moDNN: Memory optimal deep neural network training on graphics processing units[J]. IEEE Transactions on Parallel and Distributed Systems, 2018, 30(3): 646-661.</t>
-  </si>
-  <si>
-    <t>chen2018modnn</t>
-  </si>
-  <si>
-    <t>TACO</t>
-  </si>
-  <si>
-    <t>Layer-Centric Memory Reuse and Data Migration for Extreme-Scale Deep Learning on Many-Core Architectures</t>
-  </si>
-  <si>
-    <t>Layrub</t>
-  </si>
-  <si>
-    <t>Data placement, DNN, GPU, memory efficiency</t>
-  </si>
-  <si>
-    <t>[1]Jin H, Liu B, Jiang W, et al. Layer-centric memory reuse and data migration for extreme-scale deep learning on many-core architectures[J]. ACM Transactions on Architecture and Code Optimization (TACO), 2018, 15(3): 1-26.</t>
-  </si>
-  <si>
-    <t>jin2018layer</t>
+    <t>arXiv:1604.06174</t>
+  </si>
+  <si>
+    <t>Training Deep Nets with Sublinear Memory Cost</t>
+  </si>
+  <si>
+    <t>Sublinear</t>
+  </si>
+  <si>
+    <t>重计算;静态;离线;</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>intermediate results (feature maps);</t>
+  </si>
+  <si>
+    <t>gradient graph construction algorithm; greedy allocation; heuristic search;</t>
+  </si>
+  <si>
+    <t>MXNet;</t>
+  </si>
+  <si>
+    <t>[1]Chen T, Xu B, Zhang C, et al. Training deep nets with sublinear memory cost[J]. arXiv preprint arXiv:1604.06174, 2016.</t>
+  </si>
+  <si>
+    <t>chen2016training</t>
   </si>
   <si>
     <t>✔</t>
-  </si>
-  <si>
-    <t>论文地址：https://dl.acm.org/doi/abs/10.1145/3243904
-代码仓库：https://github.com/CGCL-codes/Layrub
-论文博客：https://mp.weixin.qq.com/s/pz60qGvMfQEUIbeM00TOkQ</t>
-  </si>
-  <si>
-    <t>ICCD</t>
-  </si>
-  <si>
-    <t>信工所</t>
-  </si>
-  <si>
-    <t>AccUDNN: A GPU Memory Efficient Accelerator for Training Ultra-Deep Neural Networks</t>
-  </si>
-  <si>
-    <t>AccUDNN</t>
-  </si>
-  <si>
-    <t>ultra-deep neural network, GPU, memory optimization, speed up</t>
-  </si>
-  <si>
-    <t>[1]Guo J, Liu W, Wang W, et al. AccUDNN: A GPU memory efficient accelerator for training ultra-deep neural networks[C]//2019 IEEE 37th International Conference on Computer Design (ICCD). IEEE, 2019: 65-72.</t>
-  </si>
-  <si>
-    <t>guo2019accudnn</t>
-  </si>
-  <si>
-    <t>内存领域</t>
-  </si>
-  <si>
-    <t>ISMM</t>
-  </si>
-  <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>Automatic GPU memory management for large neural models in TensorFlow</t>
-  </si>
-  <si>
-    <t>LMS</t>
-  </si>
-  <si>
-    <t>large neural models, computational graphs, simulator, GPU memory</t>
-  </si>
-  <si>
-    <t>[1]Le T D, Imai H, Negishi Y, et al. Automatic gpu memory management for large neural models in tensorflow[C]//Proceedings of the 2019 ACM SIGPLAN International Symposium on Memory Management. 2019: 1-13.</t>
-  </si>
-  <si>
-    <t>le2019automatic</t>
-  </si>
-  <si>
-    <t>代码仓库：https://github.com/IBM/tensorflow-large-model-support/tree/tflmsv2</t>
-  </si>
-  <si>
-    <t>IPDPS</t>
-  </si>
-  <si>
-    <t>印度理工学院</t>
-  </si>
-  <si>
-    <t>Dynamic Memory Management for GPU-Based Training of Deep Neural Networks</t>
-  </si>
-  <si>
-    <t>vDNN++</t>
-  </si>
-  <si>
-    <t>Deep Learning; Deep Neural Networks; GPU; Memory management;</t>
-  </si>
-  <si>
-    <t>内存交换;内存分配;</t>
-  </si>
-  <si>
-    <t>[1]Shriram S B, Garg A, Kulkarni P. Dynamic memory management for GPU-based training of deep neural networks[C]//2019 IEEE International Parallel and Distributed Processing Symposium (IPDPS). IEEE, 2019: 200-209.</t>
-  </si>
-  <si>
-    <t>shriram2019dynamic</t>
-  </si>
-  <si>
-    <t>代码仓库：https://github.com/shriramsb/vdnn-plus-plus</t>
-  </si>
-  <si>
-    <t>arXiv:1903.06631</t>
-  </si>
-  <si>
-    <t>新加坡国立大学</t>
-  </si>
-  <si>
-    <t>Efficient Memory Management for GPU-based Deep Learning Systems</t>
-  </si>
-  <si>
-    <t>GPU, Memory management, Deep learning systems.</t>
-  </si>
-  <si>
-    <t>[1]Zhang J, Yeung S H, Shu Y, et al. Efficient memory management for gpu-based deep learning systems[J]. arXiv preprint arXiv:1903.06631, 2019.</t>
-  </si>
-  <si>
-    <t>zhang2019efficient</t>
-  </si>
-  <si>
-    <t>论文地址：https://arxiv.org/abs/1903.06631</t>
-  </si>
-  <si>
-    <t>TC</t>
-  </si>
-  <si>
-    <t>UNIST（韩）</t>
-  </si>
-  <si>
-    <t>Hotness- and Lifetime-Aware Data Placement and Migration for High-Performance Deep Learning on Heterogeneous Memory Systems</t>
-  </si>
-  <si>
-    <t>HALO</t>
-  </si>
-  <si>
-    <t>Hotness-and lifetime-aware data placement and migration, high-performance deep learning, heterogeneous memory systems</t>
-  </si>
-  <si>
-    <t>[1]Han M, Hyun J, Park S, et al. Hotness-and lifetime-aware data placement and migration for high-performance deep learning on heterogeneous memory systems[J]. IEEE Transactions on Computers, 2019, 69(3): 377-391.</t>
-  </si>
-  <si>
-    <t>han2019hotness</t>
-  </si>
-  <si>
-    <t>ASPLOS</t>
-  </si>
-  <si>
-    <t>加州大学</t>
-  </si>
-  <si>
-    <t>AutoTM: Automatic Tensor Movement in Heterogeneous Memory Systems using Integer Linear Programming</t>
-  </si>
-  <si>
-    <t>AutoTM</t>
-  </si>
-  <si>
-    <t>[1]Hildebrand M, Khan J, Trika S, et al. Autotm: Automatic tensor movement in heterogeneous memory systems using integer linear programming[C]//Proceedings of the Twenty-Fifth International Conference on Architectural Support for Programming Languages and Operating Systems. 2020: 875-890.</t>
-  </si>
-  <si>
-    <t>hildebrand2020autotm</t>
-  </si>
-  <si>
-    <t>论文地址：https://dl.acm.org/doi/abs/10.1145/3373376.3378465
-代码仓库：https://github.com/darchr/AutoTM</t>
-  </si>
-  <si>
-    <t>纽约大学</t>
-  </si>
-  <si>
-    <t>SwapAdvisor: Pushing Deep Learning Beyond the GPU Memory Limit via Smart Swapping</t>
-  </si>
-  <si>
-    <t>SwapAdvisor</t>
-  </si>
-  <si>
-    <t>[1]Huang C C, Jin G, Li J. Swapadvisor: Pushing deep learning beyond the gpu memory limit via smart swapping[C]//Proceedings of the Twenty-Fifth International Conference on Architectural Support for Programming Languages and Operating Systems. 2020: 1341-1355.</t>
-  </si>
-  <si>
-    <t>huang2020swapadvisor</t>
-  </si>
-  <si>
-    <t>HPDC</t>
-  </si>
-  <si>
-    <t>北卡罗来纳大学</t>
-  </si>
-  <si>
-    <t>Efficient GPU Memory Management for Nonlinear DNNs</t>
-  </si>
-  <si>
-    <t>Dymem</t>
-  </si>
-  <si>
-    <t>GPU Memory Management; Resource Management</t>
-  </si>
-  <si>
-    <t>[1]Yang D, Cheng D. Efficient GPU memory management for nonlinear DNNs[C]//Proceedings of the 29th International Symposium on High-Performance Parallel and Distributed Computing. 2020: 185-196.</t>
-  </si>
-  <si>
-    <t>yang2020efficient</t>
-  </si>
-  <si>
-    <t>论文地址：https://dl.acm.org/doi/abs/10.1145/3369583.3392684</t>
-  </si>
-  <si>
-    <t>Euro-Par</t>
-  </si>
-  <si>
-    <t>INRIA（法）</t>
-  </si>
-  <si>
-    <t>Optimal GPU-CPU Offloading Strategies for Deep Neural Network Training</t>
-  </si>
-  <si>
-    <t>Memory management,Deep Neural Network,Dynamic programming,Scheduling</t>
-  </si>
-  <si>
-    <t>[1]Beaumont O, Eyraud-Dubois L, Shilova A. Optimal GPU-CPU offloading strategies for deep neural network training[C]//European Conference on Parallel Processing. Cham: Springer International Publishing, 2020: 151-166.</t>
-  </si>
-  <si>
-    <t>beaumont2020optimal</t>
-  </si>
-  <si>
-    <t>论文地址：https://link.springer.com/chapter/10.1007/978-3-030-57675-2_10</t>
-  </si>
-  <si>
-    <t>FAST</t>
-  </si>
-  <si>
-    <t>FlashNeuron: SSD-Enabled Large-Batch Training of Very Deep Neural Networks</t>
-  </si>
-  <si>
-    <t>FlashNeuron</t>
-  </si>
-  <si>
-    <t>[1]Bae J, Lee J, Jin Y, et al. {FlashNeuron}:{SSD-Enabled}{Large-Batch} training of very deep neural networks[C]//19th USENIX Conference on File and Storage Technologies (FAST 21). 2021: 387-401.</t>
-  </si>
-  <si>
-    <t>bae2021flashneuron</t>
-  </si>
-  <si>
-    <t>论文地址：https://www.usenix.org/conference/fast21/presentation/bae
-代码仓库：https://github.com/SNU-ARC/flashneuron</t>
-  </si>
-  <si>
-    <t>HPCA</t>
-  </si>
-  <si>
-    <t>Sentinel: Efficient Tensor Migration and Allocation on Heterogeneous Memory Systems for Deep Learning</t>
-  </si>
-  <si>
-    <t>Sentinel</t>
-  </si>
-  <si>
-    <t>heterogeneous memory, deep neural network training, memory management</t>
-  </si>
-  <si>
-    <t>[1]Ren J, Luo J, Wu K, et al. Sentinel: Efficient tensor migration and allocation on heterogeneous memory systems for deep learning[C]//2021 IEEE International Symposium on High-Performance Computer Architecture (HPCA). IEEE, 2021: 598-611.</t>
-  </si>
-  <si>
-    <t>ren2021sentinel</t>
-  </si>
-  <si>
-    <t>Accelerating Tensor Swapping in GPUs With Self-Tuning Compression</t>
-  </si>
-  <si>
-    <t>CSwap+</t>
-  </si>
-  <si>
-    <t>DNN,GPU,tensor,swapping,compression</t>
-  </si>
-  <si>
-    <t>[1]Chen P, He S, Zhang X, et al. Accelerating tensor swapping in gpus with self-tuning compression[J]. IEEE Transactions on Parallel and Distributed Systems, 2022, 33(12): 4484-4498.</t>
-  </si>
-  <si>
-    <t>chen2022accelerating</t>
-  </si>
-  <si>
-    <t>代码仓库：https://github.com/ISCS-ZJU/CSWAP</t>
-  </si>
-  <si>
-    <t>An Application-oblivious Memory Scheduling System for DNN Accelerators</t>
-  </si>
-  <si>
-    <t>AppObMem</t>
-  </si>
-  <si>
-    <t>Deep learning, memory scheduling, runtime system, DNN accelerators</t>
-  </si>
-  <si>
-    <t>[1]Li J, Wang X, Chen X, et al. An application-oblivious memory scheduling system for DNN accelerators[J]. ACM Transactions on Architecture and Code Optimization (TACO), 2022, 19(4): 1-26.</t>
-  </si>
-  <si>
-    <t>li2022application</t>
-  </si>
-  <si>
-    <t>论文地址：https://dl.acm.org/doi/full/10.1145/3535355</t>
-  </si>
-  <si>
-    <t>利兹大学</t>
-  </si>
-  <si>
-    <t>STRONGHOLD: Fast and Affordable Billion-Scale Deep Learning Model Training</t>
-  </si>
-  <si>
-    <t>STRONGHOLD</t>
-  </si>
-  <si>
-    <t>Deep learning, Distributed training, DNNs training acceleration</t>
-  </si>
-  <si>
-    <t>[1]Sun X, Wang W, Qiu S, et al. Stronghold: fast and affordable billion-scale deep learning model training[C]//SC22: International Conference for High Performance Computing, Networking, Storage and Analysis. IEEE, 2022: 1-17.</t>
-  </si>
-  <si>
-    <t>sun2022stronghold</t>
-  </si>
-  <si>
-    <t>DeepUM: Tensor Migration and Prefetching in Unified Memory</t>
-  </si>
-  <si>
-    <t>DeepUM</t>
-  </si>
-  <si>
-    <t>deep learning, neural networks, CUDA, unified memory, data prefetching, runtime system, device driver</t>
-  </si>
-  <si>
-    <t>[1]Jung J, Kim J, Lee J. Deepum: Tensor migration and prefetching in unified memory[C]//Proceedings of the 28th ACM International Conference on Architectural Support for Programming Languages and Operating Systems, Volume 2. 2023: 207-221.</t>
-  </si>
-  <si>
-    <t>jung2023deepum</t>
-  </si>
-  <si>
-    <t>UIUC（美）</t>
-  </si>
-  <si>
-    <t>G10: Enabling An Efficient Unified GPU Memory and Storage Architecture with Smart Tensor Migrations</t>
-  </si>
-  <si>
-    <t>G10</t>
-  </si>
-  <si>
-    <t>GPUDirect Storage, Unified Virtual Memory, GPU Memory, Solid State Drives, Deep Learning Compiler</t>
-  </si>
-  <si>
-    <t>[1]Zhang H, Zhou Y, Xue Y, et al. G10: Enabling an efficient unified gpu memory and storage architecture with smart tensor migrations[C]//Proceedings of the 56th Annual IEEE/ACM International Symposium on Microarchitecture. 2023: 395-410.</t>
-  </si>
-  <si>
-    <t>zhang2023g10</t>
-  </si>
-  <si>
-    <t>论文地址：https://dl.acm.org/doi/abs/10.1145/3613424.3614309
-代码仓库：https://github.com/platformxlab/g10</t>
-  </si>
-  <si>
-    <t>威廉与玛丽学院</t>
-  </si>
-  <si>
-    <t>Enabling Large Dynamic Neural Network Training with Learning-based Memory Management</t>
-  </si>
-  <si>
-    <t>DyNN-Offload</t>
-  </si>
-  <si>
-    <t>[1]Ren J, Xu D, Yang S, et al. Enabling Large Dynamic Neural Network Training with Learning-based Memory Management[C]//2024 IEEE International Symposium on High-Performance Computer Architecture (HPCA). IEEE, 2024: 788-802.</t>
-  </si>
-  <si>
-    <t>ren2024enabling</t>
-  </si>
-  <si>
-    <t>关于动态神经网络：https://arxiv.org/abs/2102.04906v4
-上文翻译：https://zhuanlan.zhihu.com/p/354507714</t>
-  </si>
-  <si>
-    <t>武大</t>
-  </si>
-  <si>
-    <t>DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training</t>
-  </si>
-  <si>
-    <t>DeepTM</t>
-  </si>
-  <si>
-    <t>Deep neural network training, heterogeneous memory, memory management, performance optimization.</t>
-  </si>
-  <si>
-    <t>[1]Zhou H, Rang W, Chen H, et al. DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training[J]. IEEE Transactions on Parallel and Distributed Systems, 2024.</t>
-  </si>
-  <si>
-    <t>zhou2024deeptm</t>
-  </si>
-  <si>
-    <t>arXiv:2406.10181</t>
-  </si>
-  <si>
-    <t>CMU（美）</t>
-  </si>
-  <si>
-    <t>Practical offloading for fine-tuning LLM on commodity GPU via learned sparse projectors</t>
-  </si>
-  <si>
-    <t>LSP-Offload</t>
-  </si>
-  <si>
-    <t>[1]Chen S, Guan Z, Liu Y, et al. Practical offloading for fine-tuning LLM on commodity GPU via learned subspace projectors[J]. arXiv preprint arXiv:2406.10181, 2024.</t>
-  </si>
-  <si>
-    <t>chen2024practical</t>
-  </si>
-  <si>
-    <t>论文地址：https://arxiv.org/abs/2406.10181
-代码仓库：https://github.com/gulang2019/LSP-Offload/tree/main</t>
-  </si>
-  <si>
-    <t>Target (s)</t>
-  </si>
-  <si>
-    <t>arXiv:1604.06174</t>
-  </si>
-  <si>
-    <t>Training Deep Nets with Sublinear Memory Cost</t>
-  </si>
-  <si>
-    <t>Sublinear</t>
-  </si>
-  <si>
-    <t>重计算;静态;离线;</t>
-  </si>
-  <si>
-    <t>Layer</t>
-  </si>
-  <si>
-    <t>intermediate results (feature maps);</t>
-  </si>
-  <si>
-    <t>gradient graph construction algorithm; greedy allocation; heuristic search;</t>
-  </si>
-  <si>
-    <t>MXNet;</t>
-  </si>
-  <si>
-    <t>[1]Chen T, Xu B, Zhang C, et al. Training deep nets with sublinear memory cost[J]. arXiv preprint arXiv:1604.06174, 2016.</t>
-  </si>
-  <si>
-    <t>chen2016training</t>
   </si>
   <si>
     <t>论文地址：https://arxiv.org/abs/1604.06174
@@ -2423,6 +1953,9 @@
     <t>arXiv:1911.13214</t>
   </si>
   <si>
+    <t>INRIA（法）</t>
+  </si>
+  <si>
     <t>Optimal checkpointing for heterogeneous chains: how to train deep neural networks with limited memory</t>
   </si>
   <si>
@@ -2483,6 +2016,9 @@
 论文博客1：https://zhuanlan.zhihu.com/p/299861314
 论文博客2：https://www.jianshu.com/p/4d3ebdd305f1
 关于MILP：https://www.zhihu.com/question/25560707?sort=created</t>
+  </si>
+  <si>
+    <t>有影响力的工作。</t>
   </si>
   <si>
     <t>ISCA</t>
@@ -2640,7 +2176,8 @@
     <t>andoorveedu2022tempo</t>
   </si>
   <si>
-    <t>论文地址：https://proceedings.neurips.cc/paper_files/paper/2022/hash/4fc81f4cd2715d995018e0799262176b-Abstract-Conference.html
+    <t>论文地址1：https://proceedings.neurips.cc/paper_files/paper/2022/hash/4fc81f4cd2715d995018e0799262176b-Abstract-Conference.html
+论文地址2：https://arxiv.org/abs/2210.10246
 论文博客：https://blog.csdn.net/qq_43207982/article/details/134215344
 代码仓库：https://github.com/UofT-EcoSystem/Tempo</t>
   </si>
@@ -2681,7 +2218,12 @@
     <t>wang2022melon</t>
   </si>
   <si>
-    <t>代码仓库：https://github.com/qipengwang/Melon</t>
+    <t>论文博客1：https://mp.weixin.qq.com/s/_qII_ztEg5blV6e8r9W0jQ
+论文博客2：https://zhuanlan.zhihu.com/p/532806517
+代码仓库：https://github.com/qipengwang/Melon</t>
+  </si>
+  <si>
+    <t>TACO</t>
   </si>
   <si>
     <t>萨尔大学（德）</t>
@@ -2717,6 +2259,9 @@
     <t>论文地址1：https://dl.acm.org/doi/full/10.1145/3568956
 论文地址2：https://arxiv.org/abs/2212.09290
 代码仓库：https://github.com/dfki-asr/xengine</t>
+  </si>
+  <si>
+    <t>IPDPS</t>
   </si>
   <si>
     <t>北航</t>
@@ -2770,7 +2315,7 @@
     <t>constraint programming;</t>
   </si>
   <si>
-    <t>没在深度学习框架上实现</t>
+    <t>模拟实现</t>
   </si>
   <si>
     <t>Checkmate;</t>
@@ -2863,6 +2408,716 @@
 代码仓库：https://github.com/nyngwang/GPU-Memory-Usage-Optimization-for-Backward-Propagation-in-Deep-Network-Training</t>
   </si>
   <si>
+    <t>MICRO</t>
+  </si>
+  <si>
+    <t>vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design</t>
+  </si>
+  <si>
+    <t>vDNN</t>
+  </si>
+  <si>
+    <t>内存交换;静态;离线;</t>
+  </si>
+  <si>
+    <t>intermediate feature maps;</t>
+  </si>
+  <si>
+    <t>heuristic;</t>
+  </si>
+  <si>
+    <t>Torch</t>
+  </si>
+  <si>
+    <t>Torch;</t>
+  </si>
+  <si>
+    <t>[1]Rhu M, Gimelshein N, Clemons J, et al. vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design[C]//2016 49th Annual IEEE/ACM International Symposium on Microarchitecture (MICRO). IEEE, 2016: 1-13.</t>
+  </si>
+  <si>
+    <t>rhu2016vdnn</t>
+  </si>
+  <si>
+    <t>论文博客1：https://blog.csdn.net/zyd2016/article/details/112721059
+论文博客2：https://zzqq2199.github.io/2021/03/11/vDNN/</t>
+  </si>
+  <si>
+    <t>C会</t>
+  </si>
+  <si>
+    <t>HiPC</t>
+  </si>
+  <si>
+    <t>OC-DNN: Exploiting Advanced Unified Memory Capabilities in CUDA 9 and Volta GPUs for Out-of-Core DNN Training</t>
+  </si>
+  <si>
+    <t>OC-DNN</t>
+  </si>
+  <si>
+    <t>内存交换;CUDA UM;静态;离线;</t>
+  </si>
+  <si>
+    <t>data;</t>
+  </si>
+  <si>
+    <t>interfaces designs;</t>
+  </si>
+  <si>
+    <t>Caffe 1.0</t>
+  </si>
+  <si>
+    <t>Caffe;</t>
+  </si>
+  <si>
+    <t>[1]Awan A A, Chu C H, Subramoni H, et al. Oc-dnn: Exploiting advanced unified memory capabilities in cuda 9 and volta gpus for out-of-core dnn training[C]//2018 IEEE 25th International Conference on High Performance Computing (HiPC). IEEE, 2018: 143-152.</t>
+  </si>
+  <si>
+    <t>awan2018oc</t>
+  </si>
+  <si>
+    <t>有影响力的工作。
+虽然是C会的工作，但引用量很高，算是CUDA UM最早的工作。</t>
+  </si>
+  <si>
+    <t>moDNN: Memory Optimal Deep Neural Network Training on Graphics Processing Units</t>
+  </si>
+  <si>
+    <t>moDNN</t>
+  </si>
+  <si>
+    <t>Deep neural networks, graphics processing units, memory usage</t>
+  </si>
+  <si>
+    <t>immediate output;</t>
+  </si>
+  <si>
+    <t>vDNN;</t>
+  </si>
+  <si>
+    <t>[1]Chen X, Chen D Z, Han Y, et al. moDNN: Memory optimal deep neural network training on graphics processing units[J]. IEEE Transactions on Parallel and Distributed Systems, 2018, 30(3): 646-661.</t>
+  </si>
+  <si>
+    <t>chen2018modnn</t>
+  </si>
+  <si>
+    <t>论文博客1：https://mp.weixin.qq.com/s/dQgNpTlxFUg-h_XruXpbtQ
+论文博客2：https://mp.weixin.qq.com/s/bBD0iZnBUVnC7gAGt8MwXg</t>
+  </si>
+  <si>
+    <t>Layer-Centric Memory Reuse and Data Migration for Extreme-Scale Deep Learning on Many-Core Architectures</t>
+  </si>
+  <si>
+    <t>Layrub</t>
+  </si>
+  <si>
+    <t>Data placement, DNN, GPU, memory efficiency</t>
+  </si>
+  <si>
+    <t>activation data; gradient;</t>
+  </si>
+  <si>
+    <t>layer-centric; reference count;</t>
+  </si>
+  <si>
+    <t>Caffe; MXNet; TensorFlow; vDNN;</t>
+  </si>
+  <si>
+    <t>[1]Jin H, Liu B, Jiang W, et al. Layer-centric memory reuse and data migration for extreme-scale deep learning on many-core architectures[J]. ACM Transactions on Architecture and Code Optimization (TACO), 2018, 15(3): 1-26.</t>
+  </si>
+  <si>
+    <t>jin2018layer</t>
+  </si>
+  <si>
+    <t>论文地址：https://dl.acm.org/doi/abs/10.1145/3243904
+代码仓库：https://github.com/CGCL-codes/Layrub
+论文博客：https://mp.weixin.qq.com/s/pz60qGvMfQEUIbeM00TOkQ</t>
+  </si>
+  <si>
+    <t>ICCD</t>
+  </si>
+  <si>
+    <t>信工所</t>
+  </si>
+  <si>
+    <t>AccUDNN: A GPU Memory Efficient Accelerator for Training Ultra-Deep Neural Networks</t>
+  </si>
+  <si>
+    <t>AccUDNN</t>
+  </si>
+  <si>
+    <t>ultra-deep neural network, GPU, memory optimization, speed up</t>
+  </si>
+  <si>
+    <t>feature map;</t>
+  </si>
+  <si>
+    <t>integer linear programming; linear search algorithm;</t>
+  </si>
+  <si>
+    <t>Caffe; SuperNeurons</t>
+  </si>
+  <si>
+    <t>[1]Guo J, Liu W, Wang W, et al. AccUDNN: A GPU memory efficient accelerator for training ultra-deep neural networks[C]//2019 IEEE 37th International Conference on Computer Design (ICCD). IEEE, 2019: 65-72.</t>
+  </si>
+  <si>
+    <t>guo2019accudnn</t>
+  </si>
+  <si>
+    <t>论文地址：https://arxiv.org/abs/1901.06773</t>
+  </si>
+  <si>
+    <t>内存领域</t>
+  </si>
+  <si>
+    <t>ISMM</t>
+  </si>
+  <si>
+    <t>IBM</t>
+  </si>
+  <si>
+    <t>Automatic GPU memory management for large neural models in TensorFlow</t>
+  </si>
+  <si>
+    <t>LMS</t>
+  </si>
+  <si>
+    <t>large neural models, computational graphs, simulator, GPU memory</t>
+  </si>
+  <si>
+    <t>内存交换;图论;静态;离线;</t>
+  </si>
+  <si>
+    <t>graph rewriting; categorized topological ordering;</t>
+  </si>
+  <si>
+    <t>TensorFlow 1.10</t>
+  </si>
+  <si>
+    <t>TensorFlow;</t>
+  </si>
+  <si>
+    <t>[1]Le T D, Imai H, Negishi Y, et al. Automatic gpu memory management for large neural models in tensorflow[C]//Proceedings of the 2019 ACM SIGPLAN International Symposium on Memory Management. 2019: 1-13.</t>
+  </si>
+  <si>
+    <t>le2019automatic</t>
+  </si>
+  <si>
+    <t>代码仓库：https://github.com/IBM/tensorflow-large-model-support/tree/tflmsv2</t>
+  </si>
+  <si>
+    <t>印度理工学院</t>
+  </si>
+  <si>
+    <t>Dynamic Memory Management for GPU-Based Training of Deep Neural Networks</t>
+  </si>
+  <si>
+    <t>vDNN++</t>
+  </si>
+  <si>
+    <t>Deep Learning; Deep Neural Networks; GPU; Memory management;</t>
+  </si>
+  <si>
+    <t>内存交换;内存分配;静态;离线;</t>
+  </si>
+  <si>
+    <t>仿真实现</t>
+  </si>
+  <si>
+    <t>[1]Shriram S B, Garg A, Kulkarni P. Dynamic memory management for GPU-based training of deep neural networks[C]//2019 IEEE International Parallel and Distributed Processing Symposium (IPDPS). IEEE, 2019: 200-209.</t>
+  </si>
+  <si>
+    <t>shriram2019dynamic</t>
+  </si>
+  <si>
+    <t>代码仓库：https://github.com/shriramsb/vdnn-plus-plus</t>
+  </si>
+  <si>
+    <t>arXiv:1903.06631</t>
+  </si>
+  <si>
+    <t>新加坡国立大学</t>
+  </si>
+  <si>
+    <t>Efficient Memory Management for GPU-based Deep Learning Systems</t>
+  </si>
+  <si>
+    <t>AutoSwap</t>
+  </si>
+  <si>
+    <t>GPU, Memory management, Deep learning systems.</t>
+  </si>
+  <si>
+    <t>内存交换;内存分配;动态;离线;</t>
+  </si>
+  <si>
+    <t>Variables</t>
+  </si>
+  <si>
+    <t>feature maps;</t>
+  </si>
+  <si>
+    <t>heuristic; graph coloring methods; bayesian optimization;</t>
+  </si>
+  <si>
+    <t>Sublinear; SuperNeurons;</t>
+  </si>
+  <si>
+    <t>[1]Zhang J, Yeung S H, Shu Y, et al. Efficient memory management for gpu-based deep learning systems[J]. arXiv preprint arXiv:1903.06631, 2019.</t>
+  </si>
+  <si>
+    <t>zhang2019efficient</t>
+  </si>
+  <si>
+    <t>论文地址：https://arxiv.org/abs/1903.06631</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>UNIST（韩）</t>
+  </si>
+  <si>
+    <t>Hotness- and Lifetime-Aware Data Placement and Migration for High-Performance Deep Learning on Heterogeneous Memory Systems</t>
+  </si>
+  <si>
+    <t>HALO</t>
+  </si>
+  <si>
+    <t>Hotness-and lifetime-aware data placement and migration, high-performance deep learning, heterogeneous memory systems</t>
+  </si>
+  <si>
+    <t>内存交换;</t>
+  </si>
+  <si>
+    <t>TensorFlow 1.4.0</t>
+  </si>
+  <si>
+    <t>[1]Han M, Hyun J, Park S, et al. Hotness-and lifetime-aware data placement and migration for high-performance deep learning on heterogeneous memory systems[J]. IEEE Transactions on Computers, 2019, 69(3): 377-391.</t>
+  </si>
+  <si>
+    <t>han2019hotness</t>
+  </si>
+  <si>
+    <t>ASPLOS</t>
+  </si>
+  <si>
+    <t>加州大学</t>
+  </si>
+  <si>
+    <t>AutoTM: Automatic Tensor Movement in Heterogeneous Memory Systems using Integer Linear Programming</t>
+  </si>
+  <si>
+    <t>AutoTM</t>
+  </si>
+  <si>
+    <t>integer linear programming;</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>[1]Hildebrand M, Khan J, Trika S, et al. Autotm: Automatic tensor movement in heterogeneous memory systems using integer linear programming[C]//Proceedings of the Twenty-Fifth International Conference on Architectural Support for Programming Languages and Operating Systems. 2020: 875-890.</t>
+  </si>
+  <si>
+    <t>hildebrand2020autotm</t>
+  </si>
+  <si>
+    <t>论文地址：https://dl.acm.org/doi/abs/10.1145/3373376.3378465
+代码仓库：https://github.com/darchr/AutoTM</t>
+  </si>
+  <si>
+    <t>纽约大学</t>
+  </si>
+  <si>
+    <t>SwapAdvisor: Pushing Deep Learning Beyond the GPU Memory Limit via Smart Swapping</t>
+  </si>
+  <si>
+    <t>SwapAdvisor</t>
+  </si>
+  <si>
+    <t>tensor;</t>
+  </si>
+  <si>
+    <t>genetic algorithm;</t>
+  </si>
+  <si>
+    <t>MXNet 1.2</t>
+  </si>
+  <si>
+    <t>MXNet; vDNN; SuperNeurons; TFLMS;</t>
+  </si>
+  <si>
+    <t>[1]Huang C C, Jin G, Li J. Swapadvisor: Pushing deep learning beyond the gpu memory limit via smart swapping[C]//Proceedings of the Twenty-Fifth International Conference on Architectural Support for Programming Languages and Operating Systems. 2020: 1341-1355.</t>
+  </si>
+  <si>
+    <t>huang2020swapadvisor</t>
+  </si>
+  <si>
+    <t>论文博客1：https://blog.csdn.net/qq_43207982/article/details/134211925
+论文博客2：https://zzqq2199.github.io/2021/03/02/SwapAdvisor/</t>
+  </si>
+  <si>
+    <t>HPDC</t>
+  </si>
+  <si>
+    <t>北卡罗来纳大学</t>
+  </si>
+  <si>
+    <t>Efficient GPU Memory Management for Nonlinear DNNs</t>
+  </si>
+  <si>
+    <t>Dymem</t>
+  </si>
+  <si>
+    <t>GPU Memory Management; Resource Management</t>
+  </si>
+  <si>
+    <t>greedy algorithm; graph analysis; depth-first-search; group tensors;</t>
+  </si>
+  <si>
+    <t>vDNN; SuperNeurons;</t>
+  </si>
+  <si>
+    <t>[1]Yang D, Cheng D. Efficient GPU memory management for nonlinear DNNs[C]//Proceedings of the 29th International Symposium on High-Performance Parallel and Distributed Computing. 2020: 185-196.</t>
+  </si>
+  <si>
+    <t>yang2020efficient</t>
+  </si>
+  <si>
+    <t>论文地址：https://dl.acm.org/doi/abs/10.1145/3369583.3392684
+论文博客：https://www.jianshu.com/p/bdba37da7a80</t>
+  </si>
+  <si>
+    <t>Euro-Par</t>
+  </si>
+  <si>
+    <t>Optimal GPU-CPU Offloading Strategies for Deep Neural Network Training</t>
+  </si>
+  <si>
+    <t>Memory management,Deep Neural Network,Dynamic programming,Scheduling</t>
+  </si>
+  <si>
+    <t>vDNN; TFLMS; rotor;</t>
+  </si>
+  <si>
+    <t>[1]Beaumont O, Eyraud-Dubois L, Shilova A. Optimal GPU-CPU offloading strategies for deep neural network training[C]//European Conference on Parallel Processing. Cham: Springer International Publishing, 2020: 151-166.</t>
+  </si>
+  <si>
+    <t>beaumont2020optimal</t>
+  </si>
+  <si>
+    <t>论文地址：https://link.springer.com/chapter/10.1007/978-3-030-57675-2_10</t>
+  </si>
+  <si>
+    <t>FAST</t>
+  </si>
+  <si>
+    <t>FlashNeuron: SSD-Enabled Large-Batch Training of Very Deep Neural Networks</t>
+  </si>
+  <si>
+    <t>FlashNeuron</t>
+  </si>
+  <si>
+    <t>heuristic; linear search;</t>
+  </si>
+  <si>
+    <t>PyTorch 1.2</t>
+  </si>
+  <si>
+    <t>[1]Bae J, Lee J, Jin Y, et al. {FlashNeuron}:{SSD-Enabled}{Large-Batch} training of very deep neural networks[C]//19th USENIX Conference on File and Storage Technologies (FAST 21). 2021: 387-401.</t>
+  </si>
+  <si>
+    <t>bae2021flashneuron</t>
+  </si>
+  <si>
+    <t>论文地址：https://www.usenix.org/conference/fast21/presentation/bae
+代码仓库：https://github.com/SNU-ARC/flashneuron
+论文博客1：https://blog.csdn.net/qq_43207982/article/details/134213871
+论文博客2：https://zhuanlan.zhihu.com/p/378504214</t>
+  </si>
+  <si>
+    <t>HPCA</t>
+  </si>
+  <si>
+    <t>Sentinel: Efficient Tensor Migration and Allocation on Heterogeneous Memory Systems for Deep Learning</t>
+  </si>
+  <si>
+    <t>Sentinel</t>
+  </si>
+  <si>
+    <t>heterogeneous memory, deep neural network training, memory management</t>
+  </si>
+  <si>
+    <t>TensorFlow 1.14</t>
+  </si>
+  <si>
+    <t>TensorFlow; vDNN; AutoTM; Capuchin; SwapAdvisor;</t>
+  </si>
+  <si>
+    <t>[1]Ren J, Luo J, Wu K, et al. Sentinel: Efficient tensor migration and allocation on heterogeneous memory systems for deep learning[C]//2021 IEEE International Symposium on High-Performance Computer Architecture (HPCA). IEEE, 2021: 598-611.</t>
+  </si>
+  <si>
+    <t>ren2021sentinel</t>
+  </si>
+  <si>
+    <t>代码仓库：https://github.com/PASAUCMerced/Sentinel</t>
+  </si>
+  <si>
+    <t>Accelerating Tensor Swapping in GPUs With Self-Tuning Compression</t>
+  </si>
+  <si>
+    <t>CSwap+</t>
+  </si>
+  <si>
+    <t>DNN,GPU,tensor,swapping,compression</t>
+  </si>
+  <si>
+    <t>内存交换;张量压缩;静态;离线;</t>
+  </si>
+  <si>
+    <t>heuristic; compression algorithms;</t>
+  </si>
+  <si>
+    <t>PyTorch; vDNN; vDNN++;</t>
+  </si>
+  <si>
+    <t>[1]Chen P, He S, Zhang X, et al. Accelerating tensor swapping in gpus with self-tuning compression[J]. IEEE Transactions on Parallel and Distributed Systems, 2022, 33(12): 4484-4498.</t>
+  </si>
+  <si>
+    <t>chen2022accelerating</t>
+  </si>
+  <si>
+    <t>代码仓库：https://github.com/ISCS-ZJU/CSWAP</t>
+  </si>
+  <si>
+    <t>An Application-oblivious Memory Scheduling System for DNN Accelerators</t>
+  </si>
+  <si>
+    <t>AppObMem</t>
+  </si>
+  <si>
+    <t>Deep learning, memory scheduling, runtime system, DNN accelerators</t>
+  </si>
+  <si>
+    <t>内存交换;动态;离线;</t>
+  </si>
+  <si>
+    <t>Memory Block</t>
+  </si>
+  <si>
+    <t>memory block;</t>
+  </si>
+  <si>
+    <t>empirical cost model (linear); dynamic programming;</t>
+  </si>
+  <si>
+    <t>Apache Singa</t>
+  </si>
+  <si>
+    <t>Apache Singa; SuperNeurons; TF-LMS;</t>
+  </si>
+  <si>
+    <t>[1]Li J, Wang X, Chen X, et al. An application-oblivious memory scheduling system for DNN accelerators[J]. ACM Transactions on Architecture and Code Optimization (TACO), 2022, 19(4): 1-26.</t>
+  </si>
+  <si>
+    <t>li2022application</t>
+  </si>
+  <si>
+    <t>论文地址：https://dl.acm.org/doi/full/10.1145/3535355</t>
+  </si>
+  <si>
+    <t>利兹大学</t>
+  </si>
+  <si>
+    <t>STRONGHOLD: Fast and Affordable Billion-Scale Deep Learning Model Training</t>
+  </si>
+  <si>
+    <t>STRONGHOLD</t>
+  </si>
+  <si>
+    <t>Deep learning, Distributed training, DNNs training acceleration</t>
+  </si>
+  <si>
+    <t>内存交换;动态;在线;</t>
+  </si>
+  <si>
+    <t>model states;</t>
+  </si>
+  <si>
+    <t>working window; sliding-window;</t>
+  </si>
+  <si>
+    <t>PyTorch 1.10.2</t>
+  </si>
+  <si>
+    <t>PyTorch; Megatron-LM; ZeRO-Offload; ZeRO-Infinity;</t>
+  </si>
+  <si>
+    <t>[1]Sun X, Wang W, Qiu S, et al. Stronghold: fast and affordable billion-scale deep learning model training[C]//SC22: International Conference for High Performance Computing, Networking, Storage and Analysis. IEEE, 2022: 1-17.</t>
+  </si>
+  <si>
+    <t>sun2022stronghold</t>
+  </si>
+  <si>
+    <t>代码仓库：https://github.com/strongh2/sc22-ae</t>
+  </si>
+  <si>
+    <t>DeepUM: Tensor Migration and Prefetching in Unified Memory</t>
+  </si>
+  <si>
+    <t>DeepUM</t>
+  </si>
+  <si>
+    <t>deep learning, neural networks, CUDA, unified memory, data prefetching, runtime system, device driver</t>
+  </si>
+  <si>
+    <t>内存交换;CUDA UM;在线;动态;</t>
+  </si>
+  <si>
+    <t>Page</t>
+  </si>
+  <si>
+    <t>UM block;</t>
+  </si>
+  <si>
+    <t>correlation prefetching;</t>
+  </si>
+  <si>
+    <t>vDNN; LMS; vDNN; AutoTM; SwapAdvisor; Capuchin; Sentinel;</t>
+  </si>
+  <si>
+    <t>[1]Jung J, Kim J, Lee J. Deepum: Tensor migration and prefetching in unified memory[C]//Proceedings of the 28th ACM International Conference on Architectural Support for Programming Languages and Operating Systems, Volume 2. 2023: 207-221.</t>
+  </si>
+  <si>
+    <t>jung2023deepum</t>
+  </si>
+  <si>
+    <t>论文博客1：https://blog.csdn.net/qq_43207982/article/details/134194540
+论文博客2：https://zhuanlan.zhihu.com/p/672931240</t>
+  </si>
+  <si>
+    <t>UIUC（美）</t>
+  </si>
+  <si>
+    <t>G10: Enabling An Efficient Unified GPU Memory and Storage Architecture with Smart Tensor Migrations</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>GPUDirect Storage, Unified Virtual Memory, GPU Memory, Solid State Drives, Deep Learning Compiler</t>
+  </si>
+  <si>
+    <t>内存交换;CUDA UM;离线;动态;</t>
+  </si>
+  <si>
+    <t>dynamic optimization problem; dynamic algorithm;</t>
+  </si>
+  <si>
+    <t>DeepUM; FlashNeuron;</t>
+  </si>
+  <si>
+    <t>[1]Zhang H, Zhou Y, Xue Y, et al. G10: Enabling an efficient unified gpu memory and storage architecture with smart tensor migrations[C]//Proceedings of the 56th Annual IEEE/ACM International Symposium on Microarchitecture. 2023: 395-410.</t>
+  </si>
+  <si>
+    <t>zhang2023g10</t>
+  </si>
+  <si>
+    <t>论文地址1：https://dl.acm.org/doi/abs/10.1145/3613424.3614309
+论文地址2：https://arxiv.org/abs/2310.09443
+代码仓库：https://github.com/platformxlab/g10
+作者主页：https://hieronzhang.github.io/
+论文博客1：https://jianh.web.engr.illinois.edu/g10.html
+论文博客2：https://mp.weixin.qq.com/s/VVDK3IkfFUGhULf7ufzjjg
+论文博客3：https://zhuanlan.zhihu.com/p/668598865</t>
+  </si>
+  <si>
+    <t>威廉与玛丽学院</t>
+  </si>
+  <si>
+    <t>Enabling Large Dynamic Neural Network Training with Learning-based Memory Management</t>
+  </si>
+  <si>
+    <t>DyNN-Offload</t>
+  </si>
+  <si>
+    <t>内存交换;离线;动态;</t>
+  </si>
+  <si>
+    <t>pilot model (a light neural network);</t>
+  </si>
+  <si>
+    <t>PyTorch 1.9</t>
+  </si>
+  <si>
+    <t>PyTorch; DTR; ZeRO-Offload;</t>
+  </si>
+  <si>
+    <t>[1]Ren J, Xu D, Yang S, et al. Enabling Large Dynamic Neural Network Training with Learning-based Memory Management[C]//2024 IEEE International Symposium on High-Performance Computer Architecture (HPCA). IEEE, 2024: 788-802.</t>
+  </si>
+  <si>
+    <t>ren2024enabling</t>
+  </si>
+  <si>
+    <t>关于动态神经网络：https://arxiv.org/abs/2102.04906v4
+上文翻译：https://zhuanlan.zhihu.com/p/354507714</t>
+  </si>
+  <si>
+    <t>武大</t>
+  </si>
+  <si>
+    <t>DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training</t>
+  </si>
+  <si>
+    <t>DeepTM</t>
+  </si>
+  <si>
+    <t>Deep neural network training, heterogeneous memory, memory management, performance optimization.</t>
+  </si>
+  <si>
+    <t>内存交换;静态;离线+在线;</t>
+  </si>
+  <si>
+    <t>deep reinforcement learning;</t>
+  </si>
+  <si>
+    <t>AutoTM; Sentinel;</t>
+  </si>
+  <si>
+    <t>[1]Zhou H, Rang W, Chen H, et al. DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training[J]. IEEE Transactions on Parallel and Distributed Systems, 2024.</t>
+  </si>
+  <si>
+    <t>zhou2024deeptm</t>
+  </si>
+  <si>
+    <t>arXiv:2406.10181</t>
+  </si>
+  <si>
+    <t>CMU（美）</t>
+  </si>
+  <si>
+    <t>Practical offloading for fine-tuning LLM on commodity GPU via learned sparse projectors</t>
+  </si>
+  <si>
+    <t>LSP-Offload</t>
+  </si>
+  <si>
+    <t>Pytorch</t>
+  </si>
+  <si>
+    <t>ZeRO-Offload;</t>
+  </si>
+  <si>
+    <t>[1]Chen S, Guan Z, Liu Y, et al. Practical offloading for fine-tuning LLM on commodity GPU via learned subspace projectors[J]. arXiv preprint arXiv:2406.10181, 2024.</t>
+  </si>
+  <si>
+    <t>chen2024practical</t>
+  </si>
+  <si>
+    <t>论文地址：https://arxiv.org/abs/2406.10181
+代码仓库：https://github.com/gulang2019/LSP-Offload/tree/main</t>
+  </si>
+  <si>
     <t>阿里</t>
   </si>
   <si>
@@ -2872,6 +3127,9 @@
     <t>内存交换;重计算;</t>
   </si>
   <si>
+    <t>TensorFlow r1.2</t>
+  </si>
+  <si>
     <t>[1]Meng C, Sun M, Yang J, et al. Training deeper models by GPU memory optimization on TensorFlow[C]//Proc. of ML Systems Workshop in NIPS. 2017, 7: 26.</t>
   </si>
   <si>
@@ -2894,6 +3152,9 @@
   </si>
   <si>
     <t>Neural Networks, GPU Memory Management, Runtime Scheduling</t>
+  </si>
+  <si>
+    <t>Caffe; MXNet; Torch; TensorFlow;</t>
   </si>
   <si>
     <t>[1]Wang L, Ye J, Zhao Y, et al. Superneurons: Dynamic GPU memory management for training deep neural networks[C]//Proceedings of the 23rd ACM SIGPLAN symposium on principles and practice of parallel programming. 2018: 41-53.</t>
@@ -2916,6 +3177,9 @@
     <t>Convolutional neural network, GPU, memory management</t>
   </si>
   <si>
+    <t>Caffe; MXNet; TensorFlow; vDNN; Layrub; SuperNeurons;</t>
+  </si>
+  <si>
     <t>[1]Jiang W, Ma Y, Liu B, et al. Layup: Layer-adaptive and multi-type intermediate-oriented memory optimization for GPU-based CNNs[J]. ACM Transactions on Architecture and Code Optimization (TACO), 2019, 16(4): 1-23.</t>
   </si>
   <si>
@@ -2936,6 +3200,12 @@
     <t>deep learning training; GPU memory management; tensor access</t>
   </si>
   <si>
+    <t>TensorFlow 1.11</t>
+  </si>
+  <si>
+    <t>TensorFlow; vDNN; Sublinear;</t>
+  </si>
+  <si>
     <t>[1]Peng X, Shi X, Dai H, et al. Capuchin: Tensor-based gpu memory management for deep learning[C]//Proceedings of the Twenty-Fifth International Conference on Architectural Support for Programming Languages and Operating Systems. 2020: 891-905.</t>
   </si>
   <si>
@@ -2963,6 +3233,9 @@
     <t>DNN, GPU, recomputation, swapping, tensor</t>
   </si>
   <si>
+    <t>PyTorch; vDNN; SuperNeurons; Capuchin;</t>
+  </si>
+  <si>
     <t>[1]He S, Chen P, Chen S, et al. Home: A holistic gpu memory management framework for deep learning[J]. IEEE Transactions on Computers, 2022, 72(3): 826-838.</t>
   </si>
   <si>
@@ -2984,6 +3257,12 @@
     <t>内存交换;重计算;内存分配;</t>
   </si>
   <si>
+    <t>MegEngine 1.7</t>
+  </si>
+  <si>
+    <t>MegEngine; Sublinear; Capuchin; DTR;</t>
+  </si>
+  <si>
     <t>[1]Hu Z, Xiao J, Deng Z, et al. MegTaiChi: Dynamic tensor-based memory management optimization for DNN training[C]//Proceedings of the 36th ACM International Conference on Supercomputing. 2022: 1-13.</t>
   </si>
   <si>
@@ -3008,6 +3287,12 @@
     <t>DB4AI, GPU memory schedule</t>
   </si>
   <si>
+    <t>tinyflow</t>
+  </si>
+  <si>
+    <t>tinyflow; vDNN; Capuchin;</t>
+  </si>
+  <si>
     <t>[1]Zhang K, Wang H, Hu H, et al. TENSILE: A tensor granularity dynamic GPU memory scheduling method toward multiple dynamic workloads system[J]. IEEE Transactions on Knowledge and Data Engineering, 2022, 35(8): 8630-8643.</t>
   </si>
   <si>
@@ -3027,6 +3312,9 @@
   </si>
   <si>
     <t>Deep Learning System, Memory Management, Large Model Support.</t>
+  </si>
+  <si>
+    <t>PyTorch; vDNN; Sublinear; SuperNeurons; ZeRO-Offload;</t>
   </si>
   <si>
     <t>[1]Nie X, Miao X, Yang Z, et al. Tsplit: Fine-grained gpu memory management for efficient dnn training via tensor splitting[C]//2022 IEEE 38th International Conference on Data Engineering (ICDE). IEEE, 2022: 2615-2628.</t>
@@ -3043,6 +3331,9 @@
   </si>
   <si>
     <t>POET</t>
+  </si>
+  <si>
+    <t>PyTorch; Sublinear; Checkmate; DTR;</t>
   </si>
   <si>
     <t>[1]Patil S G, Jain P, Dutta P, et al. POET: Training neural networks on tiny devices with integrated rematerialization and paging[C]//International Conference on Machine Learning. PMLR, 2022: 17573-17583.</t>
@@ -3066,6 +3357,12 @@
     <t>DNN training, offload memory, recomputation, rematerialization, swap.</t>
   </si>
   <si>
+    <t>TensorFlow 1.15.2</t>
+  </si>
+  <si>
+    <t>TensorFlow; Sublinear; Checkmate; Capuchin;</t>
+  </si>
+  <si>
     <t>[1]Zong Z, Lin L, Lin L, et al. STR: Hybrid tensor re-generation to break memory wall for DNN training[J]. IEEE Transactions on Parallel and Distributed Systems, 2023, 34(8): 2403-2418.</t>
   </si>
   <si>
@@ -3100,6 +3397,9 @@
   </si>
   <si>
     <t>Dynamic tensor recomputation and swapping, Knapsack Problem, bidirectional prefetching, GPU memory management</t>
+  </si>
+  <si>
+    <t>PyTorch; vDNN; SuperNeurons; Capuchin; DTR; POET;</t>
   </si>
   <si>
     <t>[1]Tang Y, Li Q, Yin L, et al. DELTA: Memory-Efficient Training via Dynamic Fine-Grained Recomputation and Swapping[J]. ACM Transactions on Architecture and Code Optimization, 2024, 21(4): 1-25.</t>
@@ -3125,6 +3425,9 @@
     <t>DNN training, GPUmemory management, Training throughput, Performance improvement</t>
   </si>
   <si>
+    <t>vDNN; SuperNeurons; SwapAdviser; HOME;</t>
+  </si>
+  <si>
     <t>[1]Chen W, Dong X, Zhang F, et al. ATP: Achieving Throughput Peak for DNN Training via Smart GPU Memory Management[J]. ACM Transactions on Architecture and Code Optimization, 2024.</t>
   </si>
   <si>
@@ -3141,6 +3444,12 @@
     <t>MAGIS</t>
   </si>
   <si>
+    <t>PyTorch 2.1.0</t>
+  </si>
+  <si>
+    <t>PyTorch; TensorFlow; DTR;</t>
+  </si>
+  <si>
     <t>[1]Chen R, Ding Z, Zheng S, et al. Magis: Memory optimization via coordinated graph transformation and scheduling for dnn[C]//Proceedings of the 29th ACM International Conference on Architectural Support for Programming Languages and Operating Systems, Volume 3. 2024: 607-621.</t>
   </si>
   <si>
@@ -3162,6 +3471,12 @@
     <t>Large Language Model, Long Context Training, Tensor Management, Data Rematerialization</t>
   </si>
   <si>
+    <t>PyTorch 2.0</t>
+  </si>
+  <si>
+    <t>Megatron-LM; DeepSpeed;</t>
+  </si>
+  <si>
     <t>[1]Zhao P, Zhang H, Fu F, et al. MEMO: Fine-grained Tensor Management For Ultra-long Context LLM Training[J]. Proceedings of the ACM on Management of Data, 2025, 3(1): 1-28.</t>
   </si>
   <si>
@@ -3175,6 +3490,12 @@
   </si>
   <si>
     <t>LoHan</t>
+  </si>
+  <si>
+    <t>PyTorch 2.0.0</t>
+  </si>
+  <si>
+    <t>ZeRO-Infinity; ZeRO-Offload; Colossal-AI; FlashNeuron;</t>
   </si>
   <si>
     <t>[1]Liao C, Sun M, Yang Z, et al. LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU[J]. arXiv preprint arXiv:2403.06504, 2024.</t>
@@ -3216,6 +3537,9 @@
     <t>Coop</t>
   </si>
   <si>
+    <t>OneFlow; DTR; MegTaiChi</t>
+  </si>
+  <si>
     <t>[1]Zhang J, Ma S, Liu P, et al. Coop: Memory is not a Commodity[J]. Advances in Neural Information Processing Systems, 2023, 36: 49870-49882.</t>
   </si>
   <si>
@@ -3260,6 +3584,9 @@
     <t>Deep Learning System, Memory Optimization, Large Model Support, Memory Efficiency</t>
   </si>
   <si>
+    <t>PyTorch 1.13.1</t>
+  </si>
+  <si>
     <t>[1]Shu H, Wang A, Shi Z, et al. ROAM: memory-efficient large DNN training via optimized operator ordering and memory layout[J]. arXiv preprint arXiv:2310.19295, 2023.</t>
   </si>
   <si>
@@ -3279,6 +3606,9 @@
   </si>
   <si>
     <t>Memory Defragmentation, GPU, Deep Learning, Virtual Memory Stitching</t>
+  </si>
+  <si>
+    <t>PyTorch; Deepspeed; Colossal-AI; FSDP;</t>
   </si>
   <si>
     <t>[1]Guo C, Zhang R, Xu J, et al. Gmlake: Efficient and transparent gpu memory defragmentation for large-scale dnn training with virtual memory stitching[C]//Proceedings of the 29th ACM International Conference on Architectural Support for Programming Languages and Operating Systems, Volume 2. 2024: 450-466.</t>
@@ -4463,10 +4793,10 @@
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2049" name="Host Control  1" hidden="1">
+            <xdr:cNvPr id="4097" name="Host Control  1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2049"/>
+                  <a14:compatExt spid="_x0000_s4097"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -4509,10 +4839,10 @@
         </xdr:to>
         <xdr:sp>
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4097" name="Host Control  1" hidden="1">
+            <xdr:cNvPr id="2049" name="Host Control  1" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s4097"/>
+                  <a14:compatExt spid="_x0000_s2049"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -8430,1311 +8760,6 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
-    <col min="2" max="3" width="10.7777777777778" style="1" customWidth="1"/>
-    <col min="4" max="5" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="14" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="15" max="17" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.77777777777778" style="1" customWidth="1"/>
-    <col min="19" max="20" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.88888888888889" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:20">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1" spans="1:20">
-      <c r="A2" s="4">
-        <f t="shared" ref="A2:A24" si="0">ROW()-1</f>
-        <v>1</v>
-      </c>
-      <c r="B2" s="4">
-        <v>2016</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4">
-        <v>540</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="Q2" s="4" t="str">
-        <f t="shared" ref="Q2:Q24" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
-        <v>2016_MICRO_A会_vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design</v>
-      </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:20">
-      <c r="A3" s="4">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2018</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4">
-        <v>42</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="Q3" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>2018_HiPC_C会_OC-DNN: Exploiting Advanced Unified Memory Capabilities in CUDA 9 and Volta GPUs for Out-of-Core DNN Training</v>
-      </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:20">
-      <c r="A4" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2018</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3">
-        <v>19</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="Q4" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2018_TPDS_A刊_moDNN: Memory Optimal Deep Neural Network Training on Graphics Processing Units</v>
-      </c>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:20">
-      <c r="A5" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" s="3">
-        <v>2018</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3">
-        <v>53</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="Q5" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2018_TACO_A刊_Layer-Centric Memory Reuse and Data Migration for Extreme-Scale Deep Learning on Many-Core Architectures</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:20">
-      <c r="A6" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" s="3">
-        <v>2019</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3">
-        <v>15</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="Q6" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2019_ICCD_B会_AccUDNN: A GPU Memory Efficient Accelerator for Training Ultra-Deep Neural Networks</v>
-      </c>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:20">
-      <c r="A7" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="3">
-        <v>2019</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3">
-        <v>22</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="Q7" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2019_ISMM_内存领域_Automatic GPU memory management for large neural models in TensorFlow</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="T7" s="3"/>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:20">
-      <c r="A8" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="3">
-        <v>2019</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3">
-        <v>58</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="Q8" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2019_IPDPS_B会_Dynamic Memory Management for GPU-Based Training of Deep Neural Networks</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:20">
-      <c r="A9" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="3">
-        <v>2019</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3">
-        <v>57</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="Q9" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2019_arXiv:1903.06631_v1_Efficient Memory Management for GPU-based Deep Learning Systems</v>
-      </c>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:20">
-      <c r="A10" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="3">
-        <v>2019</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3">
-        <v>10</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q10" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2019_TC_A刊_Hotness- and Lifetime-Aware Data Placement and Migration for High-Performance Deep Learning on Heterogeneous Memory Systems</v>
-      </c>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:20">
-      <c r="A11" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="3">
-        <v>2020</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3">
-        <v>86</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="Q11" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2020_ASPLOS_A会_AutoTM: Automatic Tensor Movement in Heterogeneous Memory Systems using Integer Linear Programming</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:20">
-      <c r="A12" s="4">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="4">
-        <v>2020</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4">
-        <v>214</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="Q12" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v>2020_ASPLOS_A会_SwapAdvisor: Pushing Deep Learning Beyond the GPU Memory Limit via Smart Swapping</v>
-      </c>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:20">
-      <c r="A13" s="3">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="3">
-        <v>2020</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3">
-        <v>15</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="Q13" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2020_HPDC_B会_Efficient GPU Memory Management for Nonlinear DNNs</v>
-      </c>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:20">
-      <c r="A14" s="3">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="3">
-        <v>2020</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3">
-        <v>27</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="Q14" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2020_Euro-Par_B会_Optimal GPU-CPU Offloading Strategies for Deep Neural Network Training</v>
-      </c>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:20">
-      <c r="A15" s="3">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="3">
-        <v>2021</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3">
-        <v>58</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q15" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2021_FAST_A会_FlashNeuron: SSD-Enabled Large-Batch Training of Very Deep Neural Networks</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:20">
-      <c r="A16" s="3">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="3">
-        <v>2021</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3">
-        <v>75</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q16" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2021_HPCA_A会_Sentinel: Efficient Tensor Migration and Allocation on Heterogeneous Memory Systems for Deep Learning</v>
-      </c>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:20">
-      <c r="A17" s="3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" s="3">
-        <v>2022</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3">
-        <v>4</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="Q17" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2022_TPDS_A刊_Accelerating Tensor Swapping in GPUs With Self-Tuning Compression</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="T17" s="3"/>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:20">
-      <c r="A18" s="3">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="3">
-        <v>2022</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3">
-        <v>3</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="Q18" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2022_TACO_A刊_An Application-oblivious Memory Scheduling System for DNN Accelerators</v>
-      </c>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="T18" s="3"/>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:20">
-      <c r="A19" s="3">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19" s="3">
-        <v>2022</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3">
-        <v>18</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="Q19" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2022_SC_A会_STRONGHOLD: Fast and Affordable Billion-Scale Deep Learning Model Training</v>
-      </c>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:20">
-      <c r="A20" s="3">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B20" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3">
-        <v>25</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="Q20" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2023_ASPLOS_A会_DeepUM: Tensor Migration and Prefetching in Unified Memory</v>
-      </c>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-    </row>
-    <row r="21" ht="36" customHeight="1" spans="1:20">
-      <c r="A21" s="3">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B21" s="3">
-        <v>2023</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3">
-        <v>18</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="Q21" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2023_MICRO_A会_G10: Enabling An Efficient Unified GPU Memory and Storage Architecture with Smart Tensor Migrations</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="T21" s="3"/>
-    </row>
-    <row r="22" ht="36" customHeight="1" spans="1:20">
-      <c r="A22" s="3">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B22" s="3">
-        <v>2024</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="Q22" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_HPCA_A会_Enabling Large Dynamic Neural Network Training with Learning-based Memory Management</v>
-      </c>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="T22" s="3"/>
-    </row>
-    <row r="23" ht="36" customHeight="1" spans="1:20">
-      <c r="A23" s="3">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B23" s="3">
-        <v>2024</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3">
-        <v>1</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="Q23" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2024_TPDS_A刊_DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training</v>
-      </c>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="3"/>
-    </row>
-    <row r="24" ht="36" customHeight="1" spans="1:20">
-      <c r="A24" s="3">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B24" s="3">
-        <v>2025</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="Q24" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2025_arXiv:2406.10181_v2_Practical offloading for fine-tuning LLM on commodity GPU via learned sparse projectors</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="T24" s="3"/>
-    </row>
-  </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T24" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:T24">
-      <sortCondition ref="B1"/>
-    </sortState>
-    <extLst/>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="41" orientation="landscape"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
-  <controls>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice Requires="x14">
-        <control shapeId="2049" r:id="rId3">
-          <controlPr defaultSize="0">
-            <anchor moveWithCells="1">
-              <from>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>0</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>0</xdr:rowOff>
-              </from>
-              <to>
-                <xdr:col>3</xdr:col>
-                <xdr:colOff>537845</xdr:colOff>
-                <xdr:row>1</xdr:row>
-                <xdr:rowOff>182880</xdr:rowOff>
-              </to>
-            </anchor>
-          </controlPr>
-        </control>
-      </mc:Choice>
-      <mc:Fallback>
-        <control shapeId="2049" r:id="rId3"/>
-      </mc:Fallback>
-    </mc:AlternateContent>
-  </controls>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:U19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
@@ -9783,16 +8808,16 @@
         <v>569</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>729</v>
+        <v>570</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>111</v>
@@ -9807,7 +8832,7 @@
         <v>11</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>112</v>
@@ -9828,57 +8853,57 @@
         <v>141</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>730</v>
+        <v>575</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>369</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>731</v>
+        <v>576</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>732</v>
+        <v>577</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>733</v>
+        <v>578</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>735</v>
+        <v>580</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>736</v>
+        <v>581</v>
       </c>
       <c r="M2" s="4" t="s">
         <v>371</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>737</v>
+        <v>582</v>
       </c>
       <c r="O2" s="4">
         <v>1122</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>738</v>
+        <v>583</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>739</v>
+        <v>584</v>
       </c>
       <c r="R2" s="4" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2016_arXiv:1604.06174_v2_Training Deep Nets with Sublinear Memory Cost</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>740</v>
+        <v>586</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>741</v>
+        <v>587</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:21">
@@ -9899,38 +8924,38 @@
         <v>376</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>742</v>
+        <v>588</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>743</v>
+        <v>589</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>733</v>
+        <v>578</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>744</v>
+        <v>590</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>745</v>
+        <v>591</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>746</v>
+        <v>592</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>747</v>
+        <v>593</v>
       </c>
       <c r="O3" s="3">
         <v>250</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>748</v>
+        <v>594</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>749</v>
+        <v>595</v>
       </c>
       <c r="R3" s="3" t="str">
         <f>B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
@@ -9938,7 +8963,7 @@
       </c>
       <c r="S3" s="3"/>
       <c r="T3" s="3" t="s">
-        <v>750</v>
+        <v>596</v>
       </c>
       <c r="U3" s="3"/>
     </row>
@@ -9960,38 +8985,38 @@
         <v>376</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>751</v>
+        <v>597</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>752</v>
+        <v>598</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>753</v>
+        <v>599</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>754</v>
+        <v>600</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>755</v>
+        <v>601</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>378</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>756</v>
+        <v>602</v>
       </c>
       <c r="O4" s="3">
         <v>65</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>757</v>
+        <v>603</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>758</v>
+        <v>604</v>
       </c>
       <c r="R4" s="3" t="str">
         <f>B4&amp;"_"&amp;D4&amp;"_"&amp;C4&amp;"_"&amp;F4&amp;""</f>
@@ -9999,7 +9024,7 @@
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>759</v>
+        <v>605</v>
       </c>
       <c r="U4" s="3"/>
     </row>
@@ -10018,49 +9043,49 @@
         <v>159</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>760</v>
+        <v>606</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>761</v>
+        <v>607</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>753</v>
+        <v>599</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>762</v>
+        <v>608</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>745</v>
+        <v>591</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>763</v>
+        <v>609</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>764</v>
+        <v>610</v>
       </c>
       <c r="O5" s="3">
         <v>49</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>765</v>
+        <v>611</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>766</v>
+        <v>612</v>
       </c>
       <c r="R5" s="3" t="str">
         <f>B5&amp;"_"&amp;D5&amp;"_"&amp;C5&amp;"_"&amp;F5&amp;""</f>
         <v>2019_NeurIPS_A会_A Graph Theoretic Framework of Recomputation Algorithms for Memory-Efficient Backpropagation</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>767</v>
+        <v>613</v>
       </c>
       <c r="U5" s="3"/>
     </row>
@@ -10076,22 +9101,22 @@
         <v>113</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>768</v>
+        <v>614</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>662</v>
+        <v>615</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>769</v>
+        <v>616</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>770</v>
+        <v>617</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>771</v>
+        <v>618</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>772</v>
+        <v>619</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="3"/>
@@ -10102,20 +9127,20 @@
         <v>35</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>773</v>
+        <v>620</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>774</v>
+        <v>621</v>
       </c>
       <c r="R6" s="5" t="str">
         <f t="shared" ref="R6:R19" si="1">B6&amp;"_"&amp;D6&amp;"_"&amp;C6&amp;"_"&amp;F6&amp;""</f>
         <v>2019_arXiv:1911.13214_v1_Optimal checkpointing for heterogeneous chains: how to train deep neural networks with limited memory</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>775</v>
+        <v>622</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>158</v>
@@ -10133,57 +9158,57 @@
         <v>472</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>776</v>
+        <v>623</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>777</v>
+        <v>624</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>778</v>
+        <v>625</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>779</v>
+        <v>626</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>780</v>
+        <v>627</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>781</v>
+        <v>628</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>782</v>
+        <v>629</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>783</v>
+        <v>630</v>
       </c>
       <c r="O7" s="4">
         <v>208</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>784</v>
+        <v>631</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>785</v>
+        <v>632</v>
       </c>
       <c r="R7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2020_MLSys_顶会_Checkmate: Breaking the Memory Wall with Optimal Tensor Rematerialization</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>786</v>
+        <v>633</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>580</v>
+        <v>634</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:21">
@@ -10198,56 +9223,56 @@
         <v>150</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>787</v>
+        <v>635</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>465</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>788</v>
+        <v>636</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>789</v>
+        <v>637</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>790</v>
+        <v>638</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>733</v>
+        <v>578</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>791</v>
+        <v>639</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>792</v>
+        <v>640</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>793</v>
+        <v>641</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>794</v>
+        <v>642</v>
       </c>
       <c r="O8" s="3">
         <v>40</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>795</v>
+        <v>643</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>796</v>
+        <v>644</v>
       </c>
       <c r="R8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_ISCA_A会_Echo: Compiler-based GPU Memory Footprint Reduction for LSTM RNN Training</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>797</v>
+        <v>645</v>
       </c>
       <c r="U8" s="3"/>
     </row>
@@ -10266,51 +9291,51 @@
         <v>473</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>798</v>
+        <v>646</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>799</v>
+        <v>647</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>800</v>
+        <v>648</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>779</v>
+        <v>626</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>801</v>
+        <v>649</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>802</v>
+        <v>650</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>803</v>
+        <v>651</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>804</v>
+        <v>652</v>
       </c>
       <c r="O9" s="3">
         <v>29</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>805</v>
+        <v>653</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>806</v>
+        <v>654</v>
       </c>
       <c r="R9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_ICLR_顶会_Memory Optimization for Deep Networks</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>807</v>
+        <v>655</v>
       </c>
       <c r="U9" s="3"/>
     </row>
@@ -10332,51 +9357,51 @@
         <v>369</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>808</v>
+        <v>656</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>809</v>
+        <v>657</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
-        <v>810</v>
+        <v>658</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>811</v>
+        <v>659</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>801</v>
+        <v>649</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>812</v>
+        <v>660</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>813</v>
+        <v>661</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>814</v>
+        <v>662</v>
       </c>
       <c r="O10" s="4">
         <v>95</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>815</v>
+        <v>663</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>816</v>
+        <v>664</v>
       </c>
       <c r="R10" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2021_ICLR_顶会_Dynamic Tensor Rematerialization</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>817</v>
+        <v>665</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>580</v>
+        <v>634</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:21">
@@ -10394,51 +9419,51 @@
         <v>480</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>818</v>
+        <v>666</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>819</v>
+        <v>667</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>820</v>
+        <v>668</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>753</v>
+        <v>599</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>821</v>
+        <v>669</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>822</v>
+        <v>670</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>823</v>
+        <v>671</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>824</v>
+        <v>672</v>
       </c>
       <c r="O11" s="3">
         <v>33</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>825</v>
+        <v>673</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>826</v>
+        <v>674</v>
       </c>
       <c r="R11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_CVPR_A会_Optimal Gradient Checkpoint Search for Arbitrary Computation Graphs</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>827</v>
+        <v>675</v>
       </c>
       <c r="U11" s="3"/>
     </row>
@@ -10460,48 +9485,48 @@
         <v>465</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>828</v>
+        <v>676</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>829</v>
+        <v>677</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>810</v>
+        <v>658</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>830</v>
+        <v>678</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>831</v>
+        <v>679</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>384</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>824</v>
+        <v>672</v>
       </c>
       <c r="O12" s="3">
         <v>7</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>832</v>
+        <v>680</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>833</v>
+        <v>681</v>
       </c>
       <c r="R12" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_NeurIPS_A会_Tempo: Accelerating Transformer-Based Model Training through Memory Footprint Reduction</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>834</v>
+        <v>682</v>
       </c>
       <c r="U12" s="3"/>
     </row>
@@ -10517,56 +9542,56 @@
         <v>450</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>835</v>
+        <v>683</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>836</v>
+        <v>684</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>837</v>
+        <v>685</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>838</v>
+        <v>686</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>839</v>
+        <v>687</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>840</v>
+        <v>688</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>811</v>
+        <v>659</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>841</v>
+        <v>689</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>842</v>
+        <v>690</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>843</v>
+        <v>691</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>844</v>
+        <v>692</v>
       </c>
       <c r="O13" s="3">
         <v>58</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>845</v>
+        <v>693</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>846</v>
+        <v>694</v>
       </c>
       <c r="R13" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_MobiSys_B会_Melon: breaking the memory wall for resource-efficient on-device machine learning</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>847</v>
+        <v>695</v>
       </c>
       <c r="U13" s="3"/>
     </row>
@@ -10582,56 +9607,56 @@
         <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>594</v>
+        <v>696</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>848</v>
+        <v>697</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>849</v>
+        <v>698</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>850</v>
+        <v>699</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>851</v>
+        <v>700</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>733</v>
+        <v>578</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>811</v>
+        <v>659</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>852</v>
+        <v>701</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>853</v>
+        <v>702</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>854</v>
+        <v>703</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>855</v>
+        <v>704</v>
       </c>
       <c r="O14" s="3">
         <v>4</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>856</v>
+        <v>705</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>857</v>
+        <v>706</v>
       </c>
       <c r="R14" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_TACO_A刊_XEngine: Optimal Tensor Rematerialization for Neural Networks in Heterogeneous Environments</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>858</v>
+        <v>707</v>
       </c>
       <c r="U14" s="3"/>
     </row>
@@ -10647,56 +9672,56 @@
         <v>450</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>618</v>
+        <v>708</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>859</v>
+        <v>709</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>860</v>
+        <v>710</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>861</v>
+        <v>711</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>862</v>
+        <v>712</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>863</v>
+        <v>713</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>762</v>
+        <v>608</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>864</v>
+        <v>714</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>865</v>
+        <v>715</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>866</v>
+        <v>716</v>
       </c>
       <c r="O15" s="3">
         <v>1</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>867</v>
+        <v>717</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>868</v>
+        <v>718</v>
       </c>
       <c r="R15" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_IPDPS_B会_Exploiting Input Tensor Dynamics in Activation Checkpointing for Efficient Training on GPU</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>869</v>
+        <v>719</v>
       </c>
       <c r="U15" s="3"/>
     </row>
@@ -10715,51 +9740,51 @@
         <v>549</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>870</v>
+        <v>720</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>871</v>
+        <v>721</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>872</v>
+        <v>722</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>733</v>
+        <v>578</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>873</v>
+        <v>723</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>874</v>
+        <v>724</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>875</v>
+        <v>725</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>876</v>
+        <v>726</v>
       </c>
       <c r="O16" s="3">
         <v>3</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>877</v>
+        <v>727</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>878</v>
+        <v>728</v>
       </c>
       <c r="R16" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_Moccasin: Efficient Tensor Rematerialization for Neural Networks</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>879</v>
+        <v>729</v>
       </c>
       <c r="U16" s="3"/>
     </row>
@@ -10775,42 +9800,42 @@
         <v>472</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>776</v>
+        <v>623</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>382</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>880</v>
+        <v>730</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>881</v>
+        <v>731</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>852</v>
+        <v>701</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>882</v>
+        <v>732</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>384</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>883</v>
+        <v>733</v>
       </c>
       <c r="O17" s="3">
         <v>4</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>884</v>
+        <v>734</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>885</v>
+        <v>735</v>
       </c>
       <c r="R17" s="3" t="str">
         <f t="shared" si="1"/>
@@ -10818,7 +9843,7 @@
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="3" t="s">
-        <v>886</v>
+        <v>736</v>
       </c>
       <c r="U17" s="3"/>
     </row>
@@ -10837,47 +9862,47 @@
         <v>549</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>662</v>
+        <v>615</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>887</v>
+        <v>737</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>888</v>
+        <v>738</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
-        <v>772</v>
+        <v>619</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="s">
-        <v>889</v>
+        <v>739</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>890</v>
+        <v>740</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>891</v>
+        <v>741</v>
       </c>
       <c r="O18" s="5">
         <v>3</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>892</v>
+        <v>742</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>893</v>
+        <v>743</v>
       </c>
       <c r="R18" s="5" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_Rockmate: an Efficient, Fast, Automatic and Generic Tool for Re-materialization in PyTorch</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>894</v>
+        <v>744</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>158</v>
@@ -10895,54 +9920,54 @@
         <v>218</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>895</v>
+        <v>745</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>896</v>
+        <v>746</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>897</v>
+        <v>747</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>898</v>
+        <v>748</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>733</v>
+        <v>578</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>734</v>
+        <v>579</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>899</v>
+        <v>749</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>745</v>
+        <v>591</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>384</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>900</v>
+        <v>750</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>901</v>
+        <v>751</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>902</v>
+        <v>752</v>
       </c>
       <c r="R19" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2025_JPDC_B刊_GPU memory usage optimization for backward propagation in deep network training</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>903</v>
+        <v>753</v>
       </c>
       <c r="U19" s="3"/>
     </row>
@@ -10988,6 +10013,1569 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:U24"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
+    <col min="2" max="3" width="10.7777777777778" style="1" customWidth="1"/>
+    <col min="4" max="5" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="9" max="15" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="16" max="18" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77777777777778" style="1" customWidth="1"/>
+    <col min="20" max="21" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88888888888889" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:21">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1" spans="1:21">
+      <c r="A2" s="4">
+        <f t="shared" ref="A2:A24" si="0">ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="4">
+        <v>2016</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="O2" s="4">
+        <v>540</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="R2" s="4" t="str">
+        <f t="shared" ref="R2:R24" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+        <v>2016_MICRO_A会_vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design</v>
+      </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:21">
+      <c r="A3" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2018</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="O3" s="4">
+        <v>42</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="R3" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>2018_HiPC_C会_OC-DNN: Exploiting Advanced Unified Memory Capabilities in CUDA 9 and Volta GPUs for Out-of-Core DNN Training</v>
+      </c>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:21">
+      <c r="A4" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>777</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="O4" s="3">
+        <v>19</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="R4" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2018_TPDS_A刊_moDNN: Memory Optimal Deep Neural Network Training on Graphics Processing Units</v>
+      </c>
+      <c r="S4" s="3"/>
+      <c r="T4" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="U4" s="3"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:21">
+      <c r="A5" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2018</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="O5" s="3">
+        <v>53</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="R5" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2018_TACO_A刊_Layer-Centric Memory Reuse and Data Migration for Extreme-Scale Deep Learning on Many-Core Architectures</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="U5" s="3"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:21">
+      <c r="A6" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="O6" s="3">
+        <v>15</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="R6" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2019_ICCD_B会_AccUDNN: A GPU Memory Efficient Accelerator for Training Ultra-Deep Neural Networks</v>
+      </c>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="U6" s="3"/>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:21">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="O7" s="3">
+        <v>22</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="R7" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2019_ISMM_内存领域_Automatic GPU memory management for large neural models in TensorFlow</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="U7" s="3"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:21">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="O8" s="3">
+        <v>58</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="R8" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2019_IPDPS_B会_Dynamic Memory Management for GPU-Based Training of Deep Neural Networks</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="U8" s="3"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:21">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2019</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="O9" s="3">
+        <v>57</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="R9" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2019_arXiv:1903.06631_v1_Efficient Memory Management for GPU-based Deep Learning Systems</v>
+      </c>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="U9" s="3"/>
+    </row>
+    <row r="10" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A10" s="5">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2019</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5">
+        <v>10</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="R10" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>2019_TC_A刊_Hotness- and Lifetime-Aware Data Placement and Migration for High-Performance Deep Learning on Heterogeneous Memory Systems</v>
+      </c>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:21">
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>757</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="O11" s="3">
+        <v>86</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="R11" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2020_ASPLOS_A会_AutoTM: Automatic Tensor Movement in Heterogeneous Memory Systems using Integer Linear Programming</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:21">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2020</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="N12" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="O12" s="4">
+        <v>214</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="R12" s="4" t="str">
+        <f t="shared" si="1"/>
+        <v>2020_ASPLOS_A会_SwapAdvisor: Pushing Deep Learning Beyond the GPU Memory Limit via Smart Swapping</v>
+      </c>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:21">
+      <c r="A13" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="3">
+        <v>2020</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="O13" s="3">
+        <v>15</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="R13" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2020_HPDC_B会_Efficient GPU Memory Management for Nonlinear DNNs</v>
+      </c>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="U13" s="3"/>
+    </row>
+    <row r="14" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A14" s="5">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2020</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="O14" s="5">
+        <v>27</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>882</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>883</v>
+      </c>
+      <c r="R14" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>2020_Euro-Par_B会_Optimal GPU-CPU Offloading Strategies for Deep Neural Network Training</v>
+      </c>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5" t="s">
+        <v>884</v>
+      </c>
+      <c r="U14" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:21">
+      <c r="A15" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
+        <v>2021</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="O15" s="3">
+        <v>58</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="R15" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2021_FAST_A会_FlashNeuron: SSD-Enabled Large-Batch Training of Very Deep Neural Networks</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="U15" s="3"/>
+    </row>
+    <row r="16" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A16" s="5">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2021</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>893</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="O16" s="5">
+        <v>75</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="R16" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>2021_HPCA_A会_Sentinel: Efficient Tensor Migration and Allocation on Heterogeneous Memory Systems for Deep Learning</v>
+      </c>
+      <c r="S16" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="T16" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="U16" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" spans="1:21">
+      <c r="A17" s="3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="O17" s="3">
+        <v>4</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="R17" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2022_TPDS_A刊_Accelerating Tensor Swapping in GPUs With Self-Tuning Compression</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="U17" s="3"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:21">
+      <c r="A18" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="O18" s="3">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="R18" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2022_TACO_A刊_An Application-oblivious Memory Scheduling System for DNN Accelerators</v>
+      </c>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="U18" s="3"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:21">
+      <c r="A19" s="3">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="O19" s="3">
+        <v>18</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="R19" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2022_SC_A会_STRONGHOLD: Fast and Affordable Billion-Scale Deep Learning Model Training</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="T19" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:21">
+      <c r="A20" s="3">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="O20" s="3">
+        <v>25</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="R20" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2023_ASPLOS_A会_DeepUM: Tensor Migration and Prefetching in Unified Memory</v>
+      </c>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="U20" s="3"/>
+    </row>
+    <row r="21" ht="36" customHeight="1" spans="1:21">
+      <c r="A21" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="O21" s="3">
+        <v>18</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>953</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="R21" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2023_MICRO_A会_G10: Enabling An Efficient Unified GPU Memory and Storage Architecture with Smart Tensor Migrations</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="U21" s="3"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" spans="1:21">
+      <c r="A22" s="3">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="O22" s="3">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="R22" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2024_HPCA_A会_Enabling Large Dynamic Neural Network Training with Learning-based Memory Management</v>
+      </c>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="U22" s="3"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" spans="1:21">
+      <c r="A23" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="O23" s="3">
+        <v>1</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="R23" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>2024_TPDS_A刊_DeepTM: Efficient Tensor Management in Heterogeneous Memory for DNN Training</v>
+      </c>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+    </row>
+    <row r="24" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A24" s="5">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>975</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>977</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>978</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5" t="s">
+        <v>979</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>980</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="P24" s="5" t="s">
+        <v>981</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>982</v>
+      </c>
+      <c r="R24" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>2025_arXiv:2406.10181_v2_Practical offloading for fine-tuning LLM on commodity GPU via learned sparse projectors</v>
+      </c>
+      <c r="S24" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="T24" s="5" t="s">
+        <v>983</v>
+      </c>
+      <c r="U24" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U24" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:U24">
+      <sortCondition ref="B1"/>
+    </sortState>
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="39" orientation="landscape"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="2049" r:id="rId3">
+          <controlPr defaultSize="0">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>0</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>537845</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>182880</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="2049" r:id="rId3"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
@@ -11041,13 +11629,13 @@
         <v>569</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>111</v>
@@ -11062,7 +11650,7 @@
         <v>11</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>112</v>
@@ -11086,28 +11674,32 @@
         <v>159</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>904</v>
+        <v>984</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>905</v>
+        <v>985</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="L2" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>378</v>
+      </c>
       <c r="N2" s="3">
         <v>105</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>907</v>
+        <v>988</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>908</v>
+        <v>989</v>
       </c>
       <c r="Q2" s="3" t="str">
         <f t="shared" ref="Q2:Q18" si="0">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
@@ -11115,7 +11707,7 @@
       </c>
       <c r="R2" s="3"/>
       <c r="S2" s="3" t="s">
-        <v>909</v>
+        <v>990</v>
       </c>
       <c r="T2" s="3"/>
     </row>
@@ -11131,48 +11723,52 @@
         <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>910</v>
+        <v>991</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>911</v>
+        <v>992</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>912</v>
+        <v>993</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>913</v>
+        <v>994</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>914</v>
+        <v>995</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
+      <c r="L3" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>996</v>
+      </c>
       <c r="N3" s="4">
         <v>322</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>915</v>
+        <v>997</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>916</v>
+        <v>998</v>
       </c>
       <c r="Q3" s="4" t="str">
         <f t="shared" si="0"/>
         <v>2018_PPoPP_A会_Superneurons: dynamic GPU memory management for training deep neural networks</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>917</v>
+        <v>999</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>580</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:20">
@@ -11187,45 +11783,49 @@
         <v>204</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>594</v>
+        <v>696</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>124</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>918</v>
+        <v>1000</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>919</v>
+        <v>1001</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>920</v>
+        <v>1002</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="L4" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>1003</v>
+      </c>
       <c r="N4" s="3">
         <v>14</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>921</v>
+        <v>1004</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>922</v>
+        <v>1005</v>
       </c>
       <c r="Q4" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2019_TACO_A刊_Layup: Layer-adaptive and Multi-type Intermediate-oriented Memory Optimization for GPU-based CNNs</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>923</v>
+        <v>1006</v>
       </c>
       <c r="T4" s="3"/>
     </row>
@@ -11241,35 +11841,39 @@
         <v>150</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>641</v>
+        <v>849</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>924</v>
+        <v>1007</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>925</v>
+        <v>1008</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>926</v>
+        <v>1009</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
+      <c r="L5" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>1011</v>
+      </c>
       <c r="N5" s="4">
         <v>185</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>927</v>
+        <v>1012</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>928</v>
+        <v>1013</v>
       </c>
       <c r="Q5" s="4" t="str">
         <f t="shared" si="0"/>
@@ -11278,56 +11882,60 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:20">
-      <c r="A6" s="3">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="6" ht="36" hidden="1" customHeight="1" spans="1:20">
+      <c r="A6" s="5">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="5">
         <v>2021</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="s">
-        <v>906</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3">
+      <c r="E6" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="s">
+        <v>986</v>
+      </c>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>823</v>
+      </c>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5">
         <v>44</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>930</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>931</v>
-      </c>
-      <c r="Q6" s="3" t="str">
+      <c r="O6" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="P6" s="5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="Q6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>2021_NeurIPS_A会_Efficient Combination of Rematerialization and Offloading for Training DNNs</v>
       </c>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3" t="s">
-        <v>932</v>
-      </c>
-      <c r="T6" s="3"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:20">
       <c r="A7" s="3">
@@ -11341,35 +11949,39 @@
         <v>204</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>634</v>
+        <v>840</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>933</v>
+        <v>1018</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>934</v>
+        <v>1019</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>935</v>
+        <v>1020</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="L7" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>1021</v>
+      </c>
       <c r="N7" s="3">
         <v>7</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>936</v>
+        <v>1022</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>937</v>
+        <v>1023</v>
       </c>
       <c r="Q7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -11391,35 +12003,39 @@
         <v>450</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>938</v>
+        <v>1024</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>220</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>939</v>
+        <v>1025</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>940</v>
+        <v>1026</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>941</v>
+        <v>1027</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>942</v>
+        <v>1028</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="L8" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>1030</v>
+      </c>
       <c r="N8" s="3">
         <v>13</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>943</v>
+        <v>1031</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>944</v>
+        <v>1032</v>
       </c>
       <c r="Q8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -11427,7 +12043,7 @@
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>945</v>
+        <v>1033</v>
       </c>
       <c r="T8" s="3"/>
     </row>
@@ -11443,45 +12059,49 @@
         <v>204</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>946</v>
+        <v>1034</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>947</v>
+        <v>1035</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>948</v>
+        <v>1036</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>949</v>
+        <v>1037</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>950</v>
+        <v>1038</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="L9" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>1040</v>
+      </c>
       <c r="N9" s="3">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>951</v>
+        <v>1041</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>952</v>
+        <v>1042</v>
       </c>
       <c r="Q9" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_TKDE_A刊_TENSILE: A Tensor Granularity Dynamic GPU Memory Scheduling Method Toward Multiple Dynamic Workloads System</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>953</v>
+        <v>1043</v>
       </c>
       <c r="T9" s="3"/>
     </row>
@@ -11497,45 +12117,49 @@
         <v>150</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>954</v>
+        <v>1044</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>836</v>
+        <v>684</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>955</v>
+        <v>1045</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>956</v>
+        <v>1046</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>957</v>
+        <v>1047</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="L10" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>1048</v>
+      </c>
       <c r="N10" s="3">
         <v>22</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>958</v>
+        <v>1049</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>959</v>
+        <v>1050</v>
       </c>
       <c r="Q10" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_ICDE_A会_TSPLIT: Fine-grained GPU Memory Management for Efficient DNN Training via Tensor Splitting</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>960</v>
+        <v>1051</v>
       </c>
       <c r="T10" s="3"/>
     </row>
@@ -11557,37 +12181,41 @@
         <v>198</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>961</v>
+        <v>1052</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>962</v>
+        <v>1053</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
+      <c r="L11" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>1054</v>
+      </c>
       <c r="N11" s="3">
         <v>52</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>963</v>
+        <v>1055</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>964</v>
+        <v>1056</v>
       </c>
       <c r="Q11" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2022_ICML_A会_POET: Training Neural Networks on Tiny Devices with Integrated Rematerialization and Paging</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>965</v>
+        <v>1057</v>
       </c>
       <c r="T11" s="3"/>
     </row>
@@ -11609,39 +12237,43 @@
         <v>301</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>966</v>
+        <v>1058</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>967</v>
+        <v>1059</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>968</v>
+        <v>1060</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
+      <c r="L12" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>1062</v>
+      </c>
       <c r="N12" s="3">
         <v>5</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>969</v>
+        <v>1063</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>970</v>
+        <v>1064</v>
       </c>
       <c r="Q12" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2023_TPDS_A刊_STR: Hybrid Tensor Re-Generation to Break Memory Wall for DNN Training</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>971</v>
+        <v>1065</v>
       </c>
       <c r="T12" s="3"/>
     </row>
@@ -11657,33 +12289,37 @@
         <v>472</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>776</v>
+        <v>623</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>972</v>
+        <v>1066</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>973</v>
+        <v>1067</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>974</v>
+        <v>1068</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
+      <c r="L13" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="N13" s="3" t="s">
         <v>51</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>975</v>
+        <v>1069</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>976</v>
+        <v>1070</v>
       </c>
       <c r="Q13" s="3" t="str">
         <f t="shared" si="0"/>
@@ -11691,7 +12327,7 @@
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>977</v>
+        <v>1071</v>
       </c>
       <c r="T13" s="3"/>
     </row>
@@ -11707,45 +12343,49 @@
         <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>594</v>
+        <v>696</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>168</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>978</v>
+        <v>1072</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>979</v>
+        <v>1073</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>980</v>
+        <v>1074</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
+      <c r="L14" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>1075</v>
+      </c>
       <c r="N14" s="3" t="s">
         <v>51</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>981</v>
+        <v>1076</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>982</v>
+        <v>1077</v>
       </c>
       <c r="Q14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2024_TACO_A刊_DELTA: Memory-Efficient Training via Dynamic Fine-Grained Recomputation and Swapping</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>983</v>
+        <v>1078</v>
       </c>
       <c r="T14" s="3"/>
     </row>
@@ -11761,35 +12401,39 @@
         <v>204</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>594</v>
+        <v>696</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>984</v>
+        <v>1079</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>985</v>
+        <v>1080</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>906</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="L15" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>1083</v>
+      </c>
       <c r="N15" s="3" t="s">
         <v>51</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>988</v>
+        <v>1084</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>989</v>
+        <v>1085</v>
       </c>
       <c r="Q15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -11797,7 +12441,7 @@
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>990</v>
+        <v>1086</v>
       </c>
       <c r="T15" s="3"/>
     </row>
@@ -11813,43 +12457,47 @@
         <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>641</v>
+        <v>849</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>836</v>
+        <v>684</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>991</v>
+        <v>1087</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>992</v>
+        <v>1088</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
+      <c r="L16" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>1090</v>
+      </c>
       <c r="N16" s="3">
         <v>4</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>993</v>
+        <v>1091</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>994</v>
+        <v>1092</v>
       </c>
       <c r="Q16" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2024_ASPLOS_A会_MAGIS: Memory Optimization via Coordinated Graph Transformation and Scheduling for DNN</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>995</v>
+        <v>1093</v>
       </c>
       <c r="T16" s="3"/>
     </row>
@@ -11865,35 +12513,39 @@
         <v>150</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>996</v>
+        <v>1094</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>836</v>
+        <v>684</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>997</v>
+        <v>1095</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>998</v>
+        <v>1096</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>999</v>
+        <v>1097</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>942</v>
+        <v>1028</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
+      <c r="L17" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>1099</v>
+      </c>
       <c r="N17" s="3" t="s">
         <v>51</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="Q17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -11901,7 +12553,7 @@
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>1002</v>
+        <v>1102</v>
       </c>
       <c r="T17" s="3"/>
     </row>
@@ -11917,46 +12569,50 @@
         <v>150</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>954</v>
+        <v>1044</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>1003</v>
+        <v>1103</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1004</v>
+        <v>1104</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>906</v>
+        <v>986</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
+      <c r="L18" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>1106</v>
+      </c>
       <c r="N18" s="3">
         <v>1</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>1005</v>
+        <v>1107</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>1006</v>
+        <v>1108</v>
       </c>
       <c r="Q18" s="3" t="str">
         <f t="shared" si="0"/>
         <v>2025_ICDE_A会_LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>1007</v>
+        <v>1109</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>1008</v>
+        <v>1110</v>
       </c>
     </row>
   </sheetData>
@@ -12054,13 +12710,13 @@
         <v>569</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>111</v>
@@ -12075,7 +12731,7 @@
         <v>11</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="S1" s="2" t="s">
         <v>112</v>
@@ -12096,31 +12752,33 @@
         <v>113</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1009</v>
+        <v>1111</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>611</v>
+        <v>807</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1010</v>
+        <v>1112</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>1011</v>
+        <v>1113</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="L2" s="4" t="s">
+        <v>823</v>
+      </c>
       <c r="M2" s="4"/>
       <c r="N2" s="4">
         <v>24</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>1012</v>
+        <v>1114</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>1013</v>
+        <v>1115</v>
       </c>
       <c r="Q2" s="4" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
@@ -12128,10 +12786,10 @@
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4" t="s">
-        <v>1014</v>
+        <v>1116</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>580</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:20">
@@ -12152,37 +12810,41 @@
         <v>426</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1015</v>
+        <v>1117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1016</v>
+        <v>1118</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>1011</v>
+        <v>1113</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
+      <c r="L3" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>1119</v>
+      </c>
       <c r="N3" s="3">
         <v>5</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>1017</v>
+        <v>1120</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>1018</v>
+        <v>1121</v>
       </c>
       <c r="Q3" s="3" t="str">
         <f t="shared" ref="Q2:Q7" si="1">B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
         <v>2023_NeurIPS_A会_Coop: Memory is not a Commodity</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>1019</v>
+        <v>1122</v>
       </c>
       <c r="T3" s="3"/>
     </row>
@@ -12204,37 +12866,41 @@
         <v>382</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1020</v>
+        <v>1123</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1021</v>
+        <v>1124</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>1011</v>
+        <v>1113</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
+      <c r="L4" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>733</v>
+      </c>
       <c r="N4" s="3">
         <v>12</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>1022</v>
+        <v>1125</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>1023</v>
+        <v>1126</v>
       </c>
       <c r="Q4" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_MODeL: Memory Optimizations for Deep Learning</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>1024</v>
+        <v>1127</v>
       </c>
       <c r="T4" s="3"/>
     </row>
@@ -12250,35 +12916,39 @@
         <v>113</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1025</v>
+        <v>1128</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1026</v>
+        <v>1129</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1027</v>
+        <v>1130</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1028</v>
+        <v>1131</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1029</v>
+        <v>1132</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>1011</v>
+        <v>1113</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
+      <c r="L5" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>733</v>
+      </c>
       <c r="N5" s="3">
         <v>2</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>1030</v>
+        <v>1134</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>1031</v>
+        <v>1135</v>
       </c>
       <c r="Q5" s="3" t="str">
         <f t="shared" si="1"/>
@@ -12286,7 +12956,7 @@
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>1032</v>
+        <v>1136</v>
       </c>
       <c r="T5" s="3"/>
     </row>
@@ -12302,48 +12972,52 @@
         <v>150</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>641</v>
+        <v>849</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1033</v>
+        <v>1137</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1034</v>
+        <v>1138</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1035</v>
+        <v>1139</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>1036</v>
+        <v>1140</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>1011</v>
+        <v>1113</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
+      <c r="L6" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>1141</v>
+      </c>
       <c r="N6" s="4">
         <v>12</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>1037</v>
+        <v>1142</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>1038</v>
+        <v>1143</v>
       </c>
       <c r="Q6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2024_ASPLOS_A会_GMLake: Efficient and Transparent GPU Memory Defragmentation for Large-scale DNN Training with Virtual Memory Stitching</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="S6" s="4" t="s">
-        <v>1039</v>
+        <v>1144</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>580</v>
+        <v>634</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:20">
@@ -12355,36 +13029,40 @@
         <v>2024</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>609</v>
+        <v>805</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>610</v>
+        <v>806</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1040</v>
+        <v>1145</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1041</v>
+        <v>1146</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3" t="s">
-        <v>1042</v>
+        <v>1147</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>1011</v>
+        <v>1113</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="L7" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>733</v>
+      </c>
       <c r="N7" s="3">
         <v>1</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>1043</v>
+        <v>1148</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>1044</v>
+        <v>1149</v>
       </c>
       <c r="Q7" s="3" t="str">
         <f t="shared" si="1"/>
@@ -12427,16 +13105,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1045</v>
+        <v>1150</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1046</v>
+        <v>1151</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1047</v>
+        <v>1152</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -12463,26 +13141,26 @@
         <v>2019</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1048</v>
+        <v>1153</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1049</v>
+        <v>1154</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1050</v>
+        <v>1155</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1051</v>
+        <v>1156</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1052</v>
+        <v>1157</v>
       </c>
       <c r="H2" s="3" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;E2&amp;""</f>
         <v>2019_A Taxonomy of Cache Replacement Policies_缓存替换策略的分类</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1053</v>
+        <v>1158</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -12495,26 +13173,26 @@
         <v>2023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1054</v>
+        <v>1159</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1055</v>
+        <v>1160</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1056</v>
+        <v>1161</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1057</v>
+        <v>1162</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1058</v>
+        <v>1163</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>B3&amp;"_"&amp;D3&amp;"_"&amp;E3&amp;""</f>
         <v>2023_Operating Systems: Three Easy Pieces_操作系统导论</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1059</v>
+        <v>1164</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -12530,21 +13208,21 @@
         <v>284</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1060</v>
+        <v>1165</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>1061</v>
+        <v>1166</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1062</v>
+        <v>1167</v>
       </c>
       <c r="H4" s="3" t="str">
         <f>B4&amp;"_"&amp;D4&amp;""</f>
         <v>2024_大语言模型</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1063</v>
+        <v>1168</v>
       </c>
       <c r="J4" s="3"/>
     </row>

--- a/InfoSummary.xlsx
+++ b/InfoSummary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="14088" firstSheet="2" activeTab="7"/>
+    <workbookView windowWidth="29868" windowHeight="14088" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="学位" sheetId="10" r:id="rId1"/>
@@ -22,11 +22,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">学位!$A$1:$M$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">综述!$A$1:$N$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">框架!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">模型!$A$1:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">模型!$A$1:$N$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Recomp!$A$1:$U$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Swap!$A$1:$U$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hybrid!$A$1:$T$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">MAS!$A$1:$T$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Hybrid!$A$1:$U$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">MAS!$A$1:$U$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">电子书!$A$1:$J$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="1215">
   <si>
     <t>序号</t>
   </si>
@@ -850,7 +850,7 @@
     <t>Computational modeling,Training data,Transformers,Bandwidth,Arithmetic,Hardware,Data models,Unsupervised learning,Artificial intelligence,Memory management</t>
   </si>
   <si>
-    <t>综述;AI 内存墙;背景;挑战;</t>
+    <t>综述;AI内存墙;背景;挑战;</t>
   </si>
   <si>
     <t>[1]Amir Gholami;Zhewei Yao;Sehoon Kim;Coleman Hooper;Michael W. Mahoney;Kurt Keutzer.AI and Memory Wall[J].IEEE Micro,2024,Vol.44(3): 33-39</t>
@@ -1128,6 +1128,27 @@
   </si>
   <si>
     <t>论文地址：https://jcst.ict.ac.cn/article/cstr/32374.14.s11390-024-4178-1</t>
+  </si>
+  <si>
+    <t>C刊/SCI三区</t>
+  </si>
+  <si>
+    <t>FITEE</t>
+  </si>
+  <si>
+    <t>Training large-scale language models with limited GPU memory: a survey</t>
+  </si>
+  <si>
+    <t>Training techniques; Memory optimization; Model parameters; Model states; Model activations</t>
+  </si>
+  <si>
+    <t>综述;LLM训练;</t>
+  </si>
+  <si>
+    <t>[1]Tang Y, Qiao L, Yin L, et al. Training large-scale language models with limited GPU memory: a survey[J]. Frontiers of Information Technology &amp; Electronic Engineering, 2025: 1-23.</t>
+  </si>
+  <si>
+    <t>tang2025training</t>
   </si>
   <si>
     <t>缩写</t>
@@ -1992,6 +2013,9 @@
     <t>重计算;静态;离线;整数线性规划;</t>
   </si>
   <si>
+    <t>Tensor</t>
+  </si>
+  <si>
     <t>activation tensors;</t>
   </si>
   <si>
@@ -2095,9 +2119,6 @@
   </si>
   <si>
     <t>重计算;动态;在线;</t>
-  </si>
-  <si>
-    <t>Tensor</t>
   </si>
   <si>
     <t>online; heuristic; greedy algorithm;</t>
@@ -2650,7 +2671,7 @@
     <t>内存交换;内存分配;动态;离线;</t>
   </si>
   <si>
-    <t>Variables</t>
+    <t>Variables / Tensor</t>
   </si>
   <si>
     <t>feature maps;</t>
@@ -2669,6 +2690,9 @@
   </si>
   <si>
     <t>论文地址：https://arxiv.org/abs/1903.06631</t>
+  </si>
+  <si>
+    <t>在 TENSILE 论文里，作者称 AutoSwap 是“首个能够按张量粒度调度 GPU 内存的方法。得益于张量粒度，该方法能够支持任何深度学习网络。”</t>
   </si>
   <si>
     <t>TC</t>
@@ -3118,13 +3142,49 @@
 代码仓库：https://github.com/gulang2019/LSP-Offload/tree/main</t>
   </si>
   <si>
+    <t>ICDE</t>
+  </si>
+  <si>
+    <t>LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU</t>
+  </si>
+  <si>
+    <t>LoHan</t>
+  </si>
+  <si>
+    <t>PyTorch 2.0.0</t>
+  </si>
+  <si>
+    <t>ZeRO-Infinity; ZeRO-Offload; Colossal-AI; FlashNeuron;</t>
+  </si>
+  <si>
+    <t>[1]Liao C, Sun M, Yang Z, et al. LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU[J]. arXiv preprint arXiv:2403.06504, 2024.</t>
+  </si>
+  <si>
+    <t>liao2024lohan</t>
+  </si>
+  <si>
+    <t>论文地址：https://arxiv.org/abs/2403.06504v2
+论文翻译（v1）：https://yiyibooks.cn/arxiv/2403.06504v1/index.html
+论文作者：https://wangzeke.github.io/
+代码仓库：https://github.com/RC4ML/LoHan</t>
+  </si>
+  <si>
+    <t>这篇论文已经被ICDE 2025接收;</t>
+  </si>
+  <si>
     <t>阿里</t>
   </si>
   <si>
     <t>Training Deeper Models by GPU Memory Optimization on TensorFlow</t>
   </si>
   <si>
-    <t>内存交换;重计算;</t>
+    <t>内存交换;重计算;离线;静态;</t>
+  </si>
+  <si>
+    <t>feature maps</t>
+  </si>
+  <si>
+    <t>graph rewriting; heuristically searching;</t>
   </si>
   <si>
     <t>TensorFlow r1.2</t>
@@ -3136,7 +3196,8 @@
     <t>meng2017training</t>
   </si>
   <si>
-    <t>论文博客：https://www.jiqizhixin.com/articles/2017-12-07-3</t>
+    <t>论文博客1：https://www.jiqizhixin.com/articles/2017-12-07-3
+论文博客2：https://zhuanlan.zhihu.com/p/31863033</t>
   </si>
   <si>
     <t>PPoPP</t>
@@ -3152,6 +3213,9 @@
   </si>
   <si>
     <t>Neural Networks, GPU Memory Management, Runtime Scheduling</t>
+  </si>
+  <si>
+    <t>greedy algorithm;</t>
   </si>
   <si>
     <t>Caffe; MXNet; Torch; TensorFlow;</t>
@@ -3165,7 +3229,12 @@
   <si>
     <t>论文地址1：https://dl.acm.org/doi/abs/10.1145/3178487.3178491
 论文地址2：https://arxiv.org/abs/1801.04380
-代码仓库：https://github.com/linnanwang/superneurons-release</t>
+作者主页：https://linnanwang.github.io/
+代码仓库：https://github.com/linnanwang/superneurons-release
+论文博客1：https://www.jianshu.com/p/1ccd353f8cf5
+论文博客2：https://blog.csdn.net/qq_43207982/article/details/134213300
+论文博客3：https://www.zhihu.com/question/595298808/answer/3032971515
+论文博客4：https://zhuanlan.zhihu.com/p/114718838</t>
   </si>
   <si>
     <t>Layup: Layer-adaptive and Multi-type Intermediate-oriented Memory Optimization for GPU-based CNNs</t>
@@ -3200,6 +3269,12 @@
     <t>deep learning training; GPU memory management; tensor access</t>
   </si>
   <si>
+    <t>内存交换;重计算;在线;动态;静态;</t>
+  </si>
+  <si>
+    <t>tensors;</t>
+  </si>
+  <si>
     <t>TensorFlow 1.11</t>
   </si>
   <si>
@@ -3212,9 +3287,16 @@
     <t>peng2020capuchin</t>
   </si>
   <si>
+    <t>论文博客1：https://mp.weixin.qq.com/s/laBH_-Kvjjir6zuBNTpygQ?poc_token=HJ-_4mejIj7XD9xK3L5sDiIk08Yi4LmCWXjZuA3O
+论文博客2：https://blog.csdn.net/qq_43207982/article/details/134193428</t>
+  </si>
+  <si>
     <t>Efficient Combination of Rematerialization and Offloading for Training DNNs</t>
   </si>
   <si>
+    <t>内存交换;重计算;</t>
+  </si>
+  <si>
     <t>[1]Beaumont O, Eyraud-Dubois L, Shilova A. Efficient combination of rematerialization and offloading for training dnns[J]. Advances in Neural Information Processing Systems, 2021, 34: 23844-23857.</t>
   </si>
   <si>
@@ -3233,6 +3315,9 @@
     <t>DNN, GPU, recomputation, swapping, tensor</t>
   </si>
   <si>
+    <t>particle swarm optimization (PSO) algorithm;</t>
+  </si>
+  <si>
     <t>PyTorch; vDNN; SuperNeurons; Capuchin;</t>
   </si>
   <si>
@@ -3254,7 +3339,13 @@
     <t>Dynamic datafow graph, Tensor partition, Tensor rematerialization</t>
   </si>
   <si>
-    <t>内存交换;重计算;内存分配;</t>
+    <t>内存交换;重计算;内存分配;在线;动态;</t>
+  </si>
+  <si>
+    <t>intermediate outputs;</t>
+  </si>
+  <si>
+    <t>greedy algorithm; rule-based simulation;</t>
   </si>
   <si>
     <t>MegEngine 1.7</t>
@@ -3287,6 +3378,12 @@
     <t>DB4AI, GPU memory schedule</t>
   </si>
   <si>
+    <t>内存交换;重计算;在线;静态;</t>
+  </si>
+  <si>
+    <t>light neural network; greedy algorithm;</t>
+  </si>
+  <si>
     <t>tinyflow</t>
   </si>
   <si>
@@ -3299,10 +3396,9 @@
     <t>zhang2022tensile</t>
   </si>
   <si>
-    <t>代码仓库：https://github.com/GIS-PuppetMaster/tinyflow</t>
-  </si>
-  <si>
-    <t>ICDE</t>
+    <t>论文地址：https://arxiv.org/abs/2105.13336v5
+论文博客：https://mp.weixin.qq.com/s/EmmJQv79oB7Ec5uxVkPZCA
+代码仓库：https://github.com/GIS-PuppetMaster/tinyflow</t>
   </si>
   <si>
     <t>TSPLIT: Fine-grained GPU Memory Management for Efficient DNN Training via Tensor Splitting</t>
@@ -3312,6 +3408,12 @@
   </si>
   <si>
     <t>Deep Learning System, Memory Management, Large Model Support.</t>
+  </si>
+  <si>
+    <t>Micro-Tensor</t>
+  </si>
+  <si>
+    <t>greedy search algorithm;</t>
   </si>
   <si>
     <t>PyTorch; vDNN; Sublinear; SuperNeurons; ZeRO-Offload;</t>
@@ -3331,6 +3433,9 @@
   </si>
   <si>
     <t>POET</t>
+  </si>
+  <si>
+    <t>mixed-integer linear program;</t>
   </si>
   <si>
     <t>PyTorch; Sublinear; Checkmate; DTR;</t>
@@ -3357,6 +3462,9 @@
     <t>DNN training, offload memory, recomputation, rematerialization, swap.</t>
   </si>
   <si>
+    <t>mixed integer linear program; Gurobi;</t>
+  </si>
+  <si>
     <t>TensorFlow 1.15.2</t>
   </si>
   <si>
@@ -3399,13 +3507,17 @@
     <t>Dynamic tensor recomputation and swapping, Knapsack Problem, bidirectional prefetching, GPU memory management</t>
   </si>
   <si>
+    <t>内存交换;重计算;在线;动态;</t>
+  </si>
+  <si>
     <t>PyTorch; vDNN; SuperNeurons; Capuchin; DTR; POET;</t>
   </si>
   <si>
     <t>[1]Tang Y, Li Q, Yin L, et al. DELTA: Memory-Efficient Training via Dynamic Fine-Grained Recomputation and Swapping[J]. ACM Transactions on Architecture and Code Optimization, 2024, 21(4): 1-25.</t>
   </si>
   <si>
-    <t>tang2024delta</t>
+    <t>tang2024delta
+tang2022delta</t>
   </si>
   <si>
     <t>论文地址1：https://dl.acm.org/doi/full/10.1145/3689338
@@ -3413,6 +3525,9 @@
 代码仓库：https://github.com/TonyTangYu/delta-examples</t>
   </si>
   <si>
+    <t>论文里的 DELTA* 是 arXiv 上的工作。</t>
+  </si>
+  <si>
     <t>西交大</t>
   </si>
   <si>
@@ -3423,6 +3538,12 @@
   </si>
   <si>
     <t>DNN training, GPUmemory management, Training throughput, Performance improvement</t>
+  </si>
+  <si>
+    <t>内存交换;重计算;内存分配;离线;静态;</t>
+  </si>
+  <si>
+    <t>greedy algorithm; genetic algorithm;</t>
   </si>
   <si>
     <t>vDNN; SuperNeurons; SwapAdviser; HOME;</t>
@@ -3444,6 +3565,9 @@
     <t>MAGIS</t>
   </si>
   <si>
+    <t>graph transformation; graph scheduling;</t>
+  </si>
+  <si>
     <t>PyTorch 2.1.0</t>
   </si>
   <si>
@@ -3471,6 +3595,9 @@
     <t>Large Language Model, Long Context Training, Tensor Management, Data Rematerialization</t>
   </si>
   <si>
+    <t>内存交换;重计算;内存分配;</t>
+  </si>
+  <si>
     <t>PyTorch 2.0</t>
   </si>
   <si>
@@ -3486,40 +3613,28 @@
     <t>论文地址：https://arxiv.org/abs/2407.12117</t>
   </si>
   <si>
-    <t>LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU</t>
-  </si>
-  <si>
-    <t>LoHan</t>
-  </si>
-  <si>
-    <t>PyTorch 2.0.0</t>
-  </si>
-  <si>
-    <t>ZeRO-Infinity; ZeRO-Offload; Colossal-AI; FlashNeuron;</t>
-  </si>
-  <si>
-    <t>[1]Liao C, Sun M, Yang Z, et al. LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU[J]. arXiv preprint arXiv:2403.06504, 2024.</t>
-  </si>
-  <si>
-    <t>liao2024lohan</t>
-  </si>
-  <si>
-    <t>论文地址：https://arxiv.org/abs/2403.06504v2
-论文翻译（v1）：https://yiyibooks.cn/arxiv/2403.06504v1/index.html
-论文作者：https://wangzeke.github.io/
-代码仓库：https://github.com/RC4ML/LoHan</t>
-  </si>
-  <si>
-    <t>这篇论文已经被ICDE 2025接收;</t>
-  </si>
-  <si>
     <t>arXiv:1804.10001</t>
   </si>
   <si>
     <t>Profile-guided memory optimization for deep neural networks</t>
   </si>
   <si>
-    <t>内存分配;</t>
+    <t>Chainer-Opt</t>
+  </si>
+  <si>
+    <t>内存分配;静态;离线;</t>
+  </si>
+  <si>
+    <t>Memory block</t>
+  </si>
+  <si>
+    <t>memory blocks;</t>
+  </si>
+  <si>
+    <t>mixed integer programming; best-fit heuristic algorithm;</t>
+  </si>
+  <si>
+    <t>Chainer;</t>
   </si>
   <si>
     <t>[1]Sekiyama T, Imamichi T, Imai H, et al. Profile-guided memory optimization for deep neural networks[J]. arXiv preprint arXiv:1804.10001, 2018.</t>
@@ -3537,6 +3652,15 @@
     <t>Coop</t>
   </si>
   <si>
+    <t>内存分配;动态;在线;</t>
+  </si>
+  <si>
+    <t>memory layout;</t>
+  </si>
+  <si>
+    <t>sliding window; heuristic;</t>
+  </si>
+  <si>
     <t>OneFlow; DTR; MegTaiChi</t>
   </si>
   <si>
@@ -3547,14 +3671,23 @@
   </si>
   <si>
     <t>论文地址1：https://proceedings.neurips.cc/paper_files/paper/2023/hash/9c534edc7ac1d6438216311be6d42eb2-Abstract-Conference.html
-论文地址2：https://arxiv.org/abs/2311.00591
-代码仓库：https://github.com/Oneflow-Inc/oneflow/pull/9861</t>
+论文地址2：https://openreview.net/forum?id=gmmXyAq8TI
+论文地址3：https://arxiv.org/abs/2311.00591
+代码仓库：https://github.com/Oneflow-Inc/oneflow/pull/9861
+论文博客：https://mp.weixin.qq.com/s/1oBszAsvrAdPVNKD2SgCFA
+论文视频：https://www.bilibili.com/video/BV1iK411d7AC/?vd_source=84320eb1655c3ce482a61278ff7b3724</t>
   </si>
   <si>
     <t>MODeL: Memory Optimizations for Deep Learning</t>
   </si>
   <si>
     <t>MODeL</t>
+  </si>
+  <si>
+    <t>computation graphs; tensor; memory location;</t>
+  </si>
+  <si>
+    <t>integer linear program; Gurobi;</t>
   </si>
   <si>
     <t>[1]Steiner B, Elhoushi M, Kahn J, et al. Model: memory optimizations for deep learning[C]//International Conference on Machine Learning. PMLR, 2023: 32618-32632.</t>
@@ -3584,6 +3717,12 @@
     <t>Deep Learning System, Memory Optimization, Large Model Support, Memory Efficiency</t>
   </si>
   <si>
+    <t>computation graphs;</t>
+  </si>
+  <si>
+    <t>integer linear program; subgraph tree divisions;</t>
+  </si>
+  <si>
     <t>PyTorch 1.13.1</t>
   </si>
   <si>
@@ -3606,6 +3745,9 @@
   </si>
   <si>
     <t>Memory Defragmentation, GPU, Deep Learning, Virtual Memory Stitching</t>
+  </si>
+  <si>
+    <t>CUDA VMM; BFC algorithm;</t>
   </si>
   <si>
     <t>PyTorch; Deepspeed; Colossal-AI; FSDP;</t>
@@ -3627,7 +3769,16 @@
     <t>A Heuristic for Periodic Memory Allocation with Little Fragmentation to Train Neural Networks</t>
   </si>
   <si>
+    <t>DSA-SA</t>
+  </si>
+  <si>
     <t>Dynamic Storage Allocation, Fragmentation, Heuristics, GPU Memory</t>
+  </si>
+  <si>
+    <t>allocations;</t>
+  </si>
+  <si>
+    <t>simulated annealing algorithm;</t>
   </si>
   <si>
     <t>[1]Imanishi A, Xu Z. A Heuristic for Periodic Memory Allocation with Little Fragmentation to Train Neural Networks[C]//Proceedings of the 2024 ACM SIGPLAN International Symposium on Memory Management. 2024: 82-94.</t>
@@ -4712,7 +4863,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1874520" y="12344400"/>
+              <a:off x="1874520" y="10058400"/>
               <a:ext cx="537845" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4736,13 +4887,13 @@
         <xdr:from>
           <xdr:col>3</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
           <xdr:colOff>537845</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>182880</xdr:rowOff>
         </xdr:to>
         <xdr:sp>
@@ -4758,7 +4909,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="1874520" y="3200400"/>
+              <a:off x="1874520" y="2743200"/>
               <a:ext cx="537845" cy="182880"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -5726,7 +5877,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -5962,7 +6113,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1" spans="1:14">
+    <row r="6" ht="36" hidden="1" customHeight="1" spans="1:14">
       <c r="A6" s="5">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -6228,7 +6379,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1" spans="1:14">
+    <row r="12" ht="36" hidden="1" customHeight="1" spans="1:14">
       <c r="A12" s="5">
         <f t="shared" si="2"/>
         <v>11</v>
@@ -6272,7 +6423,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1" spans="1:14">
+    <row r="13" ht="36" hidden="1" customHeight="1" spans="1:14">
       <c r="A13" s="5">
         <f t="shared" si="2"/>
         <v>12</v>
@@ -6360,7 +6511,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1" spans="1:14">
+    <row r="15" ht="36" hidden="1" customHeight="1" spans="1:14">
       <c r="A15" s="5">
         <f t="shared" si="2"/>
         <v>14</v>
@@ -6406,7 +6557,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1" spans="1:14">
+    <row r="16" ht="36" hidden="1" customHeight="1" spans="1:14">
       <c r="A16" s="5">
         <f t="shared" si="2"/>
         <v>15</v>
@@ -6990,7 +7141,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="29" ht="36" customHeight="1" spans="1:14">
+    <row r="29" ht="36" hidden="1" customHeight="1" spans="1:14">
       <c r="A29" s="5">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -7077,6 +7228,50 @@
         <v>349</v>
       </c>
       <c r="N30" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1" spans="1:14">
+      <c r="A31" s="3">
+        <f>ROW()-1</f>
+        <v>30</v>
+      </c>
+      <c r="B31" s="3">
+        <v>2025</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="L31" s="3" t="str">
+        <f>B31&amp;"_"&amp;D31&amp;"_"&amp;C31&amp;"_"&amp;F31&amp;""</f>
+        <v>2025_FITEE_C刊/SCI三区_Training large-scale language models with limited GPU memory: a survey</v>
+      </c>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3" t="s">
         <v>130</v>
       </c>
     </row>
@@ -7088,7 +7283,7 @@
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="44" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="53" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -7161,7 +7356,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -7197,41 +7392,41 @@
         <v>2010</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J2" s="3">
         <v>874</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="M2" s="3" t="str">
         <f t="shared" ref="M2:M17" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2010_SciPy_Python领域_Theano: A CPU and GPU Math Compiler in Python</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="O2" s="3"/>
     </row>
@@ -7247,38 +7442,38 @@
         <v>150</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>198</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="J3" s="3">
         <v>18557</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="M3" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2014_ACM MM_A会_Caffe: Convolutional Architecture for Fast Feature Embedding</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="O3" s="3"/>
     </row>
@@ -7294,36 +7489,36 @@
         <v>113</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J4" s="3">
         <v>2936</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="M4" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2015_arXiv:1512.01274_v1_MXNet: A Flexible and Efficient Machine Learning Library for Heterogeneous Distributed Systems</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="O4" s="3"/>
     </row>
@@ -7339,36 +7534,36 @@
         <v>150</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J5" s="3">
         <v>46587</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="M5" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2016_OSDI_A会_TensorFlow: A System for Large-Scale Machine Learning</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="O5" s="3"/>
     </row>
@@ -7387,33 +7582,33 @@
         <v>159</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J6" s="3">
         <v>54391</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="M6" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_NeurIPS_A会_PyTorch: An Imperative Style, High-Performance Deep Learning Library</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="O6" s="3"/>
     </row>
@@ -7429,36 +7624,36 @@
         <v>241</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J7" s="3">
         <v>364</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="M7" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_数据与计算发展前沿_T3刊_PaddlePaddle: An Open-Source Deep Learning Platform from Industrial Practice</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="O7" s="3"/>
     </row>
@@ -7474,38 +7669,38 @@
         <v>204</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>301</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J8" s="3">
         <v>160</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="M8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_SCIS_A刊_Jittor: a novel deep learning framework with meta-operators and unified graph execution</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="O8" s="3"/>
     </row>
@@ -7521,38 +7716,38 @@
         <v>150</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="J9" s="3">
         <v>1283</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_SIGKDD_A会_DeepSpeed: System Optimizations Enable Training Deep Learning Models with Over 100 Billion Parameters</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="O9" s="3"/>
     </row>
@@ -7568,36 +7763,36 @@
         <v>273</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="J10" s="3">
         <v>1996</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="M10" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_arXiv:1909.08053_v4_Megatron-LM: Training Multi-Billion Parameter Language Models Using Model Parallelism</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="O10" s="3"/>
     </row>
@@ -7613,29 +7808,29 @@
         <v>150</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="J11" s="3">
         <v>1366</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="M11" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7653,39 +7848,39 @@
         <v>2021</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J12" s="3">
         <v>45</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="M12" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_arXiv:2110.15032_v6_OneFlow: Redesign the Distributed Deep Learning Framework from Scratch</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="O12" s="3"/>
     </row>
@@ -7701,36 +7896,36 @@
         <v>150</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="J13" s="3">
         <v>427</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="M13" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_USENIX ATC_A会_ZeRO-Offload: Democratizing Billion-Scale Model Training</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="O13" s="3"/>
     </row>
@@ -7746,36 +7941,36 @@
         <v>150</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="J14" s="3">
         <v>360</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="M14" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_SC_A会_ZeRO-infinity: breaking the GPU memory wall for extreme scale deep learning</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="O14" s="3"/>
     </row>
@@ -7788,39 +7983,39 @@
         <v>2022</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J15" s="3">
         <v>7</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="M15" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_Textbook_白皮书_Huawei MindSpore AI Development Framework</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="O15" s="3"/>
     </row>
@@ -7833,41 +8028,41 @@
         <v>2023</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="J16" s="3">
         <v>146</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="M16" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICPP_B会_Colossal-AI: A Unified Deep Learning System For Large-Scale Parallel Training</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="O16" s="3"/>
     </row>
@@ -7883,36 +8078,36 @@
         <v>141</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="J17" s="3">
         <v>284</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="M17" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_arXiv:2304.11277_v2_PyTorch FSDP: Experiences on Scaling Fully Sharded Data Parallel</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="O17" s="3"/>
     </row>
@@ -7934,7 +8129,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -7966,7 +8161,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>110</v>
@@ -7990,66 +8185,91 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="36" customHeight="1" spans="1:14">
+    <row r="2" ht="36" customHeight="1" spans="1:14">
       <c r="A2" s="3">
-        <f>ROW()-1</f>
+        <f t="shared" ref="A2:A17" si="0">ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
+      <c r="B2" s="3">
+        <v>2012</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="I2" s="3">
+        <v>141067</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="L2" s="3" t="str">
+        <f t="shared" ref="L2:L17" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+        <v>2012_NeurIPS_A会_ImageNet Classification with Deep Convolutional Neural Networks</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>478</v>
+      </c>
       <c r="N2" s="3"/>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:14">
       <c r="A3" s="3">
-        <f t="shared" ref="A3:A18" si="0">ROW()-1</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3" s="3">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>150</v>
+        <v>479</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>159</v>
+        <v>480</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>465</v>
+        <v>481</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="I3" s="3">
-        <v>141067</v>
+        <v>140476</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>469</v>
+        <v>484</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>470</v>
+        <v>485</v>
       </c>
       <c r="L3" s="3" t="str">
-        <f t="shared" ref="L3:L18" si="1">B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
-        <v>2012_NeurIPS_A会_ImageNet Classification with Deep Convolutional Neural Networks</v>
+        <f t="shared" si="1"/>
+        <v>2015_ICLR_顶会_Very Deep Convolutional Networks for Large-Scale Image Recognition</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -8059,41 +8279,41 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>472</v>
+        <v>150</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>474</v>
+        <v>410</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>468</v>
-      </c>
       <c r="I4" s="3">
-        <v>140476</v>
+        <v>259309</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="L4" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2015_ICLR_顶会_Very Deep Convolutional Networks for Large-Scale Image Recognition</v>
+        <v>2016_CVPR_A会_Deep Residual Learning for Image Recognition</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -8103,41 +8323,41 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>150</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>403</v>
+        <v>493</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="I5" s="3">
-        <v>259309</v>
+        <v>52228</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="L5" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2016_CVPR_A会_Deep Residual Learning for Image Recognition</v>
+        <v>2017_CVPR_A会_Densely Connected Convolutional Networks</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -8153,35 +8373,35 @@
         <v>150</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>480</v>
+        <v>159</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>486</v>
+        <v>383</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>468</v>
+        <v>501</v>
       </c>
       <c r="I6" s="3">
-        <v>52228</v>
+        <v>170262</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="L6" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2017_CVPR_A会_Densely Connected Convolutional Networks</v>
+        <v>2017_NeurIPS_A会_Attention is All you Need</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -8191,41 +8411,41 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>150</v>
+        <v>457</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>159</v>
+        <v>505</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="I7" s="3">
-        <v>170262</v>
+        <v>125703</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="L7" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2017_NeurIPS_A会_Attention is All you Need</v>
+        <v>2019_NAACL_B会_BERT: Pre-training of Deep Bidirectional Transformers for Language Understanding</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="N7" s="3"/>
     </row>
@@ -8235,41 +8455,41 @@
         <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="I8" s="3">
-        <v>125703</v>
+        <v>56822</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="L8" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2019_NAACL_B会_BERT: Pre-training of Deep Bidirectional Transformers for Language Understanding</v>
+        <v>2021_ICLR_顶会_An Image is Worth 16x16 Words: Transformers for Image Recognition at Scale</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -8279,41 +8499,41 @@
         <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>472</v>
+        <v>273</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>473</v>
+        <v>516</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="I9" s="3">
-        <v>56822</v>
+        <v>2935</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="L9" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2021_ICLR_顶会_An Image is Worth 16x16 Words: Transformers for Image Recognition at Scale</v>
+        <v>2022_arXiv:2205.01068_v4_OPT: Open Pre-trained Transformer Language Models</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="N9" s="3"/>
     </row>
@@ -8326,38 +8546,38 @@
         <v>2022</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>273</v>
+        <v>523</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>382</v>
+        <v>525</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="I10" s="3">
-        <v>2935</v>
+        <v>1064</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>513</v>
+        <v>528</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="L10" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_arXiv:2205.01068_v4_OPT: Open Pre-trained Transformer Language Models</v>
+        <v>2022_arXiv:2203.13474_v5_CodeGen: An Open Large Language Model for Code with Multi-Turn Program Synthesis</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="N10" s="3"/>
     </row>
@@ -8367,41 +8587,41 @@
         <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>516</v>
+        <v>141</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>512</v>
-      </c>
       <c r="I11" s="3">
-        <v>1064</v>
+        <v>196</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="L11" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2022_arXiv:2203.13474_v5_CodeGen: An Open Large Language Model for Code with Multi-Turn Program Synthesis</v>
+        <v>2023_arXiv:2305.02309_v2_CodeGen2: Lessons for Training LLMs on Programming and Natural Languages</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>523</v>
+        <v>536</v>
       </c>
       <c r="N11" s="3"/>
     </row>
@@ -8411,41 +8631,41 @@
         <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>141</v>
+        <v>431</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>518</v>
+        <v>115</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="I12" s="3">
-        <v>196</v>
+        <v>9183</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="L12" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2023_arXiv:2305.02309_v2_CodeGen2: Lessons for Training LLMs on Programming and Natural Languages</v>
+        <v>2024_arXiv:2303.08774_v6_GPT-4 Technical Report</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="N12" s="3"/>
     </row>
@@ -8458,38 +8678,38 @@
         <v>2024</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>424</v>
+        <v>543</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>115</v>
+        <v>389</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="I13" s="3">
-        <v>9183</v>
+        <v>3298</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="L13" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_arXiv:2303.08774_v6_GPT-4 Technical Report</v>
+        <v>2024_arXiv:2407.21783_v3_The Llama 3 Herd of Models</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="N13" s="3"/>
     </row>
@@ -8502,38 +8722,38 @@
         <v>2024</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="I14" s="3">
-        <v>3298</v>
+        <v>522</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="L14" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_arXiv:2407.21783_v3_The Llama 3 Herd of Models</v>
+        <v>2024_arXiv:2408.00118_v3_Gemma 2: Improving Open Language Models at a Practical Size</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="N14" s="3"/>
     </row>
@@ -8546,38 +8766,38 @@
         <v>2024</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>536</v>
+        <v>150</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="I15" s="3">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>546</v>
+        <v>559</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="L15" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_arXiv:2408.00118_v3_Gemma 2: Improving Open Language Models at a Practical Size</v>
+        <v>2024_ICML_A会_MobileLLM: Optimizing Sub-billion Parameter Language Models for On-Device Use Cases</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>548</v>
+        <v>561</v>
       </c>
       <c r="N15" s="3"/>
     </row>
@@ -8590,38 +8810,38 @@
         <v>2024</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>549</v>
+        <v>562</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>382</v>
+        <v>563</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="I16" s="3">
-        <v>84</v>
+        <v>326</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="L16" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_ICML_A会_MobileLLM: Optimizing Sub-billion Parameter Language Models for On-Device Use Cases</v>
+        <v>2024_arXiv:2401.02385_v2_TinyLlama: An Open-Source Small Language Model</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="N16" s="3"/>
     </row>
@@ -8631,91 +8851,47 @@
         <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>141</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="I17" s="3">
-        <v>326</v>
+        <v>201</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="L17" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>2024_arXiv:2401.02385_v2_TinyLlama: An Open-Source Small Language Model</v>
+        <v>2025_arXiv:2412.19437_v2_DeepSeek-V3 Technical Report</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="N17" s="3"/>
     </row>
-    <row r="18" ht="36" customHeight="1" spans="1:14">
-      <c r="A18" s="3">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="3">
-        <v>2025</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="I18" s="3">
-        <v>201</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="L18" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>2025_arXiv:2412.19437_v2_DeepSeek-V3 Technical Report</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="N18" s="3"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N18" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:N18">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N17" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:N17">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
@@ -8734,13 +8910,13 @@
               <from>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>0</xdr:colOff>
-                <xdr:row>7</xdr:row>
+                <xdr:row>6</xdr:row>
                 <xdr:rowOff>0</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>3</xdr:col>
                 <xdr:colOff>537845</xdr:colOff>
-                <xdr:row>7</xdr:row>
+                <xdr:row>6</xdr:row>
                 <xdr:rowOff>182880</xdr:rowOff>
               </to>
             </anchor>
@@ -8796,7 +8972,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -8805,19 +8981,19 @@
         <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>111</v>
@@ -8832,7 +9008,7 @@
         <v>11</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>112</v>
@@ -8853,57 +9029,57 @@
         <v>141</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="O2" s="4">
         <v>1122</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
       <c r="R2" s="4" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2016_arXiv:1604.06174_v2_Training Deep Nets with Sublinear Memory Cost</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:21">
@@ -8921,41 +9097,41 @@
         <v>159</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
       <c r="O3" s="3">
         <v>250</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="R3" s="3" t="str">
         <f>B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
@@ -8963,7 +9139,7 @@
       </c>
       <c r="S3" s="3"/>
       <c r="T3" s="3" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="U3" s="3"/>
     </row>
@@ -8982,41 +9158,41 @@
         <v>159</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
       <c r="O4" s="3">
         <v>65</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
       <c r="R4" s="3" t="str">
         <f>B4&amp;"_"&amp;D4&amp;"_"&amp;C4&amp;"_"&amp;F4&amp;""</f>
@@ -9024,7 +9200,7 @@
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
       <c r="U4" s="3"/>
     </row>
@@ -9043,49 +9219,49 @@
         <v>159</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="O5" s="3">
         <v>49</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
       <c r="R5" s="3" t="str">
         <f>B5&amp;"_"&amp;D5&amp;"_"&amp;C5&amp;"_"&amp;F5&amp;""</f>
         <v>2019_NeurIPS_A会_A Graph Theoretic Framework of Recomputation Algorithms for Memory-Efficient Backpropagation</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="U5" s="3"/>
     </row>
@@ -9101,22 +9277,22 @@
         <v>113</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="3"/>
@@ -9127,20 +9303,20 @@
         <v>35</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>620</v>
+        <v>627</v>
       </c>
       <c r="Q6" s="5" t="s">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="R6" s="5" t="str">
         <f t="shared" ref="R6:R19" si="1">B6&amp;"_"&amp;D6&amp;"_"&amp;C6&amp;"_"&amp;F6&amp;""</f>
         <v>2019_arXiv:1911.13214_v1_Optimal checkpointing for heterogeneous chains: how to train deep neural networks with limited memory</v>
       </c>
       <c r="S6" s="5" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T6" s="5" t="s">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="U6" s="5" t="s">
         <v>158</v>
@@ -9155,60 +9331,60 @@
         <v>2020</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>198</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>624</v>
+        <v>631</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>579</v>
+        <v>634</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="O7" s="4">
         <v>208</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="R7" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2020_MLSys_顶会_Checkmate: Breaking the Memory Wall with Optimal Tensor Rematerialization</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="U7" s="4" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:21">
@@ -9223,56 +9399,56 @@
         <v>150</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="O8" s="3">
         <v>40</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="R8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_ISCA_A会_Echo: Compiler-based GPU Memory Footprint Reduction for LSTM RNN Training</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="U8" s="3"/>
     </row>
@@ -9285,57 +9461,57 @@
         <v>2021</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="O9" s="3">
         <v>29</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="R9" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_ICLR_顶会_Memory Optimization for Deep Networks</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="U9" s="3"/>
     </row>
@@ -9348,60 +9524,60 @@
         <v>2021</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="O10" s="4">
         <v>95</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="R10" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2021_ICLR_顶会_Dynamic Tensor Rematerialization</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="U10" s="4" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1" spans="1:21">
@@ -9416,54 +9592,54 @@
         <v>150</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="O11" s="3">
         <v>33</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="R11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_CVPR_A会_Optimal Gradient Checkpoint Search for Arbitrary Computation Graphs</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="U11" s="3"/>
     </row>
@@ -9482,51 +9658,51 @@
         <v>159</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>679</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>672</v>
       </c>
       <c r="O12" s="3">
         <v>7</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="R12" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_NeurIPS_A会_Tempo: Accelerating Transformer-Based Model Training through Memory Footprint Reduction</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="U12" s="3"/>
     </row>
@@ -9539,59 +9715,59 @@
         <v>2022</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="O13" s="3">
         <v>58</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="R13" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_MobiSys_B会_Melon: breaking the memory wall for resource-efficient on-device machine learning</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="U13" s="3"/>
     </row>
@@ -9607,56 +9783,56 @@
         <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="O14" s="3">
         <v>4</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="R14" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_TACO_A刊_XEngine: Optimal Tensor Rematerialization for Neural Networks in Heterogeneous Environments</v>
       </c>
       <c r="S14" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="U14" s="3"/>
     </row>
@@ -9669,59 +9845,59 @@
         <v>2023</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="O15" s="3">
         <v>1</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="R15" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_IPDPS_B会_Exploiting Input Tensor Dynamics in Activation Checkpointing for Efficient Training on GPU</v>
       </c>
       <c r="S15" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="U15" s="3"/>
     </row>
@@ -9737,54 +9913,54 @@
         <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="O16" s="3">
         <v>3</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="R16" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_Moccasin: Efficient Tensor Rematerialization for Neural Networks</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="U16" s="3"/>
     </row>
@@ -9797,45 +9973,45 @@
         <v>2023</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="O17" s="3">
         <v>4</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="R17" s="3" t="str">
         <f t="shared" si="1"/>
@@ -9843,7 +10019,7 @@
       </c>
       <c r="S17" s="3"/>
       <c r="T17" s="3" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="U17" s="3"/>
     </row>
@@ -9859,50 +10035,50 @@
         <v>150</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="O18" s="5">
         <v>3</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="Q18" s="5" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="R18" s="5" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_Rockmate: an Efficient, Fast, Automatic and Generic Tool for Re-materialization in PyTorch</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="U18" s="5" t="s">
         <v>158</v>
@@ -9920,54 +10096,54 @@
         <v>218</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>51</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
       <c r="R19" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2025_JPDC_B刊_GPU memory usage optimization for backward propagation in deep network training</v>
       </c>
       <c r="S19" s="6" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="U19" s="3"/>
     </row>
@@ -10018,7 +10194,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -10054,7 +10230,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -10063,19 +10239,19 @@
         <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>111</v>
@@ -10090,7 +10266,7 @@
         <v>11</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>112</v>
@@ -10101,7 +10277,7 @@
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:21">
       <c r="A2" s="4">
-        <f t="shared" ref="A2:A24" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A25" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="4">
@@ -10111,55 +10287,55 @@
         <v>150</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="O2" s="4">
         <v>540</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>763</v>
+        <v>770</v>
       </c>
       <c r="R2" s="4" t="str">
-        <f t="shared" ref="R2:R24" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+        <f t="shared" ref="R2:R25" si="1">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2016_MICRO_A会_vDNN: Virtualized deep neural networks for scalable, memory-efficient neural network design</v>
       </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:21">
@@ -10171,47 +10347,47 @@
         <v>2018</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>275</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="O3" s="4">
         <v>42</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="R3" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10220,7 +10396,7 @@
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
       <c r="U3" s="4" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:21">
@@ -10241,40 +10417,40 @@
         <v>220</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="O4" s="3">
         <v>19</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="R4" s="3" t="str">
         <f t="shared" si="1"/>
@@ -10282,7 +10458,7 @@
       </c>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="U4" s="3"/>
     </row>
@@ -10298,56 +10474,56 @@
         <v>204</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>124</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="O5" s="3">
         <v>53</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="R5" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2018_TACO_A刊_Layer-Centric Memory Reuse and Data Migration for Extreme-Scale Deep Learning on Many-Core Architectures</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="U5" s="3"/>
     </row>
@@ -10360,49 +10536,49 @@
         <v>2019</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
       <c r="O6" s="3">
         <v>15</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="R6" s="3" t="str">
         <f t="shared" si="1"/>
@@ -10410,7 +10586,7 @@
       </c>
       <c r="S6" s="3"/>
       <c r="T6" s="3" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="U6" s="3"/>
     </row>
@@ -10423,59 +10599,59 @@
         <v>2019</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="O7" s="3">
         <v>22</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="R7" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_ISMM_内存领域_Automatic GPU memory management for large neural models in TensorFlow</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="U7" s="3"/>
     </row>
@@ -10488,124 +10664,126 @@
         <v>2019</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="O8" s="3">
         <v>58</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="R8" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2019_IPDPS_B会_Dynamic Memory Management for GPU-Based Training of Deep Neural Networks</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="U8" s="3"/>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:21">
-      <c r="A9" s="3">
+      <c r="A9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>2019</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>829</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>836</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="N9" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="O9" s="4">
         <v>57</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>837</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>838</v>
-      </c>
-      <c r="R9" s="3" t="str">
+      <c r="P9" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="R9" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2019_arXiv:1903.06631_v1_Efficient Memory Management for GPU-based Deep Learning Systems</v>
       </c>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3" t="s">
-        <v>839</v>
-      </c>
-      <c r="U9" s="3"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>847</v>
+      </c>
     </row>
     <row r="10" ht="36" hidden="1" customHeight="1" spans="1:21">
       <c r="A10" s="5">
@@ -10619,38 +10797,38 @@
         <v>204</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5">
         <v>10</v>
       </c>
       <c r="P10" s="5" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="Q10" s="5" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="R10" s="5" t="str">
         <f t="shared" si="1"/>
@@ -10674,54 +10852,54 @@
         <v>150</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="O11" s="3">
         <v>86</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="R11" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2020_ASPLOS_A会_AutoTM: Automatic Tensor Movement in Heterogeneous Memory Systems using Integer Linear Programming</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="U11" s="3"/>
     </row>
@@ -10737,44 +10915,44 @@
         <v>150</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="O12" s="4">
         <v>214</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="R12" s="4" t="str">
         <f t="shared" si="1"/>
@@ -10782,10 +10960,10 @@
       </c>
       <c r="S12" s="4"/>
       <c r="T12" s="4" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="U12" s="4" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:21">
@@ -10797,49 +10975,49 @@
         <v>2020</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="O13" s="3">
         <v>15</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="R13" s="3" t="str">
         <f t="shared" si="1"/>
@@ -10847,7 +11025,7 @@
       </c>
       <c r="S13" s="3"/>
       <c r="T13" s="3" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="U13" s="3"/>
     </row>
@@ -10860,41 +11038,41 @@
         <v>2020</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="O14" s="5">
         <v>27</v>
       </c>
       <c r="P14" s="5" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="Q14" s="5" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="R14" s="5" t="str">
         <f t="shared" si="1"/>
@@ -10902,7 +11080,7 @@
       </c>
       <c r="S14" s="5"/>
       <c r="T14" s="5" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="U14" s="5" t="s">
         <v>158</v>
@@ -10920,54 +11098,54 @@
         <v>150</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>266</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="O15" s="3">
         <v>58</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="R15" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2021_FAST_A会_FlashNeuron: SSD-Enabled Large-Batch Training of Very Deep Neural Networks</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="U15" s="3"/>
     </row>
@@ -10983,50 +11161,50 @@
         <v>150</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="O16" s="5">
         <v>75</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="Q16" s="5" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="R16" s="5" t="str">
         <f t="shared" si="1"/>
         <v>2021_HPCA_A会_Sentinel: Efficient Tensor Migration and Allocation on Heterogeneous Memory Systems for Deep Learning</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T16" s="5" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="U16" s="5" t="s">
         <v>158</v>
@@ -11050,50 +11228,50 @@
         <v>69</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>834</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>906</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>651</v>
-      </c>
       <c r="N17" s="3" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="O17" s="3">
         <v>4</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="R17" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_TPDS_A刊_Accelerating Tensor Swapping in GPUs With Self-Tuning Compression</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="U17" s="3"/>
     </row>
@@ -11109,46 +11287,46 @@
         <v>204</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>220</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="O18" s="3">
         <v>3</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="R18" s="3" t="str">
         <f t="shared" si="1"/>
@@ -11156,7 +11334,7 @@
       </c>
       <c r="S18" s="3"/>
       <c r="T18" s="3" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="U18" s="3"/>
     </row>
@@ -11172,56 +11350,56 @@
         <v>150</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="O19" s="3">
         <v>18</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="R19" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2022_SC_A会_STRONGHOLD: Fast and Affordable Billion-Scale Deep Learning Model Training</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="U19" s="3"/>
     </row>
@@ -11237,46 +11415,46 @@
         <v>150</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>266</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="O20" s="3">
         <v>25</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="R20" s="3" t="str">
         <f t="shared" si="1"/>
@@ -11284,7 +11462,7 @@
       </c>
       <c r="S20" s="3"/>
       <c r="T20" s="3" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="U20" s="3"/>
     </row>
@@ -11300,56 +11478,56 @@
         <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>949</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>950</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>939</v>
-      </c>
       <c r="K21" s="3" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="O21" s="3">
         <v>18</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="R21" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_MICRO_A会_G10: Enabling An Efficient Unified GPU Memory and Storage Architecture with Smart Tensor Migrations</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="U21" s="3"/>
     </row>
@@ -11365,44 +11543,44 @@
         <v>150</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="O22" s="3">
         <v>8</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="R22" s="3" t="str">
         <f t="shared" si="1"/>
@@ -11410,7 +11588,7 @@
       </c>
       <c r="S22" s="3"/>
       <c r="T22" s="3" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="U22" s="3"/>
     </row>
@@ -11429,43 +11607,43 @@
         <v>205</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>659</v>
+        <v>634</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="O23" s="3">
         <v>1</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="R23" s="3" t="str">
         <f t="shared" si="1"/>
@@ -11487,51 +11665,110 @@
         <v>141</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="O24" s="5" t="s">
         <v>51</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="Q24" s="5" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="R24" s="5" t="str">
         <f t="shared" si="1"/>
         <v>2025_arXiv:2406.10181_v2_Practical offloading for fine-tuning LLM on commodity GPU via learned sparse projectors</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="T24" s="5" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="U24" s="5" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A25" s="5">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>992</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5" t="s">
+        <v>995</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>996</v>
+      </c>
+      <c r="O25" s="5">
+        <v>1</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="R25" s="5" t="str">
+        <f t="shared" si="1"/>
+        <v>2025_ICDE_A会_LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU</v>
+      </c>
+      <c r="S25" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="U25" s="5" t="s">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
@@ -11581,7 +11818,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -11590,14 +11827,14 @@
     <col min="6" max="6" width="20.7777777777778" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7777777777778" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="14" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="15" max="17" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.77777777777778" style="1" customWidth="1"/>
-    <col min="19" max="20" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.88888888888889" style="1"/>
+    <col min="9" max="15" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="16" max="18" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77777777777778" style="1" customWidth="1"/>
+    <col min="20" max="21" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11617,7 +11854,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -11626,94 +11863,106 @@
         <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>574</v>
-      </c>
       <c r="S1" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:20">
-      <c r="A2" s="3">
+    <row r="2" ht="36" customHeight="1" spans="1:21">
+      <c r="A2" s="4">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>2017</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="N2" s="3">
+      <c r="E2" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="O2" s="4">
         <v>105</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>988</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="Q2" s="3" t="str">
-        <f t="shared" ref="Q2:Q18" si="0">B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
+      <c r="P2" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="R2" s="4" t="str">
+        <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2017_NeurIPS_A会_Training Deeper Models by GPU Memory Optimization on TensorFlow</v>
       </c>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3" t="s">
-        <v>990</v>
-      </c>
-      <c r="T2" s="3"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:20">
+      <c r="S2" s="4"/>
+      <c r="T2" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:21">
       <c r="A3" s="4">
-        <f t="shared" ref="A3:A12" si="1">ROW()-1</f>
+        <f t="shared" ref="A3:A12" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="4">
@@ -11723,57 +11972,64 @@
         <v>150</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>991</v>
+        <v>1010</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>992</v>
+        <v>1011</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>993</v>
+        <v>1012</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>994</v>
+        <v>1013</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>995</v>
+        <v>1014</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
+        <v>1003</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>676</v>
+      </c>
       <c r="L3" s="4" t="s">
-        <v>823</v>
+        <v>1015</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>996</v>
-      </c>
-      <c r="N3" s="4">
+        <v>830</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="O3" s="4">
         <v>322</v>
       </c>
-      <c r="O3" s="4" t="s">
-        <v>997</v>
-      </c>
       <c r="P3" s="4" t="s">
-        <v>998</v>
-      </c>
-      <c r="Q3" s="4" t="str">
+        <v>1017</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="R3" s="4" t="str">
+        <f>B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
+        <v>2018_PPoPP_A会_Superneurons: dynamic GPU memory management for training deep neural networks</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="T3" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:21">
+      <c r="A4" s="3">
         <f t="shared" si="0"/>
-        <v>2018_PPoPP_A会_Superneurons: dynamic GPU memory management for training deep neural networks</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>999</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:20">
-      <c r="A4" s="3">
-        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="B4" s="3">
@@ -11783,55 +12039,62 @@
         <v>204</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>124</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1000</v>
+        <v>1020</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1001</v>
+        <v>1021</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1002</v>
+        <v>1022</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+        <v>1003</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>756</v>
+      </c>
       <c r="L4" s="3" t="s">
-        <v>363</v>
+        <v>766</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>1003</v>
-      </c>
-      <c r="N4" s="3">
+        <v>370</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="O4" s="3">
         <v>14</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>1004</v>
-      </c>
       <c r="P4" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="Q4" s="3" t="str">
+        <v>1024</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="R4" s="3" t="str">
+        <f>B4&amp;"_"&amp;D4&amp;"_"&amp;C4&amp;"_"&amp;F4&amp;""</f>
+        <v>2019_TACO_A刊_Layup: Layer-adaptive and Multi-type Intermediate-oriented Memory Optimization for GPU-based CNNs</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="U4" s="3"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:21">
+      <c r="A5" s="4">
         <f t="shared" si="0"/>
-        <v>2019_TACO_A刊_Layup: Layer-adaptive and Multi-type Intermediate-oriented Memory Optimization for GPU-based CNNs</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:20">
-      <c r="A5" s="4">
-        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="B5" s="4">
@@ -11841,53 +12104,62 @@
         <v>150</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>124</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>1007</v>
+        <v>1027</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>1008</v>
+        <v>1028</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>1009</v>
+        <v>1029</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
+        <v>1030</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>1031</v>
+      </c>
       <c r="L5" s="4" t="s">
-        <v>1010</v>
+        <v>1015</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>1011</v>
-      </c>
-      <c r="N5" s="4">
+        <v>1032</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O5" s="4">
         <v>185</v>
       </c>
-      <c r="O5" s="4" t="s">
-        <v>1012</v>
-      </c>
       <c r="P5" s="4" t="s">
-        <v>1013</v>
-      </c>
-      <c r="Q5" s="4" t="str">
-        <f t="shared" si="0"/>
+        <v>1034</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="R5" s="4" t="str">
+        <f>B5&amp;"_"&amp;D5&amp;"_"&amp;C5&amp;"_"&amp;F5&amp;""</f>
         <v>2020_ASPLOS_A会_Capuchin: Tensor-based GPU Memory Management for Deep Learning</v>
       </c>
-      <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="6" ht="36" hidden="1" customHeight="1" spans="1:20">
+        <v>1036</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="6" ht="36" hidden="1" customHeight="1" spans="1:21">
       <c r="A6" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="5">
@@ -11900,46 +12172,47 @@
         <v>159</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>1014</v>
+        <v>1037</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
-        <v>986</v>
+        <v>1038</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>823</v>
-      </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5">
+      <c r="L6" s="5"/>
+      <c r="M6" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5">
         <v>44</v>
       </c>
-      <c r="O6" s="5" t="s">
-        <v>1015</v>
-      </c>
       <c r="P6" s="5" t="s">
-        <v>1016</v>
-      </c>
-      <c r="Q6" s="5" t="str">
+        <v>1039</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="R6" s="5" t="str">
+        <f>B6&amp;"_"&amp;D6&amp;"_"&amp;C6&amp;"_"&amp;F6&amp;""</f>
+        <v>2021_NeurIPS_A会_Efficient Combination of Rematerialization and Offloading for Training DNNs</v>
+      </c>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:21">
+      <c r="A7" s="3">
         <f t="shared" si="0"/>
-        <v>2021_NeurIPS_A会_Efficient Combination of Rematerialization and Offloading for Training DNNs</v>
-      </c>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5" t="s">
-        <v>1017</v>
-      </c>
-      <c r="T6" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:20">
-      <c r="A7" s="3">
-        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="B7" s="3">
@@ -11949,107 +12222,121 @@
         <v>204</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>69</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>1018</v>
+        <v>1042</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1019</v>
+        <v>1043</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>1020</v>
+        <v>1044</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+        <v>1003</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>841</v>
+      </c>
       <c r="L7" s="3" t="s">
-        <v>651</v>
+        <v>1045</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>1021</v>
-      </c>
-      <c r="N7" s="3">
+        <v>659</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="O7" s="3">
         <v>7</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>1022</v>
-      </c>
       <c r="P7" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="Q7" s="3" t="str">
-        <f t="shared" si="0"/>
+        <v>1047</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="R7" s="3" t="str">
+        <f>B7&amp;"_"&amp;D7&amp;"_"&amp;C7&amp;"_"&amp;F7&amp;""</f>
         <v>2022_TC_A刊_HOME: A Holistic GPU Memory Management Framework for Deep Learning</v>
       </c>
-      <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:20">
+      <c r="U7" s="3"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" spans="1:21">
       <c r="A8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="3">
         <v>2022</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>1024</v>
+        <v>1049</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>220</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1027</v>
+        <v>1052</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>1028</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+        <v>1053</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>1054</v>
+      </c>
       <c r="L8" s="3" t="s">
-        <v>1029</v>
+        <v>1055</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="N8" s="3">
+        <v>1056</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="O8" s="3">
         <v>13</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>1031</v>
-      </c>
       <c r="P8" s="3" t="s">
-        <v>1032</v>
-      </c>
-      <c r="Q8" s="3" t="str">
+        <v>1058</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="R8" s="3" t="str">
+        <f>B8&amp;"_"&amp;D8&amp;"_"&amp;C8&amp;"_"&amp;F8&amp;""</f>
+        <v>2022_ICS_B会_MegTaiChi: dynamic tensor-based memory management optimization for DNN training</v>
+      </c>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="U8" s="3"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" spans="1:21">
+      <c r="A9" s="3">
         <f t="shared" si="0"/>
-        <v>2022_ICS_B会_MegTaiChi: dynamic tensor-based memory management optimization for DNN training</v>
-      </c>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3" t="s">
-        <v>1033</v>
-      </c>
-      <c r="T8" s="3"/>
-    </row>
-    <row r="9" ht="36" customHeight="1" spans="1:20">
-      <c r="A9" s="3">
-        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="B9" s="3">
@@ -12059,55 +12346,62 @@
         <v>204</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1034</v>
+        <v>1061</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1035</v>
+        <v>1062</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>1036</v>
+        <v>1063</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>1037</v>
+        <v>1064</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>1038</v>
+        <v>1065</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+        <v>1066</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>1031</v>
+      </c>
       <c r="L9" s="3" t="s">
-        <v>1039</v>
+        <v>1067</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>1040</v>
-      </c>
-      <c r="N9" s="3">
+        <v>1068</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="O9" s="3">
         <v>3</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>1041</v>
-      </c>
       <c r="P9" s="3" t="s">
-        <v>1042</v>
-      </c>
-      <c r="Q9" s="3" t="str">
+        <v>1070</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="R9" s="3" t="str">
+        <f>B9&amp;"_"&amp;D9&amp;"_"&amp;C9&amp;"_"&amp;F9&amp;""</f>
+        <v>2022_TKDE_A刊_TENSILE: A Tensor Granularity Dynamic GPU Memory Scheduling Method Toward Multiple Dynamic Workloads System</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="U9" s="3"/>
+    </row>
+    <row r="10" ht="36" customHeight="1" spans="1:21">
+      <c r="A10" s="3">
         <f t="shared" si="0"/>
-        <v>2022_TKDE_A刊_TENSILE: A Tensor Granularity Dynamic GPU Memory Scheduling Method Toward Multiple Dynamic Workloads System</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>1043</v>
-      </c>
-      <c r="T9" s="3"/>
-    </row>
-    <row r="10" ht="36" customHeight="1" spans="1:20">
-      <c r="A10" s="3">
-        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B10" s="3">
@@ -12117,55 +12411,62 @@
         <v>150</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1044</v>
+        <v>992</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>1045</v>
+        <v>1073</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>1046</v>
+        <v>1074</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1047</v>
+        <v>1075</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+        <v>1003</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>1031</v>
+      </c>
       <c r="L10" s="3" t="s">
-        <v>823</v>
+        <v>1077</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>1048</v>
-      </c>
-      <c r="N10" s="3">
+        <v>830</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="O10" s="3">
         <v>22</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>1049</v>
-      </c>
       <c r="P10" s="3" t="s">
-        <v>1050</v>
-      </c>
-      <c r="Q10" s="3" t="str">
+        <v>1079</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="R10" s="3" t="str">
+        <f>B10&amp;"_"&amp;D10&amp;"_"&amp;C10&amp;"_"&amp;F10&amp;""</f>
+        <v>2022_ICDE_A会_TSPLIT: Fine-grained GPU Memory Management for Efficient DNN Training via Tensor Splitting</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="U10" s="3"/>
+    </row>
+    <row r="11" ht="36" customHeight="1" spans="1:21">
+      <c r="A11" s="3">
         <f t="shared" si="0"/>
-        <v>2022_ICDE_A会_TSPLIT: Fine-grained GPU Memory Management for Efficient DNN Training via Tensor Splitting</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>1051</v>
-      </c>
-      <c r="T10" s="3"/>
-    </row>
-    <row r="11" ht="36" customHeight="1" spans="1:20">
-      <c r="A11" s="3">
-        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B11" s="3">
@@ -12175,53 +12476,60 @@
         <v>150</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>198</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>1052</v>
+        <v>1082</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>1053</v>
+        <v>1083</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+        <v>1003</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>1031</v>
+      </c>
       <c r="L11" s="3" t="s">
-        <v>823</v>
+        <v>1084</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>1054</v>
-      </c>
-      <c r="N11" s="3">
+        <v>830</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="O11" s="3">
         <v>52</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>1055</v>
-      </c>
       <c r="P11" s="3" t="s">
-        <v>1056</v>
-      </c>
-      <c r="Q11" s="3" t="str">
+        <v>1086</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="R11" s="3" t="str">
+        <f>B11&amp;"_"&amp;D11&amp;"_"&amp;C11&amp;"_"&amp;F11&amp;""</f>
+        <v>2022_ICML_A会_POET: Training Neural Networks on Tiny Devices with Integrated Rematerialization and Paging</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="T11" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" spans="1:21">
+      <c r="A12" s="3">
         <f t="shared" si="0"/>
-        <v>2022_ICML_A会_POET: Training Neural Networks on Tiny Devices with Integrated Rematerialization and Paging</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>1057</v>
-      </c>
-      <c r="T11" s="3"/>
-    </row>
-    <row r="12" ht="36" customHeight="1" spans="1:20">
-      <c r="A12" s="3">
-        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B12" s="3">
@@ -12237,103 +12545,117 @@
         <v>301</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>1058</v>
+        <v>1089</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>1059</v>
+        <v>1090</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1060</v>
+        <v>1091</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+        <v>1003</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>708</v>
+      </c>
       <c r="L12" s="3" t="s">
-        <v>1061</v>
+        <v>1092</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>1062</v>
-      </c>
-      <c r="N12" s="3">
+        <v>1093</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="O12" s="3">
         <v>5</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>1063</v>
-      </c>
       <c r="P12" s="3" t="s">
-        <v>1064</v>
-      </c>
-      <c r="Q12" s="3" t="str">
-        <f t="shared" si="0"/>
+        <v>1095</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="R12" s="3" t="str">
+        <f>B12&amp;"_"&amp;D12&amp;"_"&amp;C12&amp;"_"&amp;F12&amp;""</f>
         <v>2023_TPDS_A刊_STR: Hybrid Tensor Re-Generation to Break Memory Wall for DNN Training</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>585</v>
-      </c>
       <c r="S12" s="3" t="s">
-        <v>1065</v>
-      </c>
-      <c r="T12" s="3"/>
-    </row>
-    <row r="13" ht="36" customHeight="1" spans="1:20">
+        <v>592</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="U12" s="3"/>
+    </row>
+    <row r="13" ht="36" customHeight="1" spans="1:21">
       <c r="A13" s="3">
-        <f t="shared" ref="A13:A18" si="2">ROW()-1</f>
+        <f>ROW()-1</f>
         <v>12</v>
       </c>
       <c r="B13" s="3">
         <v>2023</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>623</v>
+        <v>630</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1066</v>
+        <v>1098</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>1067</v>
+        <v>1099</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>1068</v>
+        <v>1100</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+        <v>1003</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>676</v>
+      </c>
       <c r="L13" s="3" t="s">
-        <v>384</v>
+        <v>1015</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>1008</v>
+        <v>391</v>
       </c>
       <c r="N13" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="O13" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="O13" s="3" t="s">
-        <v>1069</v>
-      </c>
       <c r="P13" s="3" t="s">
-        <v>1070</v>
-      </c>
-      <c r="Q13" s="3" t="str">
-        <f t="shared" si="0"/>
+        <v>1101</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="R13" s="3" t="str">
+        <f>B13&amp;"_"&amp;D13&amp;"_"&amp;C13&amp;"_"&amp;F13&amp;""</f>
         <v>2023_MLSys_顶会_μ-TWO: 3× Faster Multi-Model Training with Orchestration and Memory Optimization</v>
       </c>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3" t="s">
-        <v>1071</v>
-      </c>
-      <c r="T13" s="3"/>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:20">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="U13" s="3"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:21">
       <c r="A14" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>13</v>
       </c>
       <c r="B14" s="3">
@@ -12343,55 +12665,64 @@
         <v>204</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>168</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>1072</v>
+        <v>1104</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>1073</v>
+        <v>1105</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>1074</v>
+        <v>1106</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+        <v>1107</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>657</v>
+      </c>
       <c r="L14" s="3" t="s">
-        <v>661</v>
+        <v>1015</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>1075</v>
+        <v>668</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>1076</v>
+        <v>1108</v>
+      </c>
+      <c r="O14" s="3">
+        <v>6</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>1077</v>
-      </c>
-      <c r="Q14" s="3" t="str">
-        <f t="shared" si="0"/>
+        <v>1109</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="R14" s="3" t="str">
+        <f>B14&amp;"_"&amp;D14&amp;"_"&amp;C14&amp;"_"&amp;F14&amp;""</f>
         <v>2024_TACO_A刊_DELTA: Memory-Efficient Training via Dynamic Fine-Grained Recomputation and Swapping</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>585</v>
-      </c>
       <c r="S14" s="3" t="s">
-        <v>1078</v>
-      </c>
-      <c r="T14" s="3"/>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:20">
+        <v>592</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:21">
       <c r="A15" s="3">
-        <f t="shared" si="2"/>
+        <f>ROW()-1</f>
         <v>14</v>
       </c>
       <c r="B15" s="3">
@@ -12401,229 +12732,187 @@
         <v>204</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>1079</v>
+        <v>1113</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>1080</v>
+        <v>1114</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>1081</v>
+        <v>1115</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>1082</v>
+        <v>1116</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+        <v>1117</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>676</v>
+      </c>
       <c r="L15" s="3" t="s">
-        <v>823</v>
+        <v>1118</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>1083</v>
+        <v>830</v>
       </c>
       <c r="N15" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>1084</v>
-      </c>
       <c r="P15" s="3" t="s">
-        <v>1085</v>
-      </c>
-      <c r="Q15" s="3" t="str">
-        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="R15" s="3" t="str">
+        <f>B15&amp;"_"&amp;D15&amp;"_"&amp;C15&amp;"_"&amp;F15&amp;""</f>
         <v>2024_TACO_A刊_ATP: Achieving Throughput Peak for DNN Training via Smart GPU Memory Management</v>
       </c>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3" t="s">
-        <v>1086</v>
-      </c>
-      <c r="T15" s="3"/>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:20">
-      <c r="A16" s="3">
-        <f t="shared" si="2"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="U15" s="3"/>
+    </row>
+    <row r="16" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A16" s="5">
+        <f>ROW()-1</f>
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="5">
         <v>2024</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>849</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>1087</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>1088</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3" t="s">
-        <v>1089</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>1090</v>
-      </c>
-      <c r="N16" s="3">
+      <c r="D16" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>1124</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="O16" s="5">
         <v>4</v>
       </c>
-      <c r="O16" s="3" t="s">
-        <v>1091</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>1092</v>
-      </c>
-      <c r="Q16" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="P16" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>1129</v>
+      </c>
+      <c r="R16" s="5" t="str">
+        <f>B16&amp;"_"&amp;D16&amp;"_"&amp;C16&amp;"_"&amp;F16&amp;""</f>
         <v>2024_ASPLOS_A会_MAGIS: Memory Optimization via Coordinated Graph Transformation and Scheduling for DNN</v>
       </c>
-      <c r="R16" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>1093</v>
-      </c>
-      <c r="T16" s="3"/>
-    </row>
-    <row r="17" ht="36" customHeight="1" spans="1:20">
-      <c r="A17" s="3">
-        <f t="shared" si="2"/>
+      <c r="S16" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="T16" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="U16" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" ht="36" hidden="1" customHeight="1" spans="1:21">
+      <c r="A17" s="5">
+        <f>ROW()-1</f>
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="5">
         <v>2025</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>1097</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>1028</v>
-      </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3" t="s">
-        <v>1098</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>1099</v>
-      </c>
-      <c r="N17" s="3" t="s">
+      <c r="D17" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>691</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J17" s="5"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="O17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>1100</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>1101</v>
-      </c>
-      <c r="Q17" s="3" t="str">
-        <f t="shared" si="0"/>
+      <c r="P17" s="5" t="s">
+        <v>1138</v>
+      </c>
+      <c r="Q17" s="5" t="s">
+        <v>1139</v>
+      </c>
+      <c r="R17" s="5" t="str">
+        <f>B17&amp;"_"&amp;D17&amp;"_"&amp;C17&amp;"_"&amp;F17&amp;""</f>
         <v>2025_SIGMOD_A会_MEMO: Fine-grained Tensor Management For Ultra-long Context LLM Training</v>
       </c>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3" t="s">
-        <v>1102</v>
-      </c>
-      <c r="T17" s="3"/>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:20">
-      <c r="A18" s="3">
-        <f t="shared" si="2"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="3">
-        <v>2025</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>1104</v>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3" t="s">
-        <v>1105</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>1106</v>
-      </c>
-      <c r="N18" s="3">
-        <v>1</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>1107</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>1108</v>
-      </c>
-      <c r="Q18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>2025_ICDE_A会_LoHan: Low-Cost High-Performance Framework to Fine-Tune 100B Model on a Consumer GPU</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>1109</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>1110</v>
-      </c>
-    </row>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5" t="s">
+        <v>1140</v>
+      </c>
+      <c r="U17" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1"/>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T18" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:T18">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U18" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:U18">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="41" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="39" orientation="landscape"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -12662,7 +12951,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -12671,14 +12960,14 @@
     <col min="6" max="6" width="20.7777777777778" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.7777777777778" style="1" customWidth="1"/>
     <col min="8" max="8" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="9" max="14" width="15.7777777777778" style="1" customWidth="1"/>
-    <col min="15" max="17" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.77777777777778" style="1" customWidth="1"/>
-    <col min="19" max="20" width="20.7777777777778" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="8.88888888888889" style="1"/>
+    <col min="9" max="15" width="15.7777777777778" style="1" customWidth="1"/>
+    <col min="16" max="18" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77777777777778" style="1" customWidth="1"/>
+    <col min="20" max="21" width="20.7777777777778" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88888888888889" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="36" customHeight="1" spans="1:21">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12698,7 +12987,7 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>7</v>
@@ -12707,40 +12996,43 @@
         <v>110</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="2" t="s">
-        <v>574</v>
-      </c>
       <c r="S1" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="T1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="36" customHeight="1" spans="1:20">
+    <row r="2" ht="36" customHeight="1" spans="1:21">
       <c r="A2" s="4">
         <f t="shared" ref="A2:A7" si="0">ROW()-1</f>
         <v>1</v>
@@ -12752,47 +13044,58 @@
         <v>113</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>1111</v>
+        <v>1141</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>1112</v>
-      </c>
-      <c r="G2" s="4"/>
+        <v>1142</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>1143</v>
+      </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
-        <v>1113</v>
-      </c>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
+        <v>1144</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>1146</v>
+      </c>
       <c r="L2" s="4" t="s">
-        <v>823</v>
-      </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4">
+        <v>1147</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="O2" s="4">
         <v>24</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>1114</v>
-      </c>
       <c r="P2" s="4" t="s">
-        <v>1115</v>
-      </c>
-      <c r="Q2" s="4" t="str">
+        <v>1149</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="R2" s="4" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;C2&amp;"_"&amp;F2&amp;""</f>
         <v>2018_arXiv:1804.10001_v1_Profile-guided memory optimization for deep neural networks</v>
       </c>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4" t="s">
-        <v>1116</v>
-      </c>
+      <c r="S2" s="4"/>
       <c r="T2" s="4" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:20">
+        <v>1151</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" spans="1:21">
       <c r="A3" s="3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -12807,48 +13110,55 @@
         <v>159</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1117</v>
+        <v>1152</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1118</v>
+        <v>1153</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+        <v>1154</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>1155</v>
+      </c>
       <c r="L3" s="3" t="s">
-        <v>426</v>
+        <v>1156</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>1119</v>
-      </c>
-      <c r="N3" s="3">
+        <v>433</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="O3" s="3">
         <v>5</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>1120</v>
-      </c>
       <c r="P3" s="3" t="s">
-        <v>1121</v>
-      </c>
-      <c r="Q3" s="3" t="str">
-        <f t="shared" ref="Q2:Q7" si="1">B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
+        <v>1158</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="R3" s="3" t="str">
+        <f t="shared" ref="R2:R7" si="1">B3&amp;"_"&amp;D3&amp;"_"&amp;C3&amp;"_"&amp;F3&amp;""</f>
         <v>2023_NeurIPS_A会_Coop: Memory is not a Commodity</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>585</v>
-      </c>
       <c r="S3" s="3" t="s">
-        <v>1122</v>
-      </c>
-      <c r="T3" s="3"/>
-    </row>
-    <row r="4" ht="36" customHeight="1" spans="1:20">
+        <v>592</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="U3" s="3"/>
+    </row>
+    <row r="4" ht="36" customHeight="1" spans="1:21">
       <c r="A4" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -12860,51 +13170,58 @@
         <v>150</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>1123</v>
+        <v>1161</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1124</v>
+        <v>1162</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+        <v>1144</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>1163</v>
+      </c>
       <c r="L4" s="3" t="s">
-        <v>715</v>
+        <v>1164</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="N4" s="3">
+        <v>722</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="O4" s="3">
         <v>12</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>1125</v>
-      </c>
       <c r="P4" s="3" t="s">
-        <v>1126</v>
-      </c>
-      <c r="Q4" s="3" t="str">
+        <v>1165</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="R4" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_ICML_A会_MODeL: Memory Optimizations for Deep Learning</v>
       </c>
-      <c r="R4" s="3" t="s">
-        <v>585</v>
-      </c>
       <c r="S4" s="3" t="s">
-        <v>1127</v>
-      </c>
-      <c r="T4" s="3"/>
-    </row>
-    <row r="5" ht="36" customHeight="1" spans="1:20">
+        <v>592</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="U4" s="3"/>
+    </row>
+    <row r="5" ht="36" customHeight="1" spans="1:21">
       <c r="A5" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -12916,51 +13233,58 @@
         <v>113</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1128</v>
+        <v>1168</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1129</v>
+        <v>1169</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>1130</v>
+        <v>1170</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>1131</v>
+        <v>1171</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>1132</v>
+        <v>1172</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+        <v>1144</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>1173</v>
+      </c>
       <c r="L5" s="3" t="s">
-        <v>1133</v>
+        <v>1174</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="N5" s="3">
+        <v>1175</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="O5" s="3">
         <v>2</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>1134</v>
-      </c>
       <c r="P5" s="3" t="s">
-        <v>1135</v>
-      </c>
-      <c r="Q5" s="3" t="str">
+        <v>1176</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="R5" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2023_arXiv:2310.19295_v1_ROAM: memory-efficient large DNN training via optimized operator ordering and memory layout</v>
       </c>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3" t="s">
-        <v>1136</v>
-      </c>
-      <c r="T5" s="3"/>
-    </row>
-    <row r="6" ht="36" customHeight="1" spans="1:20">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="U5" s="3"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" spans="1:21">
       <c r="A6" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -12972,55 +13296,62 @@
         <v>150</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>1137</v>
+        <v>1179</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>1138</v>
+        <v>1180</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1139</v>
+        <v>1181</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>1140</v>
+        <v>1182</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>1113</v>
-      </c>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
+        <v>1154</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>1146</v>
+      </c>
       <c r="L6" s="4" t="s">
-        <v>1098</v>
+        <v>1183</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>1141</v>
-      </c>
-      <c r="N6" s="4">
+        <v>1136</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>1184</v>
+      </c>
+      <c r="O6" s="4">
         <v>12</v>
       </c>
-      <c r="O6" s="4" t="s">
-        <v>1142</v>
-      </c>
       <c r="P6" s="4" t="s">
-        <v>1143</v>
-      </c>
-      <c r="Q6" s="4" t="str">
+        <v>1185</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>1186</v>
+      </c>
+      <c r="R6" s="4" t="str">
         <f t="shared" si="1"/>
         <v>2024_ASPLOS_A会_GMLake: Efficient and Transparent GPU Memory Defragmentation for Large-scale DNN Training with Virtual Memory Stitching</v>
       </c>
-      <c r="R6" s="4" t="s">
-        <v>585</v>
-      </c>
       <c r="S6" s="4" t="s">
-        <v>1144</v>
+        <v>592</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" spans="1:20">
+        <v>1187</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" spans="1:21">
       <c r="A7" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -13029,58 +13360,67 @@
         <v>2024</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>1145</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>1147</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="3" t="s">
+        <v>1192</v>
+      </c>
       <c r="L7" s="3" t="s">
-        <v>384</v>
+        <v>1193</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="N7" s="3">
+        <v>391</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="O7" s="3">
         <v>1</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>1148</v>
-      </c>
       <c r="P7" s="3" t="s">
-        <v>1149</v>
-      </c>
-      <c r="Q7" s="3" t="str">
+        <v>1194</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="R7" s="3" t="str">
         <f t="shared" si="1"/>
         <v>2024_ISMM_内存领域_A Heuristic for Periodic Memory Allocation with Little Fragmentation to Train Neural Networks</v>
       </c>
-      <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:T7" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:T7">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:U7" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:U7">
       <sortCondition ref="B1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="41" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="39" orientation="landscape"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -13105,16 +13445,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1150</v>
+        <v>1196</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>109</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>1151</v>
+        <v>1197</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1152</v>
+        <v>1198</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>9</v>
@@ -13141,26 +13481,26 @@
         <v>2019</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>1153</v>
+        <v>1199</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>1154</v>
+        <v>1200</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>1155</v>
+        <v>1201</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>1156</v>
+        <v>1202</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1157</v>
+        <v>1203</v>
       </c>
       <c r="H2" s="3" t="str">
         <f>B2&amp;"_"&amp;D2&amp;"_"&amp;E2&amp;""</f>
         <v>2019_A Taxonomy of Cache Replacement Policies_缓存替换策略的分类</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>1158</v>
+        <v>1204</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -13173,26 +13513,26 @@
         <v>2023</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>1159</v>
+        <v>1205</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>1160</v>
+        <v>1206</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1161</v>
+        <v>1207</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>1162</v>
+        <v>1208</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>1163</v>
+        <v>1209</v>
       </c>
       <c r="H3" s="3" t="str">
         <f>B3&amp;"_"&amp;D3&amp;"_"&amp;E3&amp;""</f>
         <v>2023_Operating Systems: Three Easy Pieces_操作系统导论</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>1164</v>
+        <v>1210</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -13208,21 +13548,21 @@
         <v>284</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1165</v>
+        <v>1211</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>1166</v>
+        <v>1212</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1167</v>
+        <v>1213</v>
       </c>
       <c r="H4" s="3" t="str">
         <f>B4&amp;"_"&amp;D4&amp;""</f>
         <v>2024_大语言模型</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>1168</v>
+        <v>1214</v>
       </c>
       <c r="J4" s="3"/>
     </row>

--- a/InfoSummary.xlsx
+++ b/InfoSummary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="18408" firstSheet="2" activeTab="9"/>
+    <workbookView windowWidth="29868" windowHeight="14088" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="学位" sheetId="10" r:id="rId1"/>
@@ -6217,7 +6217,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="5.77777777777778" style="1" customWidth="1"/>
@@ -6671,6 +6671,18 @@
         <v>1305</v>
       </c>
       <c r="J14" s="6"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:10">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J14" etc:filterBottomFollowUsedRange="0">
